--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W23"/>
+  <dimension ref="A1:AM23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -544,6 +544,86 @@
           <t>Price_2025-02-18 03:04</t>
         </is>
       </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-02-19 03:05</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-02-19 03:05</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-02-20 03:04</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-02-20 03:04</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-02-21 03:04</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-02-21 03:04</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-02-22 03:05</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-02-22 03:05</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-02-23 03:04</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-02-23 03:04</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-02-24 03:04</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-02-24 03:04</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-02-25 03:05</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-02-25 03:05</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-02-25 21:06</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-02-25 21:06</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -661,6 +741,86 @@
           <t>2.929</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>2.879</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>2.879</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2.829</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>2.779</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>2.779</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>2.779</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>2.679</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>2.679</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -778,6 +938,86 @@
           <t>$2.72</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>$2.72</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>$2.72</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>$2.72</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>$2.72</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>$2.72</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>$2.72</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>$2.72</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>$2.72</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -895,6 +1135,86 @@
           <t>32¢ ea.</t>
         </is>
       </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>32¢ ea.</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>32¢ ea.</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>32¢ ea.</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>32¢ ea.</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>32¢ ea.</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>32¢ ea.</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>32¢ ea.</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>32¢ ea.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1012,6 +1332,86 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1129,6 +1529,86 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1246,6 +1726,86 @@
           <t>$3.65</t>
         </is>
       </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1363,6 +1923,86 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1480,6 +2120,86 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1597,6 +2317,86 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1714,6 +2514,86 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1831,6 +2711,86 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1948,6 +2908,86 @@
           <t>16¢ ea.</t>
         </is>
       </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>16¢ ea.</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>16¢ ea.</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>16¢ ea.</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>16¢ ea.</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>16¢ ea.</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>16¢ ea.</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>16¢ ea.</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>16¢ ea.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2065,6 +3105,86 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2182,6 +3302,86 @@
           <t>$6.99/lb</t>
         </is>
       </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>$6.99/lb</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>$6.99/lb</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>$6.99/lb</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>$6.99/lb</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>$6.99/lb</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>$6.99/lb</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>$6.99/lb</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>$6.99/lb</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2299,6 +3499,86 @@
           <t>$3.19 ea.</t>
         </is>
       </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>$3.19 ea.</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>$3.19 ea.</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>$3.19 ea.</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>$3.19 ea.</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>$3.19 ea.</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>$3.83 ea.</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>$3.19 ea.</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>$3.19 ea.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2416,6 +3696,86 @@
           <t>$40,275</t>
         </is>
       </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>2025 Ram 1500</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2485,6 +3845,54 @@
       </c>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr">
         <is>
           <t>$37,000*</t>
         </is>
@@ -2590,6 +3998,54 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr"/>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2707,6 +4163,86 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2824,6 +4360,86 @@
           <t>$5.46</t>
         </is>
       </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>$5.97</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>$5.97</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>$5.97</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>$5.97</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>$5.97</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>$5.97</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>$5.97</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>$5.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2941,6 +4557,86 @@
           <t>698</t>
         </is>
       </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3054,6 +4750,86 @@
         </is>
       </c>
       <c r="W23" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
         <is>
           <t>698</t>
         </is>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM23"/>
+  <dimension ref="A1:BE23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -624,6 +624,96 @@
           <t>Price_2025-02-25 21:06</t>
         </is>
       </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-02-26 03:05</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-02-26 03:05</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-02-27 03:04</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-02-27 03:04</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-02-28 03:05</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-02-28 03:05</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-03-01 03:04</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-03-01 03:04</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-03-02 03:05</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-03-02 03:05</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-03-03 03:05</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-03-03 03:05</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-03-04 03:04</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-03-04 03:04</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-03-04 10:51</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-03-04 10:51</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-03-04 17:48</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-03-04 17:48</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -821,6 +911,96 @@
           <t>2.679</t>
         </is>
       </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>2.679</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>2.629</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>2.629</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2.599</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>2.599</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>2.599</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>2.899</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>2.899</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>2.899</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1018,6 +1198,96 @@
           <t>$2.72</t>
         </is>
       </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>$2.72</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>$2.72</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>$2.72</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>$2.72</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>$2.72</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>$2.72</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>$2.72</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>$2.72</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>$2.72</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1215,6 +1485,96 @@
           <t>32¢ ea.</t>
         </is>
       </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>32¢ ea.</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>32¢ ea.</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>32¢ ea.</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>32¢ ea.</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>32¢ ea.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>38¢ ea.</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>38¢ ea.</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>38¢ ea.</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>38¢ ea.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1412,6 +1772,96 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1609,6 +2059,96 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1806,6 +2346,96 @@
           <t>$3.65</t>
         </is>
       </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2003,6 +2633,96 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2200,6 +2920,96 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2397,6 +3207,96 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2594,6 +3494,96 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2791,6 +3781,96 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2988,6 +4068,96 @@
           <t>16¢ ea.</t>
         </is>
       </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>16¢ ea.</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>16¢ ea.</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>16¢ ea.</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>16¢ ea.</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>16¢ ea.</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>16¢ ea.</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>16¢ ea.</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>16¢ ea.</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>16¢ ea.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3185,6 +4355,96 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>$5.89</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>$5.89</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>$5.89</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>$5.89</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3382,6 +4642,96 @@
           <t>$6.99/lb</t>
         </is>
       </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>$6.99/lb</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>$6.99/lb</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>$6.99/lb</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>$6.99/lb</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>$6.99/lb</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>$6.99/lb</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>$6.99/lb</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>$6.99/lb</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>$6.99/lb</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3579,6 +4929,96 @@
           <t>$3.19 ea.</t>
         </is>
       </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>$3.19 ea.</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>$3.19 ea.</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>$3.19 ea.</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>$3.19 ea.</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>$3.19 ea.</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>$3.19 ea.</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>$3.83 ea.</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>$3.83 ea.</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>$3.83 ea.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3776,6 +5216,96 @@
           <t>$40,275</t>
         </is>
       </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3893,6 +5423,60 @@
       </c>
       <c r="AL18" t="inlineStr"/>
       <c r="AM18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="AN18" t="inlineStr"/>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr"/>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr"/>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr"/>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr"/>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="BD18" t="inlineStr"/>
+      <c r="BE18" t="inlineStr">
         <is>
           <t>$37,000*</t>
         </is>
@@ -4046,6 +5630,60 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="AN19" t="inlineStr"/>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr"/>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr"/>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr"/>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr"/>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr"/>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4243,6 +5881,96 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="BE20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4440,6 +6168,96 @@
           <t>$5.97</t>
         </is>
       </c>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>$5.97</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>$5.97</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>$5.97</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>$5.97</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>$5.97</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>$5.97</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>$5.97</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>$5.97</t>
+        </is>
+      </c>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="BE21" t="inlineStr">
+        <is>
+          <t>$5.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4637,6 +6455,96 @@
           <t>698</t>
         </is>
       </c>
+      <c r="AN22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="BE22" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4832,6 +6740,96 @@
       <c r="AM23" t="inlineStr">
         <is>
           <t>698</t>
+        </is>
+      </c>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="BE23" t="inlineStr">
+        <is>
+          <t>748</t>
         </is>
       </c>
     </row>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BE23"/>
+  <dimension ref="A1:CM23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -714,6 +714,176 @@
           <t>Price_2025-03-04 17:48</t>
         </is>
       </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-03-05 03:05</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-03-05 03:05</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-03-06 03:05</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-03-06 03:05</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-03-07 03:04</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-03-07 03:04</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-03-08 03:04</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-03-08 03:04</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-03-09 03:04</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-03-09 03:04</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-03-10 03:05</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-03-10 03:05</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-03-11 03:04</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-03-11 03:04</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-03-12 03:05</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-03-12 03:05</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-03-13 03:05</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-03-13 03:05</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-03-14 03:04</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-03-14 03:04</t>
+        </is>
+      </c>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-03-15 03:05</t>
+        </is>
+      </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-03-15 03:05</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-03-16 03:04</t>
+        </is>
+      </c>
+      <c r="CC1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-03-16 03:04</t>
+        </is>
+      </c>
+      <c r="CD1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-03-17 03:05</t>
+        </is>
+      </c>
+      <c r="CE1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-03-17 03:05</t>
+        </is>
+      </c>
+      <c r="CF1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-03-18 03:04</t>
+        </is>
+      </c>
+      <c r="CG1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-03-18 03:04</t>
+        </is>
+      </c>
+      <c r="CH1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-03-19 03:04</t>
+        </is>
+      </c>
+      <c r="CI1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-03-19 03:04</t>
+        </is>
+      </c>
+      <c r="CJ1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-03-20 03:05</t>
+        </is>
+      </c>
+      <c r="CK1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-03-20 03:05</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-03-21 03:05</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-03-21 03:05</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1001,6 +1171,176 @@
           <t>2.899</t>
         </is>
       </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>2.899</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>2.849</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>2.849</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>2.799</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>2.799</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>2.749</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>2.699</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>2.649</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>2.599</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>2.599</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>2.599</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>2.599</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
+          <t>2.899</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="CI2" t="inlineStr">
+        <is>
+          <t>2.899</t>
+        </is>
+      </c>
+      <c r="CJ2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="CK2" t="inlineStr">
+        <is>
+          <t>2.899</t>
+        </is>
+      </c>
+      <c r="CL2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="CM2" t="inlineStr">
+        <is>
+          <t>2.899</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1288,6 +1628,176 @@
           <t>$2.72</t>
         </is>
       </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>$2.72</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>$2.72</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>$2.72</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>$2.72</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>$2.72</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>$2.72</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>$2.72</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>$2.72</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>$2.72</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>$2.72</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>$2.72</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>$2.72</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>$2.72</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
+          <t>$2.72</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="CI3" t="inlineStr">
+        <is>
+          <t>$2.72</t>
+        </is>
+      </c>
+      <c r="CJ3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="CK3" t="inlineStr">
+        <is>
+          <t>$2.72</t>
+        </is>
+      </c>
+      <c r="CL3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="CM3" t="inlineStr">
+        <is>
+          <t>$2.72</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1575,6 +2085,176 @@
           <t>38¢ ea.</t>
         </is>
       </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>38¢ ea.</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>38¢ ea.</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>38¢ ea.</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>38¢ ea.</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>38¢ ea.</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>32¢ ea.</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>32¢ ea.</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>32¢ ea.</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>32¢ ea.</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>32¢ ea.</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>32¢ ea.</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>32¢ ea.</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>38¢ ea.</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
+          <t>38¢ ea.</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="CI4" t="inlineStr">
+        <is>
+          <t>38¢ ea.</t>
+        </is>
+      </c>
+      <c r="CJ4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="CK4" t="inlineStr">
+        <is>
+          <t>38¢ ea.</t>
+        </is>
+      </c>
+      <c r="CL4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="CM4" t="inlineStr">
+        <is>
+          <t>38¢ ea.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1862,6 +2542,176 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="CI5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="CJ5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="CK5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="CL5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="CM5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2149,6 +2999,176 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="CI6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="CJ6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="CK6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="CL6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="CM6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2436,6 +3456,176 @@
           <t>$3.65</t>
         </is>
       </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="CI7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="CJ7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="CK7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="CL7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="CM7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2723,6 +3913,176 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
+          <t>$1.69</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="CI8" t="inlineStr">
+        <is>
+          <t>$1.69</t>
+        </is>
+      </c>
+      <c r="CJ8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="CK8" t="inlineStr">
+        <is>
+          <t>$1.69</t>
+        </is>
+      </c>
+      <c r="CL8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="CM8" t="inlineStr">
+        <is>
+          <t>$1.69</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3010,6 +4370,176 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="CI9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="CJ9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="CK9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="CL9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="CM9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3297,6 +4827,176 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="CI10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="CJ10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="CK10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="CL10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="CM10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3584,6 +5284,176 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
+      <c r="BX11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="CI11" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
+      <c r="CJ11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="CK11" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
+      <c r="CL11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="CM11" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3871,6 +5741,176 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="BV12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="BX12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="BY12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="BZ12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="CC12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="CH12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="CI12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="CJ12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="CK12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="CL12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="CM12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4158,6 +6198,176 @@
           <t>16¢ ea.</t>
         </is>
       </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>16¢ ea.</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>16¢ ea.</t>
+        </is>
+      </c>
+      <c r="BJ13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="BK13" t="inlineStr">
+        <is>
+          <t>16¢ ea.</t>
+        </is>
+      </c>
+      <c r="BL13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="BM13" t="inlineStr">
+        <is>
+          <t>16¢ ea.</t>
+        </is>
+      </c>
+      <c r="BN13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="BO13" t="inlineStr">
+        <is>
+          <t>16¢ ea.</t>
+        </is>
+      </c>
+      <c r="BP13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="BQ13" t="inlineStr">
+        <is>
+          <t>16¢ ea.</t>
+        </is>
+      </c>
+      <c r="BR13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="BS13" t="inlineStr">
+        <is>
+          <t>16¢ ea.</t>
+        </is>
+      </c>
+      <c r="BT13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="BU13" t="inlineStr">
+        <is>
+          <t>16¢ ea.</t>
+        </is>
+      </c>
+      <c r="BV13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="BW13" t="inlineStr">
+        <is>
+          <t>16¢ ea.</t>
+        </is>
+      </c>
+      <c r="BX13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="BY13" t="inlineStr">
+        <is>
+          <t>16¢ ea.</t>
+        </is>
+      </c>
+      <c r="BZ13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="CA13" t="inlineStr">
+        <is>
+          <t>16¢ ea.</t>
+        </is>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="CC13" t="inlineStr">
+        <is>
+          <t>16¢ ea.</t>
+        </is>
+      </c>
+      <c r="CD13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="CE13" t="inlineStr">
+        <is>
+          <t>16¢ ea.</t>
+        </is>
+      </c>
+      <c r="CF13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="CG13" t="inlineStr">
+        <is>
+          <t>16¢ ea.</t>
+        </is>
+      </c>
+      <c r="CH13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="CI13" t="inlineStr">
+        <is>
+          <t>16¢ ea.</t>
+        </is>
+      </c>
+      <c r="CJ13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="CK13" t="inlineStr">
+        <is>
+          <t>16¢ ea.</t>
+        </is>
+      </c>
+      <c r="CL13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="CM13" t="inlineStr">
+        <is>
+          <t>16¢ ea.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4445,6 +6655,176 @@
           <t>$5.89</t>
         </is>
       </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>$5.89</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>$5.89</t>
+        </is>
+      </c>
+      <c r="BJ14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="BK14" t="inlineStr">
+        <is>
+          <t>$5.89</t>
+        </is>
+      </c>
+      <c r="BL14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="BM14" t="inlineStr">
+        <is>
+          <t>$5.89</t>
+        </is>
+      </c>
+      <c r="BN14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="BO14" t="inlineStr">
+        <is>
+          <t>$5.89</t>
+        </is>
+      </c>
+      <c r="BP14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="BQ14" t="inlineStr">
+        <is>
+          <t>$5.89</t>
+        </is>
+      </c>
+      <c r="BR14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="BS14" t="inlineStr">
+        <is>
+          <t>$5.89</t>
+        </is>
+      </c>
+      <c r="BT14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="BU14" t="inlineStr">
+        <is>
+          <t>$5.89</t>
+        </is>
+      </c>
+      <c r="BV14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="BW14" t="inlineStr">
+        <is>
+          <t>$5.89</t>
+        </is>
+      </c>
+      <c r="BX14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="BY14" t="inlineStr">
+        <is>
+          <t>$5.89</t>
+        </is>
+      </c>
+      <c r="BZ14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="CA14" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="CC14" t="inlineStr">
+        <is>
+          <t>$5.89</t>
+        </is>
+      </c>
+      <c r="CD14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="CE14" t="inlineStr">
+        <is>
+          <t>$5.89</t>
+        </is>
+      </c>
+      <c r="CF14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="CG14" t="inlineStr">
+        <is>
+          <t>$5.89</t>
+        </is>
+      </c>
+      <c r="CH14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="CI14" t="inlineStr">
+        <is>
+          <t>$5.89</t>
+        </is>
+      </c>
+      <c r="CJ14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="CK14" t="inlineStr">
+        <is>
+          <t>$5.89</t>
+        </is>
+      </c>
+      <c r="CL14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="CM14" t="inlineStr">
+        <is>
+          <t>$5.89</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4732,6 +7112,176 @@
           <t>$6.99/lb</t>
         </is>
       </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>$6.99/lb</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="BI15" t="inlineStr">
+        <is>
+          <t>$6.99/lb</t>
+        </is>
+      </c>
+      <c r="BJ15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="BK15" t="inlineStr">
+        <is>
+          <t>$6.99/lb</t>
+        </is>
+      </c>
+      <c r="BL15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="BM15" t="inlineStr">
+        <is>
+          <t>$6.99/lb</t>
+        </is>
+      </c>
+      <c r="BN15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="BO15" t="inlineStr">
+        <is>
+          <t>$6.99/lb</t>
+        </is>
+      </c>
+      <c r="BP15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="BQ15" t="inlineStr">
+        <is>
+          <t>$6.99/lb</t>
+        </is>
+      </c>
+      <c r="BR15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="BS15" t="inlineStr">
+        <is>
+          <t>$6.99/lb</t>
+        </is>
+      </c>
+      <c r="BT15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="BU15" t="inlineStr">
+        <is>
+          <t>$6.99/lb</t>
+        </is>
+      </c>
+      <c r="BV15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="BW15" t="inlineStr">
+        <is>
+          <t>$6.99/lb</t>
+        </is>
+      </c>
+      <c r="BX15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="BY15" t="inlineStr">
+        <is>
+          <t>$6.99/lb</t>
+        </is>
+      </c>
+      <c r="BZ15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="CA15" t="inlineStr">
+        <is>
+          <t>$6.99/lb</t>
+        </is>
+      </c>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="CC15" t="inlineStr">
+        <is>
+          <t>$6.99/lb</t>
+        </is>
+      </c>
+      <c r="CD15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="CE15" t="inlineStr">
+        <is>
+          <t>$6.99/lb</t>
+        </is>
+      </c>
+      <c r="CF15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="CG15" t="inlineStr">
+        <is>
+          <t>$6.99/lb</t>
+        </is>
+      </c>
+      <c r="CH15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="CI15" t="inlineStr">
+        <is>
+          <t>$6.99/lb</t>
+        </is>
+      </c>
+      <c r="CJ15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="CK15" t="inlineStr">
+        <is>
+          <t>$6.99/lb</t>
+        </is>
+      </c>
+      <c r="CL15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="CM15" t="inlineStr">
+        <is>
+          <t>$6.99/lb</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5019,6 +7569,176 @@
           <t>$3.83 ea.</t>
         </is>
       </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>$3.83 ea.</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="BI16" t="inlineStr">
+        <is>
+          <t>$3.83 ea.</t>
+        </is>
+      </c>
+      <c r="BJ16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="BK16" t="inlineStr">
+        <is>
+          <t>$3.83 ea.</t>
+        </is>
+      </c>
+      <c r="BL16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="BM16" t="inlineStr">
+        <is>
+          <t>$3.83 ea.</t>
+        </is>
+      </c>
+      <c r="BN16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="BO16" t="inlineStr">
+        <is>
+          <t>$3.83 ea.</t>
+        </is>
+      </c>
+      <c r="BP16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="BQ16" t="inlineStr">
+        <is>
+          <t>$3.83 ea.</t>
+        </is>
+      </c>
+      <c r="BR16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="BS16" t="inlineStr">
+        <is>
+          <t>$3.83 ea.</t>
+        </is>
+      </c>
+      <c r="BT16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="BU16" t="inlineStr">
+        <is>
+          <t>$3.83 ea.</t>
+        </is>
+      </c>
+      <c r="BV16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="BW16" t="inlineStr">
+        <is>
+          <t>$3.83 ea.</t>
+        </is>
+      </c>
+      <c r="BX16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="BY16" t="inlineStr">
+        <is>
+          <t>$3.83 ea.</t>
+        </is>
+      </c>
+      <c r="BZ16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="CA16" t="inlineStr">
+        <is>
+          <t>$3.83 ea.</t>
+        </is>
+      </c>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="CC16" t="inlineStr">
+        <is>
+          <t>$3.83 ea.</t>
+        </is>
+      </c>
+      <c r="CD16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="CE16" t="inlineStr">
+        <is>
+          <t>$3.83 ea.</t>
+        </is>
+      </c>
+      <c r="CF16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="CG16" t="inlineStr">
+        <is>
+          <t>$3.83 ea.</t>
+        </is>
+      </c>
+      <c r="CH16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="CI16" t="inlineStr">
+        <is>
+          <t>$3.83 ea.</t>
+        </is>
+      </c>
+      <c r="CJ16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="CK16" t="inlineStr">
+        <is>
+          <t>$3.83 ea.</t>
+        </is>
+      </c>
+      <c r="CL16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="CM16" t="inlineStr">
+        <is>
+          <t>$3.83 ea.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5306,6 +8026,176 @@
           <t>$40,275</t>
         </is>
       </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="BI17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="BJ17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="BK17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="BL17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="BM17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="BN17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="BO17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="BP17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="BQ17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="BR17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="BS17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="BT17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="BU17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="BV17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="BW17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="BX17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="BY17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="BZ17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="CA17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="CB17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="CC17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="CD17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="CE17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="CF17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="CG17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="CH17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="CI17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="CJ17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="CK17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="CL17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="CM17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5477,6 +8367,108 @@
       </c>
       <c r="BD18" t="inlineStr"/>
       <c r="BE18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr"/>
+      <c r="BI18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="BJ18" t="inlineStr"/>
+      <c r="BK18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="BL18" t="inlineStr"/>
+      <c r="BM18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="BN18" t="inlineStr"/>
+      <c r="BO18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="BP18" t="inlineStr"/>
+      <c r="BQ18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="BR18" t="inlineStr"/>
+      <c r="BS18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="BT18" t="inlineStr"/>
+      <c r="BU18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="BV18" t="inlineStr"/>
+      <c r="BW18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="BX18" t="inlineStr"/>
+      <c r="BY18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="BZ18" t="inlineStr"/>
+      <c r="CA18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="CB18" t="inlineStr"/>
+      <c r="CC18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="CD18" t="inlineStr"/>
+      <c r="CE18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="CF18" t="inlineStr"/>
+      <c r="CG18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="CH18" t="inlineStr"/>
+      <c r="CI18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="CJ18" t="inlineStr"/>
+      <c r="CK18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="CL18" t="inlineStr"/>
+      <c r="CM18" t="inlineStr">
         <is>
           <t>$37,000*</t>
         </is>
@@ -5684,6 +8676,108 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="BF19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr"/>
+      <c r="BI19" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="BJ19" t="inlineStr"/>
+      <c r="BK19" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="BL19" t="inlineStr"/>
+      <c r="BM19" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="BN19" t="inlineStr"/>
+      <c r="BO19" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="BP19" t="inlineStr"/>
+      <c r="BQ19" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="BR19" t="inlineStr"/>
+      <c r="BS19" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="BT19" t="inlineStr"/>
+      <c r="BU19" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="BV19" t="inlineStr"/>
+      <c r="BW19" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="BX19" t="inlineStr"/>
+      <c r="BY19" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="BZ19" t="inlineStr"/>
+      <c r="CA19" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="CB19" t="inlineStr"/>
+      <c r="CC19" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="CD19" t="inlineStr"/>
+      <c r="CE19" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="CF19" t="inlineStr"/>
+      <c r="CG19" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="CH19" t="inlineStr"/>
+      <c r="CI19" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="CJ19" t="inlineStr"/>
+      <c r="CK19" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="CL19" t="inlineStr"/>
+      <c r="CM19" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5971,6 +9065,176 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="BF20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="BG20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="BI20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="BJ20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="BK20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="BL20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="BM20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="BN20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="BO20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="BP20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="BQ20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="BR20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="BS20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="BT20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="BU20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="BV20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="BW20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="BX20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="BY20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="BZ20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="CA20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="CB20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="CC20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="CD20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="CE20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="CF20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="CG20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="CH20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="CI20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="CJ20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="CK20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="CL20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="CM20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6258,6 +9522,176 @@
           <t>$5.97</t>
         </is>
       </c>
+      <c r="BF21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="BG21" t="inlineStr">
+        <is>
+          <t>$5.97</t>
+        </is>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="BI21" t="inlineStr">
+        <is>
+          <t>$5.97</t>
+        </is>
+      </c>
+      <c r="BJ21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="BK21" t="inlineStr">
+        <is>
+          <t>$5.97</t>
+        </is>
+      </c>
+      <c r="BL21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="BM21" t="inlineStr">
+        <is>
+          <t>$5.97</t>
+        </is>
+      </c>
+      <c r="BN21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="BO21" t="inlineStr">
+        <is>
+          <t>$5.97</t>
+        </is>
+      </c>
+      <c r="BP21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="BQ21" t="inlineStr">
+        <is>
+          <t>$5.97</t>
+        </is>
+      </c>
+      <c r="BR21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="BS21" t="inlineStr">
+        <is>
+          <t>$5.97</t>
+        </is>
+      </c>
+      <c r="BT21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="BU21" t="inlineStr">
+        <is>
+          <t>$5.97</t>
+        </is>
+      </c>
+      <c r="BV21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="BW21" t="inlineStr">
+        <is>
+          <t>$5.97</t>
+        </is>
+      </c>
+      <c r="BX21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="BY21" t="inlineStr">
+        <is>
+          <t>$5.97</t>
+        </is>
+      </c>
+      <c r="BZ21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="CA21" t="inlineStr">
+        <is>
+          <t>$5.97</t>
+        </is>
+      </c>
+      <c r="CB21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="CC21" t="inlineStr">
+        <is>
+          <t>$5.97</t>
+        </is>
+      </c>
+      <c r="CD21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="CE21" t="inlineStr">
+        <is>
+          <t>$5.97</t>
+        </is>
+      </c>
+      <c r="CF21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="CG21" t="inlineStr">
+        <is>
+          <t>$5.97</t>
+        </is>
+      </c>
+      <c r="CH21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="CI21" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="CJ21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="CK21" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="CL21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="CM21" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6545,6 +9979,176 @@
           <t>748</t>
         </is>
       </c>
+      <c r="BF22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="BG22" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="BI22" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="BJ22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="BK22" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="BL22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="BM22" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="BN22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="BO22" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="BP22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="BQ22" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="BR22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="BS22" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="BT22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="BU22" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="BV22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="BW22" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="BX22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="BY22" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="BZ22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="CA22" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="CB22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="CC22" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="CD22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="CE22" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="CF22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="CG22" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="CH22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="CI22" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="CJ22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="CK22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="CL22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="CM22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -6830,6 +10434,176 @@
       <c r="BE23" t="inlineStr">
         <is>
           <t>748</t>
+        </is>
+      </c>
+      <c r="BF23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="BG23" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="BI23" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="BJ23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="BK23" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="BL23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="BM23" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="BN23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="BO23" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="BP23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="BQ23" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="BR23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="BS23" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="BT23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="BU23" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="BV23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="BW23" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="BX23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="BY23" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="BZ23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="CA23" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="CB23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="CC23" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="CD23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="CE23" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="CF23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="CG23" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="CH23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="CI23" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="CJ23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="CK23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="CL23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="CM23" t="inlineStr">
+        <is>
+          <t>Not found</t>
         </is>
       </c>
     </row>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CM23"/>
+  <dimension ref="A1:FC23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -884,6 +884,346 @@
           <t>Price_2025-03-21 03:05</t>
         </is>
       </c>
+      <c r="CN1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-03-21 10:49</t>
+        </is>
+      </c>
+      <c r="CO1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-03-21 10:49</t>
+        </is>
+      </c>
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-03-22 03:03</t>
+        </is>
+      </c>
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-03-22 03:03</t>
+        </is>
+      </c>
+      <c r="CR1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-03-23 03:07</t>
+        </is>
+      </c>
+      <c r="CS1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-03-23 03:07</t>
+        </is>
+      </c>
+      <c r="CT1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-03-24 03:05</t>
+        </is>
+      </c>
+      <c r="CU1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-03-24 03:05</t>
+        </is>
+      </c>
+      <c r="CV1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-03-25 03:04</t>
+        </is>
+      </c>
+      <c r="CW1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-03-25 03:04</t>
+        </is>
+      </c>
+      <c r="CX1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-03-26 03:04</t>
+        </is>
+      </c>
+      <c r="CY1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-03-26 03:04</t>
+        </is>
+      </c>
+      <c r="CZ1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-03-27 03:03</t>
+        </is>
+      </c>
+      <c r="DA1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-03-27 03:03</t>
+        </is>
+      </c>
+      <c r="DB1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-03-28 03:04</t>
+        </is>
+      </c>
+      <c r="DC1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-03-28 03:04</t>
+        </is>
+      </c>
+      <c r="DD1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-03-29 03:05</t>
+        </is>
+      </c>
+      <c r="DE1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-03-29 03:05</t>
+        </is>
+      </c>
+      <c r="DF1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-03-30 03:05</t>
+        </is>
+      </c>
+      <c r="DG1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-03-30 03:05</t>
+        </is>
+      </c>
+      <c r="DH1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-03-31 03:03</t>
+        </is>
+      </c>
+      <c r="DI1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-03-31 03:03</t>
+        </is>
+      </c>
+      <c r="DJ1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-04-01 03:03</t>
+        </is>
+      </c>
+      <c r="DK1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-04-01 03:03</t>
+        </is>
+      </c>
+      <c r="DL1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-04-02 03:04</t>
+        </is>
+      </c>
+      <c r="DM1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-04-02 03:04</t>
+        </is>
+      </c>
+      <c r="DN1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-04-03 03:05</t>
+        </is>
+      </c>
+      <c r="DO1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-04-03 03:05</t>
+        </is>
+      </c>
+      <c r="DP1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-04-04 03:04</t>
+        </is>
+      </c>
+      <c r="DQ1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-04-04 03:04</t>
+        </is>
+      </c>
+      <c r="DR1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-04-05 03:05</t>
+        </is>
+      </c>
+      <c r="DS1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-04-05 03:05</t>
+        </is>
+      </c>
+      <c r="DT1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-04-06 03:04</t>
+        </is>
+      </c>
+      <c r="DU1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-04-06 03:04</t>
+        </is>
+      </c>
+      <c r="DV1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-04-07 03:04</t>
+        </is>
+      </c>
+      <c r="DW1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-04-07 03:04</t>
+        </is>
+      </c>
+      <c r="DX1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-04-08 03:05</t>
+        </is>
+      </c>
+      <c r="DY1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-04-08 03:05</t>
+        </is>
+      </c>
+      <c r="DZ1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-04-09 03:10</t>
+        </is>
+      </c>
+      <c r="EA1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-04-09 03:10</t>
+        </is>
+      </c>
+      <c r="EB1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-04-10 03:05</t>
+        </is>
+      </c>
+      <c r="EC1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-04-10 03:05</t>
+        </is>
+      </c>
+      <c r="ED1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-04-11 03:04</t>
+        </is>
+      </c>
+      <c r="EE1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-04-11 03:04</t>
+        </is>
+      </c>
+      <c r="EF1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-04-12 03:04</t>
+        </is>
+      </c>
+      <c r="EG1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-04-12 03:04</t>
+        </is>
+      </c>
+      <c r="EH1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-04-13 03:05</t>
+        </is>
+      </c>
+      <c r="EI1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-04-13 03:05</t>
+        </is>
+      </c>
+      <c r="EJ1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-04-14 03:05</t>
+        </is>
+      </c>
+      <c r="EK1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-04-14 03:05</t>
+        </is>
+      </c>
+      <c r="EL1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-04-15 03:04</t>
+        </is>
+      </c>
+      <c r="EM1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-04-15 03:04</t>
+        </is>
+      </c>
+      <c r="EN1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-04-16 03:05</t>
+        </is>
+      </c>
+      <c r="EO1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-04-16 03:05</t>
+        </is>
+      </c>
+      <c r="EP1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-04-17 03:04</t>
+        </is>
+      </c>
+      <c r="EQ1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-04-17 03:04</t>
+        </is>
+      </c>
+      <c r="ER1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-04-18 03:04</t>
+        </is>
+      </c>
+      <c r="ES1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-04-18 03:04</t>
+        </is>
+      </c>
+      <c r="ET1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-04-19 03:05</t>
+        </is>
+      </c>
+      <c r="EU1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-04-19 03:05</t>
+        </is>
+      </c>
+      <c r="EV1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-04-20 03:04</t>
+        </is>
+      </c>
+      <c r="EW1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-04-20 03:04</t>
+        </is>
+      </c>
+      <c r="EX1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-04-21 03:05</t>
+        </is>
+      </c>
+      <c r="EY1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-04-21 03:05</t>
+        </is>
+      </c>
+      <c r="EZ1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-04-22 03:04</t>
+        </is>
+      </c>
+      <c r="FA1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-04-22 03:04</t>
+        </is>
+      </c>
+      <c r="FB1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-04-23 03:05</t>
+        </is>
+      </c>
+      <c r="FC1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-04-23 03:05</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1341,6 +1681,346 @@
           <t>2.899</t>
         </is>
       </c>
+      <c r="CN2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="CO2" t="inlineStr">
+        <is>
+          <t>2.899</t>
+        </is>
+      </c>
+      <c r="CP2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>2.899</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="CS2" t="inlineStr">
+        <is>
+          <t>2.899</t>
+        </is>
+      </c>
+      <c r="CT2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="CU2" t="inlineStr">
+        <is>
+          <t>2.749</t>
+        </is>
+      </c>
+      <c r="CV2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>2.749</t>
+        </is>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>2.999</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>2.999</t>
+        </is>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>2.999</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>2.899</t>
+        </is>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>2.849</t>
+        </is>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>2.849</t>
+        </is>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>2.789</t>
+        </is>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>2.789</t>
+        </is>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>2.789</t>
+        </is>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>2.789</t>
+        </is>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>2.779</t>
+        </is>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>2.759</t>
+        </is>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="DW2" t="inlineStr">
+        <is>
+          <t>2.739</t>
+        </is>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="DY2" t="inlineStr">
+        <is>
+          <t>2.709</t>
+        </is>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>2.709</t>
+        </is>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>2.689</t>
+        </is>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>2.639</t>
+        </is>
+      </c>
+      <c r="EF2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="EG2" t="inlineStr">
+        <is>
+          <t>2.639</t>
+        </is>
+      </c>
+      <c r="EH2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>2.629</t>
+        </is>
+      </c>
+      <c r="EJ2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="EK2" t="inlineStr">
+        <is>
+          <t>2.629</t>
+        </is>
+      </c>
+      <c r="EL2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="EM2" t="inlineStr">
+        <is>
+          <t>2.629</t>
+        </is>
+      </c>
+      <c r="EN2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="EO2" t="inlineStr">
+        <is>
+          <t>2.629</t>
+        </is>
+      </c>
+      <c r="EP2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="EQ2" t="inlineStr">
+        <is>
+          <t>2.629</t>
+        </is>
+      </c>
+      <c r="ER2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="ES2" t="inlineStr">
+        <is>
+          <t>2.629</t>
+        </is>
+      </c>
+      <c r="ET2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="EU2" t="inlineStr">
+        <is>
+          <t>2.589</t>
+        </is>
+      </c>
+      <c r="EV2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="EW2" t="inlineStr">
+        <is>
+          <t>2.589</t>
+        </is>
+      </c>
+      <c r="EX2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="EY2" t="inlineStr">
+        <is>
+          <t>2.589</t>
+        </is>
+      </c>
+      <c r="EZ2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="FA2" t="inlineStr">
+        <is>
+          <t>2.999</t>
+        </is>
+      </c>
+      <c r="FB2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="FC2" t="inlineStr">
+        <is>
+          <t>2.999</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1798,6 +2478,346 @@
           <t>$2.72</t>
         </is>
       </c>
+      <c r="CN3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="CO3" t="inlineStr">
+        <is>
+          <t>$2.72</t>
+        </is>
+      </c>
+      <c r="CP3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="CQ3" t="inlineStr">
+        <is>
+          <t>$2.72</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="CS3" t="inlineStr">
+        <is>
+          <t>$2.72</t>
+        </is>
+      </c>
+      <c r="CT3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="CU3" t="inlineStr">
+        <is>
+          <t>$2.72</t>
+        </is>
+      </c>
+      <c r="CV3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="CW3" t="inlineStr">
+        <is>
+          <t>$2.72</t>
+        </is>
+      </c>
+      <c r="CX3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="CY3" t="inlineStr">
+        <is>
+          <t>$2.72</t>
+        </is>
+      </c>
+      <c r="CZ3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="DA3" t="inlineStr">
+        <is>
+          <t>$2.72</t>
+        </is>
+      </c>
+      <c r="DB3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="DC3" t="inlineStr">
+        <is>
+          <t>$2.72</t>
+        </is>
+      </c>
+      <c r="DD3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="DE3" t="inlineStr">
+        <is>
+          <t>$2.72</t>
+        </is>
+      </c>
+      <c r="DF3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="DG3" t="inlineStr">
+        <is>
+          <t>$2.72</t>
+        </is>
+      </c>
+      <c r="DH3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="DI3" t="inlineStr">
+        <is>
+          <t>$2.72</t>
+        </is>
+      </c>
+      <c r="DJ3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="DK3" t="inlineStr">
+        <is>
+          <t>$2.72</t>
+        </is>
+      </c>
+      <c r="DL3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="DM3" t="inlineStr">
+        <is>
+          <t>$2.72</t>
+        </is>
+      </c>
+      <c r="DN3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="DO3" t="inlineStr">
+        <is>
+          <t>$2.72</t>
+        </is>
+      </c>
+      <c r="DP3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="DQ3" t="inlineStr">
+        <is>
+          <t>$2.72</t>
+        </is>
+      </c>
+      <c r="DR3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="DS3" t="inlineStr">
+        <is>
+          <t>$2.72</t>
+        </is>
+      </c>
+      <c r="DT3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="DU3" t="inlineStr">
+        <is>
+          <t>$2.72</t>
+        </is>
+      </c>
+      <c r="DV3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="DW3" t="inlineStr">
+        <is>
+          <t>$2.72</t>
+        </is>
+      </c>
+      <c r="DX3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="DY3" t="inlineStr">
+        <is>
+          <t>$2.87</t>
+        </is>
+      </c>
+      <c r="DZ3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="EA3" t="inlineStr">
+        <is>
+          <t>$2.87</t>
+        </is>
+      </c>
+      <c r="EB3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="EC3" t="inlineStr">
+        <is>
+          <t>$2.87</t>
+        </is>
+      </c>
+      <c r="ED3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="EE3" t="inlineStr">
+        <is>
+          <t>$2.87</t>
+        </is>
+      </c>
+      <c r="EF3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="EG3" t="inlineStr">
+        <is>
+          <t>$2.87</t>
+        </is>
+      </c>
+      <c r="EH3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="EI3" t="inlineStr">
+        <is>
+          <t>$2.87</t>
+        </is>
+      </c>
+      <c r="EJ3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="EK3" t="inlineStr">
+        <is>
+          <t>$2.87</t>
+        </is>
+      </c>
+      <c r="EL3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="EM3" t="inlineStr">
+        <is>
+          <t>$2.87</t>
+        </is>
+      </c>
+      <c r="EN3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="EO3" t="inlineStr">
+        <is>
+          <t>$2.87</t>
+        </is>
+      </c>
+      <c r="EP3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="EQ3" t="inlineStr">
+        <is>
+          <t>$2.87</t>
+        </is>
+      </c>
+      <c r="ER3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="ES3" t="inlineStr">
+        <is>
+          <t>$2.87</t>
+        </is>
+      </c>
+      <c r="ET3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="EU3" t="inlineStr">
+        <is>
+          <t>$2.87</t>
+        </is>
+      </c>
+      <c r="EV3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="EW3" t="inlineStr">
+        <is>
+          <t>$2.87</t>
+        </is>
+      </c>
+      <c r="EX3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="EY3" t="inlineStr">
+        <is>
+          <t>$2.87</t>
+        </is>
+      </c>
+      <c r="EZ3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="FA3" t="inlineStr">
+        <is>
+          <t>$2.87</t>
+        </is>
+      </c>
+      <c r="FB3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="FC3" t="inlineStr">
+        <is>
+          <t>$2.87</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2255,6 +3275,346 @@
           <t>38¢ ea.</t>
         </is>
       </c>
+      <c r="CN4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="CO4" t="inlineStr">
+        <is>
+          <t>38¢ ea.</t>
+        </is>
+      </c>
+      <c r="CP4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="CQ4" t="inlineStr">
+        <is>
+          <t>38¢ ea.</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="CS4" t="inlineStr">
+        <is>
+          <t>38¢ ea.</t>
+        </is>
+      </c>
+      <c r="CT4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="CU4" t="inlineStr">
+        <is>
+          <t>38¢ ea.</t>
+        </is>
+      </c>
+      <c r="CV4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="CW4" t="inlineStr">
+        <is>
+          <t>38¢ ea.</t>
+        </is>
+      </c>
+      <c r="CX4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="CY4" t="inlineStr">
+        <is>
+          <t>38¢ ea.</t>
+        </is>
+      </c>
+      <c r="CZ4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="DA4" t="inlineStr">
+        <is>
+          <t>38¢ ea.</t>
+        </is>
+      </c>
+      <c r="DB4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="DC4" t="inlineStr">
+        <is>
+          <t>30¢ ea.</t>
+        </is>
+      </c>
+      <c r="DD4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="DE4" t="inlineStr">
+        <is>
+          <t>30¢ ea.</t>
+        </is>
+      </c>
+      <c r="DF4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="DG4" t="inlineStr">
+        <is>
+          <t>30¢ ea.</t>
+        </is>
+      </c>
+      <c r="DH4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="DI4" t="inlineStr">
+        <is>
+          <t>38¢ ea.</t>
+        </is>
+      </c>
+      <c r="DJ4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="DK4" t="inlineStr">
+        <is>
+          <t>38¢ ea.</t>
+        </is>
+      </c>
+      <c r="DL4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="DM4" t="inlineStr">
+        <is>
+          <t>38¢ ea.</t>
+        </is>
+      </c>
+      <c r="DN4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="DO4" t="inlineStr">
+        <is>
+          <t>38¢ ea.</t>
+        </is>
+      </c>
+      <c r="DP4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="DQ4" t="inlineStr">
+        <is>
+          <t>38¢ ea.</t>
+        </is>
+      </c>
+      <c r="DR4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="DS4" t="inlineStr">
+        <is>
+          <t>38¢ ea.</t>
+        </is>
+      </c>
+      <c r="DT4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="DU4" t="inlineStr">
+        <is>
+          <t>38¢ ea.</t>
+        </is>
+      </c>
+      <c r="DV4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="DW4" t="inlineStr">
+        <is>
+          <t>38¢ ea.</t>
+        </is>
+      </c>
+      <c r="DX4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="DY4" t="inlineStr">
+        <is>
+          <t>38¢ ea.</t>
+        </is>
+      </c>
+      <c r="DZ4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="EA4" t="inlineStr">
+        <is>
+          <t>38¢ ea.</t>
+        </is>
+      </c>
+      <c r="EB4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="EC4" t="inlineStr">
+        <is>
+          <t>38¢ ea.</t>
+        </is>
+      </c>
+      <c r="ED4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="EE4" t="inlineStr">
+        <is>
+          <t>38¢ ea.</t>
+        </is>
+      </c>
+      <c r="EF4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="EG4" t="inlineStr">
+        <is>
+          <t>38¢ ea.</t>
+        </is>
+      </c>
+      <c r="EH4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="EI4" t="inlineStr">
+        <is>
+          <t>38¢ ea.</t>
+        </is>
+      </c>
+      <c r="EJ4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="EK4" t="inlineStr">
+        <is>
+          <t>32¢ ea.</t>
+        </is>
+      </c>
+      <c r="EL4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="EM4" t="inlineStr">
+        <is>
+          <t>32¢ ea.</t>
+        </is>
+      </c>
+      <c r="EN4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="EO4" t="inlineStr">
+        <is>
+          <t>32¢ ea.</t>
+        </is>
+      </c>
+      <c r="EP4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="EQ4" t="inlineStr">
+        <is>
+          <t>32¢ ea.</t>
+        </is>
+      </c>
+      <c r="ER4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="ES4" t="inlineStr">
+        <is>
+          <t>32¢ ea.</t>
+        </is>
+      </c>
+      <c r="ET4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="EU4" t="inlineStr">
+        <is>
+          <t>32¢ ea.</t>
+        </is>
+      </c>
+      <c r="EV4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="EW4" t="inlineStr">
+        <is>
+          <t>32¢ ea.</t>
+        </is>
+      </c>
+      <c r="EX4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="EY4" t="inlineStr">
+        <is>
+          <t>32¢ ea.</t>
+        </is>
+      </c>
+      <c r="EZ4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="FA4" t="inlineStr">
+        <is>
+          <t>32¢ ea.</t>
+        </is>
+      </c>
+      <c r="FB4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="FC4" t="inlineStr">
+        <is>
+          <t>32¢ ea.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2712,6 +4072,346 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="CN5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="CO5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="CP5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="CQ5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="CS5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="CT5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="CU5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="CV5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="CW5" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="CX5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="CY5" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="CZ5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="DA5" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="DB5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="DC5" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="DD5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="DE5" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="DF5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="DG5" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="DH5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="DI5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="DJ5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="DK5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="DL5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="DM5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="DN5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="DO5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="DP5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="DQ5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="DR5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="DS5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="DT5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="DU5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="DV5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="DW5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="DX5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="DY5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="DZ5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="EA5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="EB5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="EC5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="ED5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="EE5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="EF5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="EG5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="EH5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="EI5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="EJ5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="EK5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="EL5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="EM5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="EN5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="EO5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="EP5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="EQ5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="ER5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="ES5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="ET5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="EU5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="EV5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="EW5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="EX5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="EY5" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="EZ5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="FA5" t="inlineStr">
+        <is>
+          <t>$4.59</t>
+        </is>
+      </c>
+      <c r="FB5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="FC5" t="inlineStr">
+        <is>
+          <t>$4.59</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3169,6 +4869,346 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="CN6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="CO6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="CP6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="CQ6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="CR6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="CS6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="CT6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="CU6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="CV6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="CW6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="CX6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="CY6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="CZ6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="DA6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="DB6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="DC6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="DD6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="DE6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="DF6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="DG6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="DH6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="DI6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="DJ6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="DK6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="DL6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="DM6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="DN6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="DO6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="DP6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="DQ6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="DR6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="DS6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="DT6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="DU6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="DV6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="DW6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="DX6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="DY6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="DZ6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="EA6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="EB6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="EC6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="ED6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="EE6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="EF6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="EG6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="EH6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="EI6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="EJ6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="EK6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="EL6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="EM6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="EN6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="EO6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="EP6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="EQ6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="ER6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="ES6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="ET6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="EU6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="EV6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="EW6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="EX6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="EY6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="EZ6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="FA6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="FB6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="FC6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3626,6 +5666,346 @@
           <t>$3.65</t>
         </is>
       </c>
+      <c r="CN7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="CO7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="CP7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="CQ7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="CR7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="CS7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="CT7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="CU7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="CV7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="CW7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="CX7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="CY7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="CZ7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="DA7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="DB7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="DC7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="DD7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="DE7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="DF7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="DG7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="DH7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="DI7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="DJ7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="DK7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="DL7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="DM7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="DN7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="DO7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="DP7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="DQ7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="DR7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="DS7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="DT7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="DU7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="DV7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="DW7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="DX7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="DY7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="DZ7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="EA7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="EB7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="EC7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="ED7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="EE7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="EF7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="EG7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="EH7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="EI7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="EJ7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="EK7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="EL7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="EM7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="EN7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="EO7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="EP7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="EQ7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="ER7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="ES7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="ET7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="EU7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="EV7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="EW7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="EX7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="EY7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="EZ7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="FA7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="FB7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="FC7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4083,6 +6463,346 @@
           <t>$1.69</t>
         </is>
       </c>
+      <c r="CN8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="CO8" t="inlineStr">
+        <is>
+          <t>$1.69</t>
+        </is>
+      </c>
+      <c r="CP8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="CQ8" t="inlineStr">
+        <is>
+          <t>$1.69</t>
+        </is>
+      </c>
+      <c r="CR8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="CS8" t="inlineStr">
+        <is>
+          <t>$1.69</t>
+        </is>
+      </c>
+      <c r="CT8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="CU8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
+      <c r="CV8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="CW8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
+      <c r="CX8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="CY8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
+      <c r="CZ8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="DA8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
+      <c r="DB8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="DC8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
+      <c r="DD8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="DE8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
+      <c r="DF8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="DG8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
+      <c r="DH8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="DI8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
+      <c r="DJ8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="DK8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
+      <c r="DL8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="DM8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
+      <c r="DN8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="DO8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
+      <c r="DP8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="DQ8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
+      <c r="DR8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="DS8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
+      <c r="DT8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="DU8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
+      <c r="DV8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="DW8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
+      <c r="DX8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="DY8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
+      <c r="DZ8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="EA8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
+      <c r="EB8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="EC8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
+      <c r="ED8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="EE8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
+      <c r="EF8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="EG8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
+      <c r="EH8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="EI8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
+      <c r="EJ8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="EK8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
+      <c r="EL8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="EM8" t="inlineStr">
+        <is>
+          <t>$1.77</t>
+        </is>
+      </c>
+      <c r="EN8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="EO8" t="inlineStr">
+        <is>
+          <t>$1.77</t>
+        </is>
+      </c>
+      <c r="EP8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="EQ8" t="inlineStr">
+        <is>
+          <t>$1.77</t>
+        </is>
+      </c>
+      <c r="ER8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="ES8" t="inlineStr">
+        <is>
+          <t>$1.77</t>
+        </is>
+      </c>
+      <c r="ET8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="EU8" t="inlineStr">
+        <is>
+          <t>$1.77</t>
+        </is>
+      </c>
+      <c r="EV8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="EW8" t="inlineStr">
+        <is>
+          <t>$1.77</t>
+        </is>
+      </c>
+      <c r="EX8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="EY8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
+      <c r="EZ8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="FA8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
+      <c r="FB8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="FC8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4540,6 +7260,346 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="CN9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="CO9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="CP9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="CQ9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="CR9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="CS9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="CT9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="CU9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="CV9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="CW9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="CX9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="CY9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="CZ9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="DA9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="DB9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="DC9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="DD9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="DE9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="DF9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="DG9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="DH9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="DI9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="DJ9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="DK9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="DL9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="DM9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="DN9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="DO9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="DP9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="DQ9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="DR9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="DS9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="DT9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="DU9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="DV9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="DW9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="DX9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="DY9" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
+      <c r="DZ9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="EA9" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
+      <c r="EB9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="EC9" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
+      <c r="ED9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="EE9" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
+      <c r="EF9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="EG9" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
+      <c r="EH9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="EI9" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
+      <c r="EJ9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="EK9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="EL9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="EM9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="EN9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="EO9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="EP9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="EQ9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="ER9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="ES9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="ET9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="EU9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="EV9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="EW9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="EX9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="EY9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="EZ9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="FA9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="FB9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="FC9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4997,6 +8057,346 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="CN10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="CO10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="CP10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="CQ10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="CR10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="CS10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="CT10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="CU10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="CV10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="CW10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="CX10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="CY10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="CZ10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="DA10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="DB10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="DC10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="DD10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="DE10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="DF10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="DG10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="DH10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="DI10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="DJ10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="DK10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="DL10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="DM10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="DN10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="DO10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="DP10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="DQ10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="DR10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="DS10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="DT10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="DU10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="DV10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="DW10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="DX10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="DY10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="DZ10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="EA10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="EB10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="EC10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="ED10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="EE10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="EF10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="EG10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="EH10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="EI10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="EJ10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="EK10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="EL10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="EM10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="EN10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="EO10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="EP10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="EQ10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="ER10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="ES10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="ET10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="EU10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="EV10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="EW10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="EX10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="EY10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="EZ10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="FA10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="FB10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="FC10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5454,6 +8854,346 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="CN11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="CO11" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
+      <c r="CP11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="CQ11" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
+      <c r="CR11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="CS11" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
+      <c r="CT11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="CU11" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
+      <c r="CV11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="CW11" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
+      <c r="CX11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="CY11" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
+      <c r="CZ11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="DA11" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
+      <c r="DB11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="DC11" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
+      <c r="DD11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="DE11" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
+      <c r="DF11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="DG11" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
+      <c r="DH11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="DI11" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
+      <c r="DJ11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="DK11" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
+      <c r="DL11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="DM11" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
+      <c r="DN11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="DO11" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
+      <c r="DP11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="DQ11" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
+      <c r="DR11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="DS11" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
+      <c r="DT11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="DU11" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
+      <c r="DV11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="DW11" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
+      <c r="DX11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="DY11" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
+      <c r="DZ11" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="EA11" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="EB11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="EC11" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
+      <c r="ED11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="EE11" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
+      <c r="EF11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="EG11" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
+      <c r="EH11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="EI11" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
+      <c r="EJ11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="EK11" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
+      <c r="EL11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="EM11" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
+      <c r="EN11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="EO11" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
+      <c r="EP11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="EQ11" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
+      <c r="ER11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="ES11" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
+      <c r="ET11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="EU11" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
+      <c r="EV11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="EW11" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
+      <c r="EX11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="EY11" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
+      <c r="EZ11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="FA11" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
+      <c r="FB11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="FC11" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5911,6 +9651,346 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="CN12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="CO12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="CP12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="CQ12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="CR12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="CS12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="CT12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="CU12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="CV12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="CW12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="CX12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="CY12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="CZ12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="DA12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="DB12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="DC12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="DD12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="DE12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="DF12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="DG12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="DH12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="DI12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="DJ12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="DK12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="DL12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="DM12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="DN12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="DO12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="DP12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="DQ12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="DR12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="DS12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="DT12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="DU12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="DV12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="DW12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="DX12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="DY12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="DZ12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="EA12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="EB12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="EC12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="ED12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="EE12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="EF12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="EG12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="EH12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="EI12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="EJ12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="EK12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="EL12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="EM12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="EN12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="EO12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="EP12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="EQ12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="ER12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="ES12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="ET12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="EU12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="EV12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="EW12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="EX12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="EY12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="EZ12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="FA12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="FB12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="FC12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6368,6 +10448,346 @@
           <t>16¢ ea.</t>
         </is>
       </c>
+      <c r="CN13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="CO13" t="inlineStr">
+        <is>
+          <t>16¢ ea.</t>
+        </is>
+      </c>
+      <c r="CP13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="CQ13" t="inlineStr">
+        <is>
+          <t>16¢ ea.</t>
+        </is>
+      </c>
+      <c r="CR13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="CS13" t="inlineStr">
+        <is>
+          <t>16¢ ea.</t>
+        </is>
+      </c>
+      <c r="CT13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="CU13" t="inlineStr">
+        <is>
+          <t>16¢ ea.</t>
+        </is>
+      </c>
+      <c r="CV13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="CW13" t="inlineStr">
+        <is>
+          <t>16¢ ea.</t>
+        </is>
+      </c>
+      <c r="CX13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="CY13" t="inlineStr">
+        <is>
+          <t>16¢ ea.</t>
+        </is>
+      </c>
+      <c r="CZ13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="DA13" t="inlineStr">
+        <is>
+          <t>16¢ ea.</t>
+        </is>
+      </c>
+      <c r="DB13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="DC13" t="inlineStr">
+        <is>
+          <t>16¢ ea.</t>
+        </is>
+      </c>
+      <c r="DD13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="DE13" t="inlineStr">
+        <is>
+          <t>16¢ ea.</t>
+        </is>
+      </c>
+      <c r="DF13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="DG13" t="inlineStr">
+        <is>
+          <t>16¢ ea.</t>
+        </is>
+      </c>
+      <c r="DH13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="DI13" t="inlineStr">
+        <is>
+          <t>16¢ ea.</t>
+        </is>
+      </c>
+      <c r="DJ13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="DK13" t="inlineStr">
+        <is>
+          <t>16¢ ea.</t>
+        </is>
+      </c>
+      <c r="DL13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="DM13" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="DN13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="DO13" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="DP13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="DQ13" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="DR13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="DS13" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="DT13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="DU13" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="DV13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="DW13" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="DX13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="DY13" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="DZ13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="EA13" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="EB13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="EC13" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="ED13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="EE13" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="EF13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="EG13" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="EH13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="EI13" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="EJ13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="EK13" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="EL13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="EM13" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="EN13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="EO13" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="EP13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="EQ13" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="ER13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="ES13" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="ET13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="EU13" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="EV13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="EW13" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="EX13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="EY13" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="EZ13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="FA13" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="FB13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="FC13" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6825,6 +11245,346 @@
           <t>$5.89</t>
         </is>
       </c>
+      <c r="CN14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="CO14" t="inlineStr">
+        <is>
+          <t>$5.89</t>
+        </is>
+      </c>
+      <c r="CP14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="CQ14" t="inlineStr">
+        <is>
+          <t>$5.89</t>
+        </is>
+      </c>
+      <c r="CR14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="CS14" t="inlineStr">
+        <is>
+          <t>$5.89</t>
+        </is>
+      </c>
+      <c r="CT14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="CU14" t="inlineStr">
+        <is>
+          <t>$5.89</t>
+        </is>
+      </c>
+      <c r="CV14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="CW14" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
+      <c r="CX14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="CY14" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
+      <c r="CZ14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="DA14" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
+      <c r="DB14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="DC14" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
+      <c r="DD14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="DE14" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
+      <c r="DF14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="DG14" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
+      <c r="DH14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="DI14" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
+      <c r="DJ14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="DK14" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
+      <c r="DL14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="DM14" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
+      <c r="DN14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="DO14" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
+      <c r="DP14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="DQ14" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
+      <c r="DR14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="DS14" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
+      <c r="DT14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="DU14" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
+      <c r="DV14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="DW14" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
+      <c r="DX14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="DY14" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
+      <c r="DZ14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="EA14" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
+      <c r="EB14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="EC14" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
+      <c r="ED14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="EE14" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
+      <c r="EF14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="EG14" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
+      <c r="EH14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="EI14" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
+      <c r="EJ14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="EK14" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
+      <c r="EL14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="EM14" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
+      <c r="EN14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="EO14" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
+      <c r="EP14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="EQ14" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
+      <c r="ER14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="ES14" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
+      <c r="ET14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="EU14" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
+      <c r="EV14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="EW14" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
+      <c r="EX14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="EY14" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
+      <c r="EZ14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="FA14" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
+      <c r="FB14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="FC14" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7282,6 +12042,346 @@
           <t>$6.99/lb</t>
         </is>
       </c>
+      <c r="CN15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="CO15" t="inlineStr">
+        <is>
+          <t>$6.99/lb</t>
+        </is>
+      </c>
+      <c r="CP15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="CQ15" t="inlineStr">
+        <is>
+          <t>$6.99/lb</t>
+        </is>
+      </c>
+      <c r="CR15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="CS15" t="inlineStr">
+        <is>
+          <t>$6.99/lb</t>
+        </is>
+      </c>
+      <c r="CT15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="CU15" t="inlineStr">
+        <is>
+          <t>$4.99/lb</t>
+        </is>
+      </c>
+      <c r="CV15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="CW15" t="inlineStr">
+        <is>
+          <t>$4.99/lb</t>
+        </is>
+      </c>
+      <c r="CX15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="CY15" t="inlineStr">
+        <is>
+          <t>$4.99/lb</t>
+        </is>
+      </c>
+      <c r="CZ15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="DA15" t="inlineStr">
+        <is>
+          <t>$4.99/lb</t>
+        </is>
+      </c>
+      <c r="DB15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="DC15" t="inlineStr">
+        <is>
+          <t>$4.99/lb</t>
+        </is>
+      </c>
+      <c r="DD15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="DE15" t="inlineStr">
+        <is>
+          <t>$6.99/lb</t>
+        </is>
+      </c>
+      <c r="DF15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="DG15" t="inlineStr">
+        <is>
+          <t>$6.99/lb</t>
+        </is>
+      </c>
+      <c r="DH15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="DI15" t="inlineStr">
+        <is>
+          <t>$6.99/lb</t>
+        </is>
+      </c>
+      <c r="DJ15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="DK15" t="inlineStr">
+        <is>
+          <t>$6.99/lb</t>
+        </is>
+      </c>
+      <c r="DL15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="DM15" t="inlineStr">
+        <is>
+          <t>$6.99/lb</t>
+        </is>
+      </c>
+      <c r="DN15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="DO15" t="inlineStr">
+        <is>
+          <t>$6.99/lb</t>
+        </is>
+      </c>
+      <c r="DP15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="DQ15" t="inlineStr">
+        <is>
+          <t>$6.99/lb</t>
+        </is>
+      </c>
+      <c r="DR15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="DS15" t="inlineStr">
+        <is>
+          <t>$6.99/lb</t>
+        </is>
+      </c>
+      <c r="DT15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="DU15" t="inlineStr">
+        <is>
+          <t>$6.99/lb</t>
+        </is>
+      </c>
+      <c r="DV15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="DW15" t="inlineStr">
+        <is>
+          <t>$6.99/lb</t>
+        </is>
+      </c>
+      <c r="DX15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="DY15" t="inlineStr">
+        <is>
+          <t>$6.99/lb</t>
+        </is>
+      </c>
+      <c r="DZ15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="EA15" t="inlineStr">
+        <is>
+          <t>$6.99/lb</t>
+        </is>
+      </c>
+      <c r="EB15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="EC15" t="inlineStr">
+        <is>
+          <t>$6.99/lb</t>
+        </is>
+      </c>
+      <c r="ED15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="EE15" t="inlineStr">
+        <is>
+          <t>$6.99/lb</t>
+        </is>
+      </c>
+      <c r="EF15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="EG15" t="inlineStr">
+        <is>
+          <t>$6.99/lb</t>
+        </is>
+      </c>
+      <c r="EH15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="EI15" t="inlineStr">
+        <is>
+          <t>$6.99/lb</t>
+        </is>
+      </c>
+      <c r="EJ15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="EK15" t="inlineStr">
+        <is>
+          <t>$6.99/lb</t>
+        </is>
+      </c>
+      <c r="EL15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="EM15" t="inlineStr">
+        <is>
+          <t>$7.49/lb</t>
+        </is>
+      </c>
+      <c r="EN15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="EO15" t="inlineStr">
+        <is>
+          <t>$7.49/lb</t>
+        </is>
+      </c>
+      <c r="EP15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="EQ15" t="inlineStr">
+        <is>
+          <t>$7.49/lb</t>
+        </is>
+      </c>
+      <c r="ER15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="ES15" t="inlineStr">
+        <is>
+          <t>$7.49/lb</t>
+        </is>
+      </c>
+      <c r="ET15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="EU15" t="inlineStr">
+        <is>
+          <t>$7.49/lb</t>
+        </is>
+      </c>
+      <c r="EV15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="EW15" t="inlineStr">
+        <is>
+          <t>$7.49/lb</t>
+        </is>
+      </c>
+      <c r="EX15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="EY15" t="inlineStr">
+        <is>
+          <t>$7.49/lb</t>
+        </is>
+      </c>
+      <c r="EZ15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="FA15" t="inlineStr">
+        <is>
+          <t>$7.49/lb</t>
+        </is>
+      </c>
+      <c r="FB15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="FC15" t="inlineStr">
+        <is>
+          <t>$7.49/lb</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -7739,6 +12839,346 @@
           <t>$3.83 ea.</t>
         </is>
       </c>
+      <c r="CN16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="CO16" t="inlineStr">
+        <is>
+          <t>$3.83 ea.</t>
+        </is>
+      </c>
+      <c r="CP16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="CQ16" t="inlineStr">
+        <is>
+          <t>$3.83 ea.</t>
+        </is>
+      </c>
+      <c r="CR16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="CS16" t="inlineStr">
+        <is>
+          <t>$3.83 ea.</t>
+        </is>
+      </c>
+      <c r="CT16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="CU16" t="inlineStr">
+        <is>
+          <t>$3.83 ea.</t>
+        </is>
+      </c>
+      <c r="CV16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="CW16" t="inlineStr">
+        <is>
+          <t>$4.39 ea.</t>
+        </is>
+      </c>
+      <c r="CX16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="CY16" t="inlineStr">
+        <is>
+          <t>$4.39 ea.</t>
+        </is>
+      </c>
+      <c r="CZ16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="DA16" t="inlineStr">
+        <is>
+          <t>$4.39 ea.</t>
+        </is>
+      </c>
+      <c r="DB16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="DC16" t="inlineStr">
+        <is>
+          <t>$4.39 ea.</t>
+        </is>
+      </c>
+      <c r="DD16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="DE16" t="inlineStr">
+        <is>
+          <t>$4.39 ea.</t>
+        </is>
+      </c>
+      <c r="DF16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="DG16" t="inlineStr">
+        <is>
+          <t>$4.39 ea.</t>
+        </is>
+      </c>
+      <c r="DH16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="DI16" t="inlineStr">
+        <is>
+          <t>$4.39 ea.</t>
+        </is>
+      </c>
+      <c r="DJ16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="DK16" t="inlineStr">
+        <is>
+          <t>$4.39 ea.</t>
+        </is>
+      </c>
+      <c r="DL16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="DM16" t="inlineStr">
+        <is>
+          <t>$4.39 ea.</t>
+        </is>
+      </c>
+      <c r="DN16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="DO16" t="inlineStr">
+        <is>
+          <t>$4.39 ea.</t>
+        </is>
+      </c>
+      <c r="DP16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="DQ16" t="inlineStr">
+        <is>
+          <t>$4.39 ea.</t>
+        </is>
+      </c>
+      <c r="DR16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="DS16" t="inlineStr">
+        <is>
+          <t>$4.39 ea.</t>
+        </is>
+      </c>
+      <c r="DT16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="DU16" t="inlineStr">
+        <is>
+          <t>$4.39 ea.</t>
+        </is>
+      </c>
+      <c r="DV16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="DW16" t="inlineStr">
+        <is>
+          <t>$4.39 ea.</t>
+        </is>
+      </c>
+      <c r="DX16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="DY16" t="inlineStr">
+        <is>
+          <t>$4.39 ea.</t>
+        </is>
+      </c>
+      <c r="DZ16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="EA16" t="inlineStr">
+        <is>
+          <t>$4.39 ea.</t>
+        </is>
+      </c>
+      <c r="EB16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="EC16" t="inlineStr">
+        <is>
+          <t>$4.39 ea.</t>
+        </is>
+      </c>
+      <c r="ED16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="EE16" t="inlineStr">
+        <is>
+          <t>$4.39 ea.</t>
+        </is>
+      </c>
+      <c r="EF16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="EG16" t="inlineStr">
+        <is>
+          <t>$2.39 ea.</t>
+        </is>
+      </c>
+      <c r="EH16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="EI16" t="inlineStr">
+        <is>
+          <t>$2.39 ea.</t>
+        </is>
+      </c>
+      <c r="EJ16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="EK16" t="inlineStr">
+        <is>
+          <t>$4.12 ea.</t>
+        </is>
+      </c>
+      <c r="EL16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="EM16" t="inlineStr">
+        <is>
+          <t>$4.34 ea.</t>
+        </is>
+      </c>
+      <c r="EN16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="EO16" t="inlineStr">
+        <is>
+          <t>$4.34 ea.</t>
+        </is>
+      </c>
+      <c r="EP16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="EQ16" t="inlineStr">
+        <is>
+          <t>$4.34 ea.</t>
+        </is>
+      </c>
+      <c r="ER16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="ES16" t="inlineStr">
+        <is>
+          <t>$4.34 ea.</t>
+        </is>
+      </c>
+      <c r="ET16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="EU16" t="inlineStr">
+        <is>
+          <t>$4.34 ea.</t>
+        </is>
+      </c>
+      <c r="EV16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="EW16" t="inlineStr">
+        <is>
+          <t>$4.34 ea.</t>
+        </is>
+      </c>
+      <c r="EX16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="EY16" t="inlineStr">
+        <is>
+          <t>$4.34 ea.</t>
+        </is>
+      </c>
+      <c r="EZ16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="FA16" t="inlineStr">
+        <is>
+          <t>$4.34 ea.</t>
+        </is>
+      </c>
+      <c r="FB16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="FC16" t="inlineStr">
+        <is>
+          <t>$4.34 ea.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8196,6 +13636,346 @@
           <t>$40,275</t>
         </is>
       </c>
+      <c r="CN17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="CO17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="CP17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="CQ17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="CR17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="CS17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="CT17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="CU17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="CV17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="CW17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="CX17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="CY17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="CZ17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="DA17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="DB17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="DC17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="DD17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="DE17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="DF17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="DG17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="DH17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="DI17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="DJ17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="DK17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="DL17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="DM17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="DN17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="DO17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="DP17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="DQ17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="DR17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="DS17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="DT17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="DU17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="DV17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="DW17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="DX17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="DY17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="DZ17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="EA17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="EB17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="EC17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="ED17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="EE17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="EF17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="EG17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="EH17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="EI17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="EJ17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="EK17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="EL17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="EM17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="EN17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="EO17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="EP17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="EQ17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="ER17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="ES17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="ET17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="EU17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="EV17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="EW17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="EX17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="EY17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="EZ17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="FA17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="FB17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="FC17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -8469,6 +14249,346 @@
       </c>
       <c r="CL18" t="inlineStr"/>
       <c r="CM18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="CN18" t="inlineStr">
+        <is>
+          <t>Silverado</t>
+        </is>
+      </c>
+      <c r="CO18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="CP18" t="inlineStr">
+        <is>
+          <t>Silverado</t>
+        </is>
+      </c>
+      <c r="CQ18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="CR18" t="inlineStr">
+        <is>
+          <t>Silverado</t>
+        </is>
+      </c>
+      <c r="CS18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="CT18" t="inlineStr">
+        <is>
+          <t>Silverado</t>
+        </is>
+      </c>
+      <c r="CU18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="CV18" t="inlineStr">
+        <is>
+          <t>Silverado</t>
+        </is>
+      </c>
+      <c r="CW18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="CX18" t="inlineStr">
+        <is>
+          <t>Silverado</t>
+        </is>
+      </c>
+      <c r="CY18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="CZ18" t="inlineStr">
+        <is>
+          <t>Silverado</t>
+        </is>
+      </c>
+      <c r="DA18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="DB18" t="inlineStr">
+        <is>
+          <t>Silverado</t>
+        </is>
+      </c>
+      <c r="DC18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="DD18" t="inlineStr">
+        <is>
+          <t>Silverado</t>
+        </is>
+      </c>
+      <c r="DE18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="DF18" t="inlineStr">
+        <is>
+          <t>Silverado</t>
+        </is>
+      </c>
+      <c r="DG18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="DH18" t="inlineStr">
+        <is>
+          <t>Silverado</t>
+        </is>
+      </c>
+      <c r="DI18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="DJ18" t="inlineStr">
+        <is>
+          <t>Silverado</t>
+        </is>
+      </c>
+      <c r="DK18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="DL18" t="inlineStr">
+        <is>
+          <t>Silverado</t>
+        </is>
+      </c>
+      <c r="DM18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="DN18" t="inlineStr">
+        <is>
+          <t>Silverado</t>
+        </is>
+      </c>
+      <c r="DO18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="DP18" t="inlineStr">
+        <is>
+          <t>Silverado</t>
+        </is>
+      </c>
+      <c r="DQ18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="DR18" t="inlineStr">
+        <is>
+          <t>Silverado</t>
+        </is>
+      </c>
+      <c r="DS18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="DT18" t="inlineStr">
+        <is>
+          <t>Silverado</t>
+        </is>
+      </c>
+      <c r="DU18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="DV18" t="inlineStr">
+        <is>
+          <t>Silverado</t>
+        </is>
+      </c>
+      <c r="DW18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="DX18" t="inlineStr">
+        <is>
+          <t>Silverado</t>
+        </is>
+      </c>
+      <c r="DY18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="DZ18" t="inlineStr">
+        <is>
+          <t>Silverado</t>
+        </is>
+      </c>
+      <c r="EA18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="EB18" t="inlineStr">
+        <is>
+          <t>Silverado</t>
+        </is>
+      </c>
+      <c r="EC18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="ED18" t="inlineStr">
+        <is>
+          <t>Silverado</t>
+        </is>
+      </c>
+      <c r="EE18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="EF18" t="inlineStr">
+        <is>
+          <t>Silverado</t>
+        </is>
+      </c>
+      <c r="EG18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="EH18" t="inlineStr">
+        <is>
+          <t>Silverado</t>
+        </is>
+      </c>
+      <c r="EI18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="EJ18" t="inlineStr">
+        <is>
+          <t>Silverado</t>
+        </is>
+      </c>
+      <c r="EK18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="EL18" t="inlineStr">
+        <is>
+          <t>Silverado</t>
+        </is>
+      </c>
+      <c r="EM18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="EN18" t="inlineStr">
+        <is>
+          <t>Silverado</t>
+        </is>
+      </c>
+      <c r="EO18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="EP18" t="inlineStr">
+        <is>
+          <t>Silverado</t>
+        </is>
+      </c>
+      <c r="EQ18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="ER18" t="inlineStr">
+        <is>
+          <t>Silverado</t>
+        </is>
+      </c>
+      <c r="ES18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="ET18" t="inlineStr">
+        <is>
+          <t>Silverado</t>
+        </is>
+      </c>
+      <c r="EU18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="EV18" t="inlineStr">
+        <is>
+          <t>Silverado</t>
+        </is>
+      </c>
+      <c r="EW18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="EX18" t="inlineStr">
+        <is>
+          <t>Silverado</t>
+        </is>
+      </c>
+      <c r="EY18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="EZ18" t="inlineStr">
+        <is>
+          <t>Silverado</t>
+        </is>
+      </c>
+      <c r="FA18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="FB18" t="inlineStr">
+        <is>
+          <t>Silverado</t>
+        </is>
+      </c>
+      <c r="FC18" t="inlineStr">
         <is>
           <t>$37,000*</t>
         </is>
@@ -8778,6 +14898,346 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="CN19" t="inlineStr">
+        <is>
+          <t>2 x 4 x 8' Construction/Framing Lumber</t>
+        </is>
+      </c>
+      <c r="CO19" t="inlineStr">
+        <is>
+          <t>$3.85</t>
+        </is>
+      </c>
+      <c r="CP19" t="inlineStr">
+        <is>
+          <t>2 x 4 x 8' Construction/Framing Lumber</t>
+        </is>
+      </c>
+      <c r="CQ19" t="inlineStr">
+        <is>
+          <t>$3.85</t>
+        </is>
+      </c>
+      <c r="CR19" t="inlineStr">
+        <is>
+          <t>2 x 4 x 8' Construction/Framing Lumber</t>
+        </is>
+      </c>
+      <c r="CS19" t="inlineStr">
+        <is>
+          <t>$3.85</t>
+        </is>
+      </c>
+      <c r="CT19" t="inlineStr">
+        <is>
+          <t>2 x 4 x 8' Construction/Framing Lumber</t>
+        </is>
+      </c>
+      <c r="CU19" t="inlineStr">
+        <is>
+          <t>$3.85</t>
+        </is>
+      </c>
+      <c r="CV19" t="inlineStr">
+        <is>
+          <t>2 x 4 x 8' Construction/Framing Lumber</t>
+        </is>
+      </c>
+      <c r="CW19" t="inlineStr">
+        <is>
+          <t>$3.85</t>
+        </is>
+      </c>
+      <c r="CX19" t="inlineStr">
+        <is>
+          <t>2 x 4 x 8' Construction/Framing Lumber</t>
+        </is>
+      </c>
+      <c r="CY19" t="inlineStr">
+        <is>
+          <t>$3.85</t>
+        </is>
+      </c>
+      <c r="CZ19" t="inlineStr">
+        <is>
+          <t>2 x 4 x 8' Construction/Framing Lumber</t>
+        </is>
+      </c>
+      <c r="DA19" t="inlineStr">
+        <is>
+          <t>$3.85</t>
+        </is>
+      </c>
+      <c r="DB19" t="inlineStr">
+        <is>
+          <t>2 x 4 x 8' Construction/Framing Lumber</t>
+        </is>
+      </c>
+      <c r="DC19" t="inlineStr">
+        <is>
+          <t>$3.85</t>
+        </is>
+      </c>
+      <c r="DD19" t="inlineStr">
+        <is>
+          <t>2 x 4 x 8' Construction/Framing Lumber</t>
+        </is>
+      </c>
+      <c r="DE19" t="inlineStr">
+        <is>
+          <t>$3.85</t>
+        </is>
+      </c>
+      <c r="DF19" t="inlineStr">
+        <is>
+          <t>2 x 4 x 8' Construction/Framing Lumber</t>
+        </is>
+      </c>
+      <c r="DG19" t="inlineStr">
+        <is>
+          <t>$3.85</t>
+        </is>
+      </c>
+      <c r="DH19" t="inlineStr">
+        <is>
+          <t>2 x 4 x 8' Construction/Framing Lumber</t>
+        </is>
+      </c>
+      <c r="DI19" t="inlineStr">
+        <is>
+          <t>$3.85</t>
+        </is>
+      </c>
+      <c r="DJ19" t="inlineStr">
+        <is>
+          <t>2 x 4 x 8' Construction/Framing Lumber</t>
+        </is>
+      </c>
+      <c r="DK19" t="inlineStr">
+        <is>
+          <t>$3.85</t>
+        </is>
+      </c>
+      <c r="DL19" t="inlineStr">
+        <is>
+          <t>2 x 4 x 8' Construction/Framing Lumber</t>
+        </is>
+      </c>
+      <c r="DM19" t="inlineStr">
+        <is>
+          <t>$3.85</t>
+        </is>
+      </c>
+      <c r="DN19" t="inlineStr">
+        <is>
+          <t>2 x 4 x 8' Construction/Framing Lumber</t>
+        </is>
+      </c>
+      <c r="DO19" t="inlineStr">
+        <is>
+          <t>$3.85</t>
+        </is>
+      </c>
+      <c r="DP19" t="inlineStr">
+        <is>
+          <t>2 x 4 x 8' Construction/Framing Lumber</t>
+        </is>
+      </c>
+      <c r="DQ19" t="inlineStr">
+        <is>
+          <t>$3.85</t>
+        </is>
+      </c>
+      <c r="DR19" t="inlineStr">
+        <is>
+          <t>2 x 4 x 8' Construction/Framing Lumber</t>
+        </is>
+      </c>
+      <c r="DS19" t="inlineStr">
+        <is>
+          <t>$3.85</t>
+        </is>
+      </c>
+      <c r="DT19" t="inlineStr">
+        <is>
+          <t>2 x 4 x 8' Construction/Framing Lumber</t>
+        </is>
+      </c>
+      <c r="DU19" t="inlineStr">
+        <is>
+          <t>$3.85</t>
+        </is>
+      </c>
+      <c r="DV19" t="inlineStr">
+        <is>
+          <t>2 x 4 x 8' Construction/Framing Lumber</t>
+        </is>
+      </c>
+      <c r="DW19" t="inlineStr">
+        <is>
+          <t>$3.85</t>
+        </is>
+      </c>
+      <c r="DX19" t="inlineStr">
+        <is>
+          <t>2 x 4 x 8' Construction/Framing Lumber</t>
+        </is>
+      </c>
+      <c r="DY19" t="inlineStr">
+        <is>
+          <t>$3.85</t>
+        </is>
+      </c>
+      <c r="DZ19" t="inlineStr">
+        <is>
+          <t>2 x 4 x 8' Construction/Framing Lumber</t>
+        </is>
+      </c>
+      <c r="EA19" t="inlineStr">
+        <is>
+          <t>$3.85</t>
+        </is>
+      </c>
+      <c r="EB19" t="inlineStr">
+        <is>
+          <t>2 x 4 x 8' Construction/Framing Lumber</t>
+        </is>
+      </c>
+      <c r="EC19" t="inlineStr">
+        <is>
+          <t>$3.85</t>
+        </is>
+      </c>
+      <c r="ED19" t="inlineStr">
+        <is>
+          <t>2 x 4 x 8' Construction/Framing Lumber</t>
+        </is>
+      </c>
+      <c r="EE19" t="inlineStr">
+        <is>
+          <t>$3.85</t>
+        </is>
+      </c>
+      <c r="EF19" t="inlineStr">
+        <is>
+          <t>2 x 4 x 8' Construction/Framing Lumber</t>
+        </is>
+      </c>
+      <c r="EG19" t="inlineStr">
+        <is>
+          <t>$3.85</t>
+        </is>
+      </c>
+      <c r="EH19" t="inlineStr">
+        <is>
+          <t>2 x 4 x 8' Construction/Framing Lumber</t>
+        </is>
+      </c>
+      <c r="EI19" t="inlineStr">
+        <is>
+          <t>$3.85</t>
+        </is>
+      </c>
+      <c r="EJ19" t="inlineStr">
+        <is>
+          <t>2 x 4 x 8' Construction/Framing Lumber</t>
+        </is>
+      </c>
+      <c r="EK19" t="inlineStr">
+        <is>
+          <t>$3.85</t>
+        </is>
+      </c>
+      <c r="EL19" t="inlineStr">
+        <is>
+          <t>2 x 4 x 8' Construction/Framing Lumber</t>
+        </is>
+      </c>
+      <c r="EM19" t="inlineStr">
+        <is>
+          <t>$3.85</t>
+        </is>
+      </c>
+      <c r="EN19" t="inlineStr">
+        <is>
+          <t>2 x 4 x 8' Construction/Framing Lumber</t>
+        </is>
+      </c>
+      <c r="EO19" t="inlineStr">
+        <is>
+          <t>$3.85</t>
+        </is>
+      </c>
+      <c r="EP19" t="inlineStr">
+        <is>
+          <t>2 x 4 x 8' Construction/Framing Lumber</t>
+        </is>
+      </c>
+      <c r="EQ19" t="inlineStr">
+        <is>
+          <t>$3.85</t>
+        </is>
+      </c>
+      <c r="ER19" t="inlineStr">
+        <is>
+          <t>2 x 4 x 8' Construction/Framing Lumber</t>
+        </is>
+      </c>
+      <c r="ES19" t="inlineStr">
+        <is>
+          <t>$3.85</t>
+        </is>
+      </c>
+      <c r="ET19" t="inlineStr">
+        <is>
+          <t>2 x 4 x 8' Construction/Framing Lumber</t>
+        </is>
+      </c>
+      <c r="EU19" t="inlineStr">
+        <is>
+          <t>$3.85</t>
+        </is>
+      </c>
+      <c r="EV19" t="inlineStr">
+        <is>
+          <t>2 x 4 x 8' Construction/Framing Lumber</t>
+        </is>
+      </c>
+      <c r="EW19" t="inlineStr">
+        <is>
+          <t>$3.85</t>
+        </is>
+      </c>
+      <c r="EX19" t="inlineStr">
+        <is>
+          <t>2 x 4 x 8' Construction/Framing Lumber</t>
+        </is>
+      </c>
+      <c r="EY19" t="inlineStr">
+        <is>
+          <t>$3.85</t>
+        </is>
+      </c>
+      <c r="EZ19" t="inlineStr">
+        <is>
+          <t>2 x 4 x 8' Construction/Framing Lumber</t>
+        </is>
+      </c>
+      <c r="FA19" t="inlineStr">
+        <is>
+          <t>$3.94</t>
+        </is>
+      </c>
+      <c r="FB19" t="inlineStr">
+        <is>
+          <t>2 x 4 x 8' Construction/Framing Lumber</t>
+        </is>
+      </c>
+      <c r="FC19" t="inlineStr">
+        <is>
+          <t>$3.94</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -9235,6 +15695,346 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="CN20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="CO20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="CP20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="CQ20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="CR20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="CS20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="CT20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="CU20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="CV20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="CW20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="CX20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="CY20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="CZ20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="DA20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="DB20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="DC20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="DD20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="DE20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="DF20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="DG20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="DH20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="DI20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="DJ20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="DK20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="DL20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="DM20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="DN20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="DO20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="DP20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="DQ20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="DR20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="DS20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="DT20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="DU20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="DV20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="DW20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="DX20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="DY20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="DZ20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="EA20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="EB20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="EC20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="ED20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="EE20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="EF20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="EG20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="EH20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="EI20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="EJ20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="EK20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="EL20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="EM20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="EN20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="EO20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="EP20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="EQ20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="ER20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="ES20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="ET20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="EU20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="EV20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="EW20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="EX20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="EY20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="EZ20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="FA20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="FB20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="FC20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -9692,6 +16492,346 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="CN21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="CO21" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="CP21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="CQ21" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="CR21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="CS21" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="CT21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="CU21" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="CV21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="CW21" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="CX21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="CY21" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="CZ21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="DA21" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="DB21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="DC21" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="DD21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="DE21" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="DF21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="DG21" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="DH21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="DI21" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="DJ21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="DK21" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="DL21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="DM21" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="DN21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="DO21" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="DP21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="DQ21" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="DR21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="DS21" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="DT21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="DU21" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="DV21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="DW21" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="DX21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="DY21" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="DZ21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="EA21" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="EB21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="EC21" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="ED21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="EE21" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="EF21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="EG21" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="EH21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="EI21" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="EJ21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="EK21" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="EL21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="EM21" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="EN21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="EO21" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="EP21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="EQ21" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="ER21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="ES21" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="ET21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="EU21" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="EV21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="EW21" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="EX21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="EY21" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="EZ21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="FA21" t="inlineStr">
+        <is>
+          <t>$4.47</t>
+        </is>
+      </c>
+      <c r="FB21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="FC21" t="inlineStr">
+        <is>
+          <t>$4.47</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -10149,6 +17289,234 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="CN22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="CO22" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="CP22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="CQ22" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="CR22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="CS22" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="CT22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="CU22" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="CV22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="CW22" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="CX22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="CY22" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="CZ22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="DA22" t="inlineStr"/>
+      <c r="DB22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="DC22" t="inlineStr"/>
+      <c r="DD22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="DE22" t="inlineStr"/>
+      <c r="DF22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="DG22" t="inlineStr"/>
+      <c r="DH22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="DI22" t="inlineStr"/>
+      <c r="DJ22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="DK22" t="inlineStr"/>
+      <c r="DL22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="DM22" t="inlineStr"/>
+      <c r="DN22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="DO22" t="inlineStr"/>
+      <c r="DP22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="DQ22" t="inlineStr"/>
+      <c r="DR22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="DS22" t="inlineStr"/>
+      <c r="DT22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="DU22" t="inlineStr"/>
+      <c r="DV22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="DW22" t="inlineStr"/>
+      <c r="DX22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="DY22" t="inlineStr"/>
+      <c r="DZ22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="EA22" t="inlineStr"/>
+      <c r="EB22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="EC22" t="inlineStr"/>
+      <c r="ED22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="EE22" t="inlineStr"/>
+      <c r="EF22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="EG22" t="inlineStr"/>
+      <c r="EH22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="EI22" t="inlineStr"/>
+      <c r="EJ22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="EK22" t="inlineStr"/>
+      <c r="EL22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="EM22" t="inlineStr"/>
+      <c r="EN22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="EO22" t="inlineStr"/>
+      <c r="EP22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="EQ22" t="inlineStr"/>
+      <c r="ER22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="ES22" t="inlineStr"/>
+      <c r="ET22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="EU22" t="inlineStr"/>
+      <c r="EV22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="EW22" t="inlineStr"/>
+      <c r="EX22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="EY22" t="inlineStr"/>
+      <c r="EZ22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="FA22" t="inlineStr"/>
+      <c r="FB22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="FC22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -10606,6 +17974,234 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="CN23" t="inlineStr">
+        <is>
+          <t>7.4 cu. ft. Vented Smart Electric Dryer with Steam Sanitize Plus in White</t>
+        </is>
+      </c>
+      <c r="CO23" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="CP23" t="inlineStr">
+        <is>
+          <t>7.4 cu. ft. Vented Smart Electric Dryer with Steam Sanitize Plus in White</t>
+        </is>
+      </c>
+      <c r="CQ23" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="CR23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="CS23" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="CT23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="CU23" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="CV23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="CW23" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="CX23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="CY23" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="CZ23" t="inlineStr">
+        <is>
+          <t>7.4 cu. ft. Vented Smart Electric Dryer with Steam Sanitize Plus in White</t>
+        </is>
+      </c>
+      <c r="DA23" t="inlineStr"/>
+      <c r="DB23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="DC23" t="inlineStr"/>
+      <c r="DD23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="DE23" t="inlineStr"/>
+      <c r="DF23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="DG23" t="inlineStr"/>
+      <c r="DH23" t="inlineStr">
+        <is>
+          <t>7.4 cu. ft. Vented Smart Electric Dryer with Steam Sanitize Plus in White</t>
+        </is>
+      </c>
+      <c r="DI23" t="inlineStr"/>
+      <c r="DJ23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="DK23" t="inlineStr"/>
+      <c r="DL23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="DM23" t="inlineStr"/>
+      <c r="DN23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="DO23" t="inlineStr"/>
+      <c r="DP23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="DQ23" t="inlineStr"/>
+      <c r="DR23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="DS23" t="inlineStr"/>
+      <c r="DT23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="DU23" t="inlineStr"/>
+      <c r="DV23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="DW23" t="inlineStr"/>
+      <c r="DX23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="DY23" t="inlineStr"/>
+      <c r="DZ23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="EA23" t="inlineStr"/>
+      <c r="EB23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="EC23" t="inlineStr"/>
+      <c r="ED23" t="inlineStr">
+        <is>
+          <t>7.4 cu. ft. Vented Smart Electric Dryer with Steam Sanitize Plus in White</t>
+        </is>
+      </c>
+      <c r="EE23" t="inlineStr"/>
+      <c r="EF23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="EG23" t="inlineStr"/>
+      <c r="EH23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="EI23" t="inlineStr"/>
+      <c r="EJ23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="EK23" t="inlineStr"/>
+      <c r="EL23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="EM23" t="inlineStr"/>
+      <c r="EN23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="EO23" t="inlineStr"/>
+      <c r="EP23" t="inlineStr">
+        <is>
+          <t>7.4 cu. ft. Vented Smart Electric Dryer with Steam Sanitize Plus in White</t>
+        </is>
+      </c>
+      <c r="EQ23" t="inlineStr"/>
+      <c r="ER23" t="inlineStr">
+        <is>
+          <t>7.4 cu. ft. Vented Smart Electric Dryer with Steam Sanitize Plus in White</t>
+        </is>
+      </c>
+      <c r="ES23" t="inlineStr"/>
+      <c r="ET23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="EU23" t="inlineStr"/>
+      <c r="EV23" t="inlineStr">
+        <is>
+          <t>7.4 cu. ft. Vented Smart Electric Dryer with Steam Sanitize Plus in White</t>
+        </is>
+      </c>
+      <c r="EW23" t="inlineStr"/>
+      <c r="EX23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="EY23" t="inlineStr"/>
+      <c r="EZ23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="FA23" t="inlineStr"/>
+      <c r="FB23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="FC23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FC23"/>
+  <dimension ref="A1:FG23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1224,6 +1224,26 @@
           <t>Price_2025-04-23 03:05</t>
         </is>
       </c>
+      <c r="FD1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-04-24 03:04</t>
+        </is>
+      </c>
+      <c r="FE1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-04-24 03:04</t>
+        </is>
+      </c>
+      <c r="FF1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-04-25 03:05</t>
+        </is>
+      </c>
+      <c r="FG1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-04-25 03:05</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2021,6 +2041,26 @@
           <t>2.999</t>
         </is>
       </c>
+      <c r="FD2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="FE2" t="inlineStr">
+        <is>
+          <t>2.999</t>
+        </is>
+      </c>
+      <c r="FF2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="FG2" t="inlineStr">
+        <is>
+          <t>2.999</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2818,6 +2858,26 @@
           <t>$2.87</t>
         </is>
       </c>
+      <c r="FD3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="FE3" t="inlineStr">
+        <is>
+          <t>$2.87</t>
+        </is>
+      </c>
+      <c r="FF3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="FG3" t="inlineStr">
+        <is>
+          <t>$2.87</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3615,6 +3675,26 @@
           <t>32¢ ea.</t>
         </is>
       </c>
+      <c r="FD4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="FE4" t="inlineStr">
+        <is>
+          <t>32¢ ea.</t>
+        </is>
+      </c>
+      <c r="FF4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="FG4" t="inlineStr">
+        <is>
+          <t>32¢ ea.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4412,6 +4492,26 @@
           <t>$4.59</t>
         </is>
       </c>
+      <c r="FD5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="FE5" t="inlineStr">
+        <is>
+          <t>$4.59</t>
+        </is>
+      </c>
+      <c r="FF5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="FG5" t="inlineStr">
+        <is>
+          <t>$4.59</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5209,6 +5309,26 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="FD6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="FE6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="FF6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="FG6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6006,6 +6126,26 @@
           <t>$3.65</t>
         </is>
       </c>
+      <c r="FD7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="FE7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
+      <c r="FF7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="FG7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6803,6 +6943,26 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="FD8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="FE8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
+      <c r="FF8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="FG8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7600,6 +7760,26 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="FD9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="FE9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="FF9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="FG9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8397,6 +8577,26 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="FD10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="FE10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
+      <c r="FF10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="FG10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -9194,6 +9394,26 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="FD11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="FE11" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
+      <c r="FF11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="FG11" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -9991,6 +10211,26 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="FD12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="FE12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
+      <c r="FF12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="FG12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -10788,6 +11028,26 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="FD13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="FE13" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="FF13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="FG13" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -11585,6 +11845,26 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="FD14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="FE14" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
+      <c r="FF14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="FG14" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -12382,6 +12662,26 @@
           <t>$7.49/lb</t>
         </is>
       </c>
+      <c r="FD15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="FE15" t="inlineStr">
+        <is>
+          <t>$7.49/lb</t>
+        </is>
+      </c>
+      <c r="FF15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="FG15" t="inlineStr">
+        <is>
+          <t>$7.49/lb</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -13179,6 +13479,26 @@
           <t>$4.34 ea.</t>
         </is>
       </c>
+      <c r="FD16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="FE16" t="inlineStr">
+        <is>
+          <t>$4.34 ea.</t>
+        </is>
+      </c>
+      <c r="FF16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="FG16" t="inlineStr">
+        <is>
+          <t>$4.34 ea.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -13976,6 +14296,26 @@
           <t>$40,275</t>
         </is>
       </c>
+      <c r="FD17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="FE17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
+      <c r="FF17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="FG17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -14589,6 +14929,26 @@
         </is>
       </c>
       <c r="FC18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="FD18" t="inlineStr">
+        <is>
+          <t>Silverado</t>
+        </is>
+      </c>
+      <c r="FE18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="FF18" t="inlineStr">
+        <is>
+          <t>Silverado</t>
+        </is>
+      </c>
+      <c r="FG18" t="inlineStr">
         <is>
           <t>$37,000*</t>
         </is>
@@ -15238,6 +15598,26 @@
           <t>$3.94</t>
         </is>
       </c>
+      <c r="FD19" t="inlineStr">
+        <is>
+          <t>2 x 4 x 8' Construction/Framing Lumber</t>
+        </is>
+      </c>
+      <c r="FE19" t="inlineStr">
+        <is>
+          <t>$3.94</t>
+        </is>
+      </c>
+      <c r="FF19" t="inlineStr">
+        <is>
+          <t>2 x 4 x 8' Construction/Framing Lumber</t>
+        </is>
+      </c>
+      <c r="FG19" t="inlineStr">
+        <is>
+          <t>$3.94</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -16035,6 +16415,26 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="FD20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="FE20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
+      <c r="FF20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="FG20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -16832,6 +17232,26 @@
           <t>$4.47</t>
         </is>
       </c>
+      <c r="FD21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="FE21" t="inlineStr">
+        <is>
+          <t>$4.47</t>
+        </is>
+      </c>
+      <c r="FF21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="FG21" t="inlineStr">
+        <is>
+          <t>$4.47</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -17517,6 +17937,18 @@
         </is>
       </c>
       <c r="FC22" t="inlineStr"/>
+      <c r="FD22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="FE22" t="inlineStr"/>
+      <c r="FF22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="FG22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -18202,6 +18634,18 @@
         </is>
       </c>
       <c r="FC23" t="inlineStr"/>
+      <c r="FD23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="FE23" t="inlineStr"/>
+      <c r="FF23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="FG23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FG23"/>
+  <dimension ref="A1:FI23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1244,6 +1244,16 @@
           <t>Price_2025-04-25 03:05</t>
         </is>
       </c>
+      <c r="FH1" s="1" t="inlineStr">
+        <is>
+          <t>Product Name_2025-04-25 11:25</t>
+        </is>
+      </c>
+      <c r="FI1" s="1" t="inlineStr">
+        <is>
+          <t>Price_2025-04-25 11:25</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2061,6 +2071,16 @@
           <t>2.999</t>
         </is>
       </c>
+      <c r="FH2" t="inlineStr">
+        <is>
+          <t>UNLEADED 87 (10% ETH)</t>
+        </is>
+      </c>
+      <c r="FI2" t="inlineStr">
+        <is>
+          <t>2.999</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2878,6 +2898,16 @@
           <t>$2.87</t>
         </is>
       </c>
+      <c r="FH3" t="inlineStr">
+        <is>
+          <t>That's Smart! Fat Free Skim Milk</t>
+        </is>
+      </c>
+      <c r="FI3" t="inlineStr">
+        <is>
+          <t>$2.87</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3695,6 +3725,16 @@
           <t>32¢ ea.</t>
         </is>
       </c>
+      <c r="FH4" t="inlineStr">
+        <is>
+          <t>Roma Tomatoes</t>
+        </is>
+      </c>
+      <c r="FI4" t="inlineStr">
+        <is>
+          <t>32¢ ea.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4512,6 +4552,16 @@
           <t>$4.59</t>
         </is>
       </c>
+      <c r="FH5" t="inlineStr">
+        <is>
+          <t>Quaker Cap'n Crunch Regular Cereal</t>
+        </is>
+      </c>
+      <c r="FI5" t="inlineStr">
+        <is>
+          <t>$4.59</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5329,6 +5379,16 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="FH6" t="inlineStr">
+        <is>
+          <t>Sara Lee Artesano Brioche Buns, 8 count</t>
+        </is>
+      </c>
+      <c r="FI6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6146,6 +6206,16 @@
           <t>$3.65</t>
         </is>
       </c>
+      <c r="FH7" t="inlineStr">
+        <is>
+          <t>That's Smart! Mayonnaise</t>
+        </is>
+      </c>
+      <c r="FI7" t="inlineStr">
+        <is>
+          <t>$3.65</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6963,6 +7033,16 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="FH8" t="inlineStr">
+        <is>
+          <t>Hy-Vee Light Bartlett Pear Halves In Pear Juice From Concentrate</t>
+        </is>
+      </c>
+      <c r="FI8" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -7780,6 +7860,16 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="FH9" t="inlineStr">
+        <is>
+          <t>Dole Fresh Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="FI9" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8597,6 +8687,16 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="FH10" t="inlineStr">
+        <is>
+          <t>Hy-Vee Oven Roasted Cured Turkey Breast &amp; White Turkey Shaved Slices</t>
+        </is>
+      </c>
+      <c r="FI10" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -9414,6 +9514,16 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="FH11" t="inlineStr">
+        <is>
+          <t>That's Smart! Small Curd Cottage Cheese 4% Milkfat</t>
+        </is>
+      </c>
+      <c r="FI11" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -10231,6 +10341,16 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="FH12" t="inlineStr">
+        <is>
+          <t>Fairlife Fat Free Ultra-Filtered Milk</t>
+        </is>
+      </c>
+      <c r="FI12" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -11048,6 +11168,16 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="FH13" t="inlineStr">
+        <is>
+          <t>Fresh Chiquita Bananas</t>
+        </is>
+      </c>
+      <c r="FI13" t="inlineStr">
+        <is>
+          <t>22¢ ea.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -11865,6 +11995,16 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="FH14" t="inlineStr">
+        <is>
+          <t>Wonderful Halos Mandarin Oranges</t>
+        </is>
+      </c>
+      <c r="FI14" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -12682,6 +12822,16 @@
           <t>$7.49/lb</t>
         </is>
       </c>
+      <c r="FH15" t="inlineStr">
+        <is>
+          <t>Certified Ground Round 90% Lean 10% Fat</t>
+        </is>
+      </c>
+      <c r="FI15" t="inlineStr">
+        <is>
+          <t>$7.49/lb</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -13499,6 +13649,16 @@
           <t>$4.34 ea.</t>
         </is>
       </c>
+      <c r="FH16" t="inlineStr">
+        <is>
+          <t>Boneless Skinless Chicken Breast</t>
+        </is>
+      </c>
+      <c r="FI16" t="inlineStr">
+        <is>
+          <t>$4.34 ea.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -14316,6 +14476,16 @@
           <t>$40,275</t>
         </is>
       </c>
+      <c r="FH17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="FI17" t="inlineStr">
+        <is>
+          <t>$40,275</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -14949,6 +15119,16 @@
         </is>
       </c>
       <c r="FG18" t="inlineStr">
+        <is>
+          <t>$37,000*</t>
+        </is>
+      </c>
+      <c r="FH18" t="inlineStr">
+        <is>
+          <t>Silverado</t>
+        </is>
+      </c>
+      <c r="FI18" t="inlineStr">
         <is>
           <t>$37,000*</t>
         </is>
@@ -15618,6 +15798,16 @@
           <t>$3.94</t>
         </is>
       </c>
+      <c r="FH19" t="inlineStr">
+        <is>
+          <t>2 x 4 x 8' Construction/Framing Lumber</t>
+        </is>
+      </c>
+      <c r="FI19" t="inlineStr">
+        <is>
+          <t>$3.94</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -16435,6 +16625,16 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="FH20" t="inlineStr">
+        <is>
+          <t>Hy-Vee Select 100% Pure Maple Syrup</t>
+        </is>
+      </c>
+      <c r="FI20" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -17252,6 +17452,16 @@
           <t>$4.47</t>
         </is>
       </c>
+      <c r="FH21" t="inlineStr">
+        <is>
+          <t>That's Smart! Large Shell Eggs</t>
+        </is>
+      </c>
+      <c r="FI21" t="inlineStr">
+        <is>
+          <t>$4.47</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -17949,6 +18159,16 @@
         </is>
       </c>
       <c r="FG22" t="inlineStr"/>
+      <c r="FH22" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="FI22" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -18646,6 +18866,16 @@
         </is>
       </c>
       <c r="FG23" t="inlineStr"/>
+      <c r="FH23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="FI23" t="inlineStr">
+        <is>
+          <t>748</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,2063 +413,2068 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:OU24"/>
+  <dimension ref="A1:OV24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Product Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Price_2025-02-12 14:57</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Price_2025-02-14 03:04</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Price_2025-02-14 08:31</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Price_2025-02-15 03:04</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Price_2025-02-16 03:05</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Price_2025-02-17 03:04</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Price_2025-02-18 03:04</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Price_2025-02-19 03:05</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Price_2025-02-20 03:04</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Price_2025-02-21 03:04</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Price_2025-02-22 03:05</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Price_2025-02-23 03:04</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Price_2025-02-24 03:04</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Price_2025-02-25 03:05</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Price_2025-02-25 21:06</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Price_2025-02-26 03:05</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Price_2025-02-27 03:04</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Price_2025-02-28 03:05</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Price_2025-03-01 03:04</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Price_2025-03-02 03:05</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Price_2025-03-03 03:05</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Price_2025-03-04 03:04</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Price_2025-03-04 10:51</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Price_2025-03-04 17:48</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Price_2025-03-05 03:05</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Price_2025-03-06 03:05</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Price_2025-03-07 03:04</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Price_2025-03-08 03:04</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Price_2025-03-09 03:04</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Price_2025-03-10 03:05</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Price_2025-03-11 03:04</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Price_2025-03-12 03:05</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Price_2025-03-13 03:05</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Price_2025-03-14 03:04</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Price_2025-03-15 03:05</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Price_2025-03-16 03:04</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>Price_2025-03-17 03:05</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>Price_2025-03-18 03:04</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>Price_2025-03-19 03:04</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>Price_2025-03-20 03:05</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>Price_2025-03-21 03:05</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>Price_2025-03-21 10:49</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>Price_2025-03-22 03:03</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>Price_2025-03-23 03:07</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Price_2025-03-24 03:05</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>Price_2025-03-25 03:04</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>Price_2025-03-26 03:04</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>Price_2025-03-27 03:03</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>Price_2025-03-28 03:04</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>Price_2025-03-29 03:05</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>Price_2025-03-30 03:05</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>Price_2025-03-31 03:03</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>Price_2025-04-01 03:03</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>Price_2025-04-02 03:04</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>Price_2025-04-03 03:05</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>Price_2025-04-04 03:04</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>Price_2025-04-05 03:05</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>Price_2025-04-06 03:04</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>Price_2025-04-07 03:04</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>Price_2025-04-08 03:05</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>Price_2025-04-09 03:10</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>Price_2025-04-10 03:05</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>Price_2025-04-11 03:04</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>Price_2025-04-12 03:04</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>Price_2025-04-13 03:05</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>Price_2025-04-14 03:05</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>Price_2025-04-15 03:04</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>Price_2025-04-16 03:05</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>Price_2025-04-17 03:04</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>Price_2025-04-18 03:04</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>Price_2025-04-19 03:05</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>Price_2025-04-20 03:04</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>Price_2025-04-21 03:05</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>Price_2025-04-22 03:04</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>Price_2025-04-23 03:05</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>Price_2025-04-24 03:04</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>Price_2025-04-25 03:05</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>Price_2025-04-25 11:25</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>Price_2025-04-26 03:04</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>Price_2025-04-27 03:04</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>Price_2025-04-27 09:01</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>Price_2025-05-21 03:04</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>Price_2025-05-22 03:05</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>Price_2025-05-23 03:04</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>Price_2025-05-24 03:04</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>Price_2025-05-25 03:04</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>Price_2025-05-26 03:05</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>Price_2025-05-27 03:04</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>Price_2025-05-28 03:04</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>Price_2025-05-29 03:05</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>Price_2025-05-30 03:04</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>Price_2025-05-31 03:05</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>Price_2025-06-01 03:04</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>Price_2025-06-02 03:04</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>Price_2025-06-03 03:05</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>Price_2025-06-04 03:04</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>Price_2025-06-05 03:04</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>Price_2025-06-06 03:04</t>
         </is>
       </c>
-      <c r="CW1" s="1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>Price_2025-06-07 03:04</t>
         </is>
       </c>
-      <c r="CX1" s="1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>Price_2025-06-08 03:04</t>
         </is>
       </c>
-      <c r="CY1" s="1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>Price_2025-06-09 03:05</t>
         </is>
       </c>
-      <c r="CZ1" s="1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>Price_2025-06-10 03:04</t>
         </is>
       </c>
-      <c r="DA1" s="1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>Price_2025-06-11 03:04</t>
         </is>
       </c>
-      <c r="DB1" s="1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>Price_2025-06-12 03:03</t>
         </is>
       </c>
-      <c r="DC1" s="1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>Price_2025-06-13 03:04</t>
         </is>
       </c>
-      <c r="DD1" s="1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>Price_2025-06-14 03:05</t>
         </is>
       </c>
-      <c r="DE1" s="1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>Price_2025-06-15 03:05</t>
         </is>
       </c>
-      <c r="DF1" s="1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>Price_2025-06-16 03:04</t>
         </is>
       </c>
-      <c r="DG1" s="1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>Price_2025-06-17 03:04</t>
         </is>
       </c>
-      <c r="DH1" s="1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>Price_2025-06-18 03:05</t>
         </is>
       </c>
-      <c r="DI1" s="1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>Price_2025-06-19 03:05</t>
         </is>
       </c>
-      <c r="DJ1" s="1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>Price_2025-06-20 03:05</t>
         </is>
       </c>
-      <c r="DK1" s="1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>Price_2025-06-21 03:05</t>
         </is>
       </c>
-      <c r="DL1" s="1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>Price_2025-07-08 03:04</t>
         </is>
       </c>
-      <c r="DM1" s="1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>Price_2025-07-09 03:04</t>
         </is>
       </c>
-      <c r="DN1" s="1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>Price_2025-07-10 03:04</t>
         </is>
       </c>
-      <c r="DO1" s="1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>Price_2025-07-11 03:04</t>
         </is>
       </c>
-      <c r="DP1" s="1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>Price_2025-07-12 03:04</t>
         </is>
       </c>
-      <c r="DQ1" s="1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>Price_2025-07-13 03:05</t>
         </is>
       </c>
-      <c r="DR1" s="1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>Price_2025-07-14 03:04</t>
         </is>
       </c>
-      <c r="DS1" s="1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>Price_2025-07-15 03:05</t>
         </is>
       </c>
-      <c r="DT1" s="1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>Price_2025-07-16 03:05</t>
         </is>
       </c>
-      <c r="DU1" s="1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>Price_2025-07-17 03:04</t>
         </is>
       </c>
-      <c r="DV1" s="1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>Price_2025-07-18 03:05</t>
         </is>
       </c>
-      <c r="DW1" s="1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>Price_2025-07-19 03:04</t>
         </is>
       </c>
-      <c r="DX1" s="1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>Price_2025-07-20 03:05</t>
         </is>
       </c>
-      <c r="DY1" s="1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>Price_2025-07-21 03:04</t>
         </is>
       </c>
-      <c r="DZ1" s="1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>Price_2025-07-22 03:04</t>
         </is>
       </c>
-      <c r="EA1" s="1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>Price_2025-08-07 03:05</t>
         </is>
       </c>
-      <c r="EB1" s="1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>Price_2025-08-08 03:05</t>
         </is>
       </c>
-      <c r="EC1" s="1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>Price_2025-08-09 03:06</t>
         </is>
       </c>
-      <c r="ED1" s="1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>Price_2025-08-10 03:06</t>
         </is>
       </c>
-      <c r="EE1" s="1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>Price_2025-08-11 03:05</t>
         </is>
       </c>
-      <c r="EF1" s="1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>Price_2025-08-12 03:06</t>
         </is>
       </c>
-      <c r="EG1" s="1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>Price_2025-08-13 03:06</t>
         </is>
       </c>
-      <c r="EH1" s="1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>Price_2025-08-14 03:06</t>
         </is>
       </c>
-      <c r="EI1" s="1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>Price_2025-08-15 03:05</t>
         </is>
       </c>
-      <c r="EJ1" s="1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>Price_2025-08-16 03:05</t>
         </is>
       </c>
-      <c r="EK1" s="1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>Price_2025-08-17 03:05</t>
         </is>
       </c>
-      <c r="EL1" s="1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>Price_2025-08-18 03:05</t>
         </is>
       </c>
-      <c r="EM1" s="1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
         <is>
           <t>Price_2025-08-19 03:05</t>
         </is>
       </c>
-      <c r="EN1" s="1" t="inlineStr">
+      <c r="EN1" t="inlineStr">
         <is>
           <t>Price_2025-08-20 03:06</t>
         </is>
       </c>
-      <c r="EO1" s="1" t="inlineStr">
+      <c r="EO1" t="inlineStr">
         <is>
           <t>Price_2025-08-21 03:06</t>
         </is>
       </c>
-      <c r="EP1" s="1" t="inlineStr">
+      <c r="EP1" t="inlineStr">
         <is>
           <t>Price_2025-08-22 03:06</t>
         </is>
       </c>
-      <c r="EQ1" s="1" t="inlineStr">
+      <c r="EQ1" t="inlineStr">
         <is>
           <t>Price_2025-08-23 03:04</t>
         </is>
       </c>
-      <c r="ER1" s="1" t="inlineStr">
+      <c r="ER1" t="inlineStr">
         <is>
           <t>Price_2025-08-24 03:05</t>
         </is>
       </c>
-      <c r="ES1" s="1" t="inlineStr">
+      <c r="ES1" t="inlineStr">
         <is>
           <t>Price_2025-08-25 03:04</t>
         </is>
       </c>
-      <c r="ET1" s="1" t="inlineStr">
+      <c r="ET1" t="inlineStr">
         <is>
           <t>Price_2025-08-26 03:05</t>
         </is>
       </c>
-      <c r="EU1" s="1" t="inlineStr">
+      <c r="EU1" t="inlineStr">
         <is>
           <t>Price_2025-08-26 10:01</t>
         </is>
       </c>
-      <c r="EV1" s="1" t="inlineStr">
+      <c r="EV1" t="inlineStr">
         <is>
           <t>Price_2025-08-26 10:09</t>
         </is>
       </c>
-      <c r="EW1" s="1" t="inlineStr">
+      <c r="EW1" t="inlineStr">
         <is>
           <t>Price_2025-08-26 10:23</t>
         </is>
       </c>
-      <c r="EX1" s="1" t="inlineStr">
+      <c r="EX1" t="inlineStr">
         <is>
           <t>Price_2025-08-27 03:04</t>
         </is>
       </c>
-      <c r="EY1" s="1" t="inlineStr">
+      <c r="EY1" t="inlineStr">
         <is>
           <t>Price_2025-08-28 03:04</t>
         </is>
       </c>
-      <c r="EZ1" s="1" t="inlineStr">
+      <c r="EZ1" t="inlineStr">
         <is>
           <t>Price_2025-08-29 03:04</t>
         </is>
       </c>
-      <c r="FA1" s="1" t="inlineStr">
+      <c r="FA1" t="inlineStr">
         <is>
           <t>Price_2025-08-30 03:05</t>
         </is>
       </c>
-      <c r="FB1" s="1" t="inlineStr">
+      <c r="FB1" t="inlineStr">
         <is>
           <t>Price_2025-08-31 03:04</t>
         </is>
       </c>
-      <c r="FC1" s="1" t="inlineStr">
+      <c r="FC1" t="inlineStr">
         <is>
           <t>Price_2025-09-01 03:04</t>
         </is>
       </c>
-      <c r="FD1" s="1" t="inlineStr">
+      <c r="FD1" t="inlineStr">
         <is>
           <t>Price_2025-09-02 03:06</t>
         </is>
       </c>
-      <c r="FE1" s="1" t="inlineStr">
+      <c r="FE1" t="inlineStr">
         <is>
           <t>Price_2025-09-03 03:04</t>
         </is>
       </c>
-      <c r="FF1" s="1" t="inlineStr">
+      <c r="FF1" t="inlineStr">
         <is>
           <t>Price_2025-09-04 03:05</t>
         </is>
       </c>
-      <c r="FG1" s="1" t="inlineStr">
+      <c r="FG1" t="inlineStr">
         <is>
           <t>Price_2025-09-05 03:04</t>
         </is>
       </c>
-      <c r="FH1" s="1" t="inlineStr">
+      <c r="FH1" t="inlineStr">
         <is>
           <t>Price_2025-09-06 03:05</t>
         </is>
       </c>
-      <c r="FI1" s="1" t="inlineStr">
+      <c r="FI1" t="inlineStr">
         <is>
           <t>Price_2025-09-07 03:04</t>
         </is>
       </c>
-      <c r="FJ1" s="1" t="inlineStr">
+      <c r="FJ1" t="inlineStr">
         <is>
           <t>Price_2025-09-08 03:04</t>
         </is>
       </c>
-      <c r="FK1" s="1" t="inlineStr">
+      <c r="FK1" t="inlineStr">
         <is>
           <t>Price_2025-09-09 03:04</t>
         </is>
       </c>
-      <c r="FL1" s="1" t="inlineStr">
+      <c r="FL1" t="inlineStr">
         <is>
           <t>Price_2025-09-10 03:04</t>
         </is>
       </c>
-      <c r="FM1" s="1" t="inlineStr">
+      <c r="FM1" t="inlineStr">
         <is>
           <t>Price_2025-09-11 03:05</t>
         </is>
       </c>
-      <c r="FN1" s="1" t="inlineStr">
+      <c r="FN1" t="inlineStr">
         <is>
           <t>Price_2025-09-12 03:05</t>
         </is>
       </c>
-      <c r="FO1" s="1" t="inlineStr">
+      <c r="FO1" t="inlineStr">
         <is>
           <t>Price_2025-09-13 03:04</t>
         </is>
       </c>
-      <c r="FP1" s="1" t="inlineStr">
+      <c r="FP1" t="inlineStr">
         <is>
           <t>Price_2025-09-14 03:05</t>
         </is>
       </c>
-      <c r="FQ1" s="1" t="inlineStr">
+      <c r="FQ1" t="inlineStr">
         <is>
           <t>Price_2025-09-15 03:05</t>
         </is>
       </c>
-      <c r="FR1" s="1" t="inlineStr">
+      <c r="FR1" t="inlineStr">
         <is>
           <t>Price_2025-09-16 03:04</t>
         </is>
       </c>
-      <c r="FS1" s="1" t="inlineStr">
+      <c r="FS1" t="inlineStr">
         <is>
           <t>Price_2025-09-17 03:05</t>
         </is>
       </c>
-      <c r="FT1" s="1" t="inlineStr">
+      <c r="FT1" t="inlineStr">
         <is>
           <t>Price_2025-09-18 03:04</t>
         </is>
       </c>
-      <c r="FU1" s="1" t="inlineStr">
+      <c r="FU1" t="inlineStr">
         <is>
           <t>Price_2025-09-19 03:04</t>
         </is>
       </c>
-      <c r="FV1" s="1" t="inlineStr">
+      <c r="FV1" t="inlineStr">
         <is>
           <t>Price_2025-09-20 03:04</t>
         </is>
       </c>
-      <c r="FW1" s="1" t="inlineStr">
+      <c r="FW1" t="inlineStr">
         <is>
           <t>Price_2025-09-21 03:04</t>
         </is>
       </c>
-      <c r="FX1" s="1" t="inlineStr">
+      <c r="FX1" t="inlineStr">
         <is>
           <t>Price_2025-09-22 03:05</t>
         </is>
       </c>
-      <c r="FY1" s="1" t="inlineStr">
+      <c r="FY1" t="inlineStr">
         <is>
           <t>Price_2025-09-23 03:04</t>
         </is>
       </c>
-      <c r="FZ1" s="1" t="inlineStr">
+      <c r="FZ1" t="inlineStr">
         <is>
           <t>Price_2025-09-24 03:05</t>
         </is>
       </c>
-      <c r="GA1" s="1" t="inlineStr">
+      <c r="GA1" t="inlineStr">
         <is>
           <t>Price_2025-09-25 03:04</t>
         </is>
       </c>
-      <c r="GB1" s="1" t="inlineStr">
+      <c r="GB1" t="inlineStr">
         <is>
           <t>Price_2025-09-26 03:04</t>
         </is>
       </c>
-      <c r="GC1" s="1" t="inlineStr">
+      <c r="GC1" t="inlineStr">
         <is>
           <t>Price_2025-09-27 03:04</t>
         </is>
       </c>
-      <c r="GD1" s="1" t="inlineStr">
+      <c r="GD1" t="inlineStr">
         <is>
           <t>Price_2025-09-28 03:04</t>
         </is>
       </c>
-      <c r="GE1" s="1" t="inlineStr">
+      <c r="GE1" t="inlineStr">
         <is>
           <t>Price_2025-09-29 03:05</t>
         </is>
       </c>
-      <c r="GF1" s="1" t="inlineStr">
+      <c r="GF1" t="inlineStr">
         <is>
           <t>Price_2025-09-30 03:04</t>
         </is>
       </c>
-      <c r="GG1" s="1" t="inlineStr">
+      <c r="GG1" t="inlineStr">
         <is>
           <t>Price_2025-10-01 03:05</t>
         </is>
       </c>
-      <c r="GH1" s="1" t="inlineStr">
+      <c r="GH1" t="inlineStr">
         <is>
           <t>Price_2025-10-02 03:06</t>
         </is>
       </c>
-      <c r="GI1" s="1" t="inlineStr">
+      <c r="GI1" t="inlineStr">
         <is>
           <t>Price_2025-10-03 03:16</t>
         </is>
       </c>
-      <c r="GJ1" s="1" t="inlineStr">
+      <c r="GJ1" t="inlineStr">
         <is>
           <t>Price_2025-10-04 03:17</t>
         </is>
       </c>
-      <c r="GK1" s="1" t="inlineStr">
+      <c r="GK1" t="inlineStr">
         <is>
           <t>Price_2025-10-05 03:17</t>
         </is>
       </c>
-      <c r="GL1" s="1" t="inlineStr">
+      <c r="GL1" t="inlineStr">
         <is>
           <t>Price_2025-10-06 03:16</t>
         </is>
       </c>
-      <c r="GM1" s="1" t="inlineStr">
+      <c r="GM1" t="inlineStr">
         <is>
           <t>Price_2025-10-07 03:16</t>
         </is>
       </c>
-      <c r="GN1" s="1" t="inlineStr">
+      <c r="GN1" t="inlineStr">
         <is>
           <t>Price_2025-10-08 03:17</t>
         </is>
       </c>
-      <c r="GO1" s="1" t="inlineStr">
+      <c r="GO1" t="inlineStr">
         <is>
           <t>Price_2025-10-09 03:17</t>
         </is>
       </c>
-      <c r="GP1" s="1" t="inlineStr">
+      <c r="GP1" t="inlineStr">
         <is>
           <t>Price_2025-10-10 03:16</t>
         </is>
       </c>
-      <c r="GQ1" s="1" t="inlineStr">
+      <c r="GQ1" t="inlineStr">
         <is>
           <t>Price_2025-10-11 03:16</t>
         </is>
       </c>
-      <c r="GR1" s="1" t="inlineStr">
+      <c r="GR1" t="inlineStr">
         <is>
           <t>Price_2025-10-12 03:16</t>
         </is>
       </c>
-      <c r="GS1" s="1" t="inlineStr">
+      <c r="GS1" t="inlineStr">
         <is>
           <t>Price_2025-10-13 03:16</t>
         </is>
       </c>
-      <c r="GT1" s="1" t="inlineStr">
+      <c r="GT1" t="inlineStr">
         <is>
           <t>Price_2025-10-14 03:17</t>
         </is>
       </c>
-      <c r="GU1" s="1" t="inlineStr">
+      <c r="GU1" t="inlineStr">
         <is>
           <t>Price_2025-10-15 03:16</t>
         </is>
       </c>
-      <c r="GV1" s="1" t="inlineStr">
+      <c r="GV1" t="inlineStr">
         <is>
           <t>Price_2025-10-16 03:16</t>
         </is>
       </c>
-      <c r="GW1" s="1" t="inlineStr">
+      <c r="GW1" t="inlineStr">
         <is>
           <t>Price_2025-10-17 03:17</t>
         </is>
       </c>
-      <c r="GX1" s="1" t="inlineStr">
+      <c r="GX1" t="inlineStr">
         <is>
           <t>Price_2025-10-18 03:16</t>
         </is>
       </c>
-      <c r="GY1" s="1" t="inlineStr">
+      <c r="GY1" t="inlineStr">
         <is>
           <t>Price_2025-10-19 03:17</t>
         </is>
       </c>
-      <c r="GZ1" s="1" t="inlineStr">
+      <c r="GZ1" t="inlineStr">
         <is>
           <t>Price_2025-10-20 03:17</t>
         </is>
       </c>
-      <c r="HA1" s="1" t="inlineStr">
+      <c r="HA1" t="inlineStr">
         <is>
           <t>Price_2025-10-21 03:16</t>
         </is>
       </c>
-      <c r="HB1" s="1" t="inlineStr">
+      <c r="HB1" t="inlineStr">
         <is>
           <t>Price_2025-10-22 03:16</t>
         </is>
       </c>
-      <c r="HC1" s="1" t="inlineStr">
+      <c r="HC1" t="inlineStr">
         <is>
           <t>Price_2025-10-23 03:17</t>
         </is>
       </c>
-      <c r="HD1" s="1" t="inlineStr">
+      <c r="HD1" t="inlineStr">
         <is>
           <t>Price_2025-10-24 03:16</t>
         </is>
       </c>
-      <c r="HE1" s="1" t="inlineStr">
+      <c r="HE1" t="inlineStr">
         <is>
           <t>Price_2025-10-25 03:16</t>
         </is>
       </c>
-      <c r="HF1" s="1" t="inlineStr">
+      <c r="HF1" t="inlineStr">
         <is>
           <t>Price_2025-10-26 03:16</t>
         </is>
       </c>
-      <c r="HG1" s="1" t="inlineStr">
+      <c r="HG1" t="inlineStr">
         <is>
           <t>Price_2025-10-27 03:16</t>
         </is>
       </c>
-      <c r="HH1" s="1" t="inlineStr">
+      <c r="HH1" t="inlineStr">
         <is>
           <t>Price_2025-10-28 03:16</t>
         </is>
       </c>
-      <c r="HI1" s="1" t="inlineStr">
+      <c r="HI1" t="inlineStr">
         <is>
           <t>Price_2025-10-29 03:16</t>
         </is>
       </c>
-      <c r="HJ1" s="1" t="inlineStr">
+      <c r="HJ1" t="inlineStr">
         <is>
           <t>Price_2025-10-30 03:16</t>
         </is>
       </c>
-      <c r="HK1" s="1" t="inlineStr">
+      <c r="HK1" t="inlineStr">
         <is>
           <t>Price_2025-10-31 03:16</t>
         </is>
       </c>
-      <c r="HL1" s="1" t="inlineStr">
+      <c r="HL1" t="inlineStr">
         <is>
           <t>Price_2025-11-01 03:16</t>
         </is>
       </c>
-      <c r="HM1" s="1" t="inlineStr">
+      <c r="HM1" t="inlineStr">
         <is>
           <t>Price_2025-11-02 03:16</t>
         </is>
       </c>
-      <c r="HN1" s="1" t="inlineStr">
+      <c r="HN1" t="inlineStr">
         <is>
           <t>Price_2025-11-03 03:16</t>
         </is>
       </c>
-      <c r="HO1" s="1" t="inlineStr">
+      <c r="HO1" t="inlineStr">
         <is>
           <t>Price_2025-11-04 03:16</t>
         </is>
       </c>
-      <c r="HP1" s="1" t="inlineStr">
+      <c r="HP1" t="inlineStr">
         <is>
           <t>Price_2025-11-05 03:16</t>
         </is>
       </c>
-      <c r="HQ1" s="1" t="inlineStr">
+      <c r="HQ1" t="inlineStr">
         <is>
           <t>Price_2025-11-06 03:17</t>
         </is>
       </c>
-      <c r="HR1" s="1" t="inlineStr">
+      <c r="HR1" t="inlineStr">
         <is>
           <t>Price_2025-11-07 03:16</t>
         </is>
       </c>
-      <c r="HS1" s="1" t="inlineStr">
+      <c r="HS1" t="inlineStr">
         <is>
           <t>Price_2025-11-08 03:16</t>
         </is>
       </c>
-      <c r="HT1" s="1" t="inlineStr">
+      <c r="HT1" t="inlineStr">
         <is>
           <t>Price_2025-11-09 03:15</t>
         </is>
       </c>
-      <c r="HU1" s="1" t="inlineStr">
+      <c r="HU1" t="inlineStr">
         <is>
           <t>Price_2025-11-10 03:16</t>
         </is>
       </c>
-      <c r="HV1" s="1" t="inlineStr">
+      <c r="HV1" t="inlineStr">
         <is>
           <t>Price_2025-11-11 03:16</t>
         </is>
       </c>
-      <c r="HW1" s="1" t="inlineStr">
+      <c r="HW1" t="inlineStr">
         <is>
           <t>Price_2025-11-12 03:16</t>
         </is>
       </c>
-      <c r="HX1" s="1" t="inlineStr">
+      <c r="HX1" t="inlineStr">
         <is>
           <t>Price_2025-11-13 03:16</t>
         </is>
       </c>
-      <c r="HY1" s="1" t="inlineStr">
+      <c r="HY1" t="inlineStr">
         <is>
           <t>Price_2025-11-14 03:16</t>
         </is>
       </c>
-      <c r="HZ1" s="1" t="inlineStr">
+      <c r="HZ1" t="inlineStr">
         <is>
           <t>Price_2025-11-15 03:16</t>
         </is>
       </c>
-      <c r="IA1" s="1" t="inlineStr">
+      <c r="IA1" t="inlineStr">
         <is>
           <t>Price_2025-11-16 03:16</t>
         </is>
       </c>
-      <c r="IB1" s="1" t="inlineStr">
+      <c r="IB1" t="inlineStr">
         <is>
           <t>Price_2025-11-17 03:17</t>
         </is>
       </c>
-      <c r="IC1" s="1" t="inlineStr">
+      <c r="IC1" t="inlineStr">
         <is>
           <t>Price_2025-11-18 03:16</t>
         </is>
       </c>
-      <c r="ID1" s="1" t="inlineStr">
+      <c r="ID1" t="inlineStr">
         <is>
           <t>Price_2025-11-19 03:16</t>
         </is>
       </c>
-      <c r="IE1" s="1" t="inlineStr">
+      <c r="IE1" t="inlineStr">
         <is>
           <t>Price_2025-11-20 03:16</t>
         </is>
       </c>
-      <c r="IF1" s="1" t="inlineStr">
+      <c r="IF1" t="inlineStr">
         <is>
           <t>Price_2025-11-21 03:16</t>
         </is>
       </c>
-      <c r="IG1" s="1" t="inlineStr">
+      <c r="IG1" t="inlineStr">
         <is>
           <t>Price_2025-11-22 03:16</t>
         </is>
       </c>
-      <c r="IH1" s="1" t="inlineStr">
+      <c r="IH1" t="inlineStr">
         <is>
           <t>Price_2025-11-23 03:16</t>
         </is>
       </c>
-      <c r="II1" s="1" t="inlineStr">
+      <c r="II1" t="inlineStr">
         <is>
           <t>Price_2025-11-24 03:16</t>
         </is>
       </c>
-      <c r="IJ1" s="1" t="inlineStr">
+      <c r="IJ1" t="inlineStr">
         <is>
           <t>Price_2025-11-25 03:16</t>
         </is>
       </c>
-      <c r="IK1" s="1" t="inlineStr">
+      <c r="IK1" t="inlineStr">
         <is>
           <t>Price_2025-11-26 03:16</t>
         </is>
       </c>
-      <c r="IL1" s="1" t="inlineStr">
+      <c r="IL1" t="inlineStr">
         <is>
           <t>Price_2025-11-27 03:16</t>
         </is>
       </c>
-      <c r="IM1" s="1" t="inlineStr">
+      <c r="IM1" t="inlineStr">
         <is>
           <t>Price_2025-11-28 03:17</t>
         </is>
       </c>
-      <c r="IN1" s="1" t="inlineStr">
+      <c r="IN1" t="inlineStr">
         <is>
           <t>Price_2025-11-29 03:17</t>
         </is>
       </c>
-      <c r="IO1" s="1" t="inlineStr">
+      <c r="IO1" t="inlineStr">
         <is>
           <t>Price_2025-12-05 03:16</t>
         </is>
       </c>
-      <c r="IP1" s="1" t="inlineStr">
+      <c r="IP1" t="inlineStr">
         <is>
           <t>Price_2025-12-06 03:16</t>
         </is>
       </c>
-      <c r="IQ1" s="1" t="inlineStr">
+      <c r="IQ1" t="inlineStr">
         <is>
           <t>Price_2025-12-07 03:17</t>
         </is>
       </c>
-      <c r="IR1" s="1" t="inlineStr">
+      <c r="IR1" t="inlineStr">
         <is>
           <t>Price_2025-12-08 03:17</t>
         </is>
       </c>
-      <c r="IS1" s="1" t="inlineStr">
+      <c r="IS1" t="inlineStr">
         <is>
           <t>Price_2025-12-09 03:18</t>
         </is>
       </c>
-      <c r="IT1" s="1" t="inlineStr">
+      <c r="IT1" t="inlineStr">
         <is>
           <t>Price_2025-12-10 03:16</t>
         </is>
       </c>
-      <c r="IU1" s="1" t="inlineStr">
+      <c r="IU1" t="inlineStr">
         <is>
           <t>Price_2025-12-11 03:17</t>
         </is>
       </c>
-      <c r="IV1" s="1" t="inlineStr">
+      <c r="IV1" t="inlineStr">
         <is>
           <t>Price_2025-12-12 03:16</t>
         </is>
       </c>
-      <c r="IW1" s="1" t="inlineStr">
+      <c r="IW1" t="inlineStr">
         <is>
           <t>Price_2025-12-13 03:17</t>
         </is>
       </c>
-      <c r="IX1" s="1" t="inlineStr">
+      <c r="IX1" t="inlineStr">
         <is>
           <t>Price_2025-12-14 03:17</t>
         </is>
       </c>
-      <c r="IY1" s="1" t="inlineStr">
+      <c r="IY1" t="inlineStr">
         <is>
           <t>Price_2025-12-15 03:16</t>
         </is>
       </c>
-      <c r="IZ1" s="1" t="inlineStr">
+      <c r="IZ1" t="inlineStr">
         <is>
           <t>Price_2025-12-16 03:17</t>
         </is>
       </c>
-      <c r="JA1" s="1" t="inlineStr">
+      <c r="JA1" t="inlineStr">
         <is>
           <t>Price_2025-12-17 03:17</t>
         </is>
       </c>
-      <c r="JB1" s="1" t="inlineStr">
+      <c r="JB1" t="inlineStr">
         <is>
           <t>Price_2025-12-18 03:16</t>
         </is>
       </c>
-      <c r="JC1" s="1" t="inlineStr">
+      <c r="JC1" t="inlineStr">
         <is>
           <t>Price_2025-12-19 03:16</t>
         </is>
       </c>
-      <c r="JD1" s="1" t="inlineStr">
+      <c r="JD1" t="inlineStr">
         <is>
           <t>Price_2025-12-20 03:16</t>
         </is>
       </c>
-      <c r="JE1" s="1" t="inlineStr">
+      <c r="JE1" t="inlineStr">
         <is>
           <t>Price_2025-12-21 03:16</t>
         </is>
       </c>
-      <c r="JF1" s="1" t="inlineStr">
+      <c r="JF1" t="inlineStr">
         <is>
           <t>Price_2025-12-22 03:17</t>
         </is>
       </c>
-      <c r="JG1" s="1" t="inlineStr">
+      <c r="JG1" t="inlineStr">
         <is>
           <t>Price_2025-12-23 03:16</t>
         </is>
       </c>
-      <c r="JH1" s="1" t="inlineStr">
+      <c r="JH1" t="inlineStr">
         <is>
           <t>Price_2025-12-24 03:17</t>
         </is>
       </c>
-      <c r="JI1" s="1" t="inlineStr">
+      <c r="JI1" t="inlineStr">
         <is>
           <t>Price_2025-12-25 03:17</t>
         </is>
       </c>
-      <c r="JJ1" s="1" t="inlineStr">
+      <c r="JJ1" t="inlineStr">
         <is>
           <t>Price_2025-12-29 03:17</t>
         </is>
       </c>
-      <c r="JK1" s="1" t="inlineStr">
+      <c r="JK1" t="inlineStr">
         <is>
           <t>Price_2025-12-30 03:17</t>
         </is>
       </c>
-      <c r="JL1" s="1" t="inlineStr">
+      <c r="JL1" t="inlineStr">
         <is>
           <t>Price_2025-12-31 03:16</t>
         </is>
       </c>
-      <c r="JM1" s="1" t="inlineStr">
+      <c r="JM1" t="inlineStr">
         <is>
           <t>Price_2026-01-01 03:17</t>
         </is>
       </c>
-      <c r="JN1" s="1" t="inlineStr">
+      <c r="JN1" t="inlineStr">
         <is>
           <t>Price_2026-01-02 03:17</t>
         </is>
       </c>
-      <c r="JO1" s="1" t="inlineStr">
+      <c r="JO1" t="inlineStr">
         <is>
           <t>Price_2026-01-03 03:17</t>
         </is>
       </c>
-      <c r="JP1" s="1" t="inlineStr">
+      <c r="JP1" t="inlineStr">
         <is>
           <t>Price_2026-01-04 03:17</t>
         </is>
       </c>
-      <c r="JQ1" s="1" t="inlineStr">
+      <c r="JQ1" t="inlineStr">
         <is>
           <t>Price_2026-01-05 03:16</t>
         </is>
       </c>
-      <c r="JR1" s="1" t="inlineStr">
+      <c r="JR1" t="inlineStr">
         <is>
           <t>Price_2026-01-06 03:17</t>
         </is>
       </c>
-      <c r="JS1" s="1" t="inlineStr">
+      <c r="JS1" t="inlineStr">
         <is>
           <t>Price_2026-01-07 03:17</t>
         </is>
       </c>
-      <c r="JT1" s="1" t="inlineStr">
+      <c r="JT1" t="inlineStr">
         <is>
           <t>Price_2026-01-08 03:16</t>
         </is>
       </c>
-      <c r="JU1" s="1" t="inlineStr">
+      <c r="JU1" t="inlineStr">
         <is>
           <t>Price_2026-01-09 03:16</t>
         </is>
       </c>
-      <c r="JV1" s="1" t="inlineStr">
+      <c r="JV1" t="inlineStr">
         <is>
           <t>Price_2026-01-10 03:16</t>
         </is>
       </c>
-      <c r="JW1" s="1" t="inlineStr">
+      <c r="JW1" t="inlineStr">
         <is>
           <t>Price_2026-01-11 03:16</t>
         </is>
       </c>
-      <c r="JX1" s="1" t="inlineStr">
+      <c r="JX1" t="inlineStr">
         <is>
           <t>Price_2026-01-12 03:16</t>
         </is>
       </c>
-      <c r="JY1" s="1" t="inlineStr">
+      <c r="JY1" t="inlineStr">
         <is>
           <t>Price_2026-01-13 03:17</t>
         </is>
       </c>
-      <c r="JZ1" s="1" t="inlineStr">
+      <c r="JZ1" t="inlineStr">
         <is>
           <t>Price_2026-01-14 03:17</t>
         </is>
       </c>
-      <c r="KA1" s="1" t="inlineStr">
+      <c r="KA1" t="inlineStr">
         <is>
           <t>Price_2026-01-15 03:16</t>
         </is>
       </c>
-      <c r="KB1" s="1" t="inlineStr">
+      <c r="KB1" t="inlineStr">
         <is>
           <t>Price_2026-01-16 03:16</t>
         </is>
       </c>
-      <c r="KC1" s="1" t="inlineStr">
+      <c r="KC1" t="inlineStr">
         <is>
           <t>Price_2026-01-17 03:16</t>
         </is>
       </c>
-      <c r="KD1" s="1" t="inlineStr">
+      <c r="KD1" t="inlineStr">
         <is>
           <t>Price_2026-01-18 03:16</t>
         </is>
       </c>
-      <c r="KE1" s="1" t="inlineStr">
+      <c r="KE1" t="inlineStr">
         <is>
           <t>Price_2026-01-19 03:16</t>
         </is>
       </c>
-      <c r="KF1" s="1" t="inlineStr">
+      <c r="KF1" t="inlineStr">
         <is>
           <t>Price_2026-01-20 03:17</t>
         </is>
       </c>
-      <c r="KG1" s="1" t="inlineStr">
+      <c r="KG1" t="inlineStr">
         <is>
           <t>Price_2026-01-21 03:17</t>
         </is>
       </c>
-      <c r="KH1" s="1" t="inlineStr">
+      <c r="KH1" t="inlineStr">
         <is>
           <t>Price_2026-01-22 03:18</t>
         </is>
       </c>
-      <c r="KI1" s="1" t="inlineStr">
+      <c r="KI1" t="inlineStr">
         <is>
           <t>Price_2026-01-23 03:17</t>
         </is>
       </c>
-      <c r="KJ1" s="1" t="inlineStr">
+      <c r="KJ1" t="inlineStr">
         <is>
           <t>Price_2026-01-24 03:18</t>
         </is>
       </c>
-      <c r="KK1" s="1" t="inlineStr">
+      <c r="KK1" t="inlineStr">
         <is>
           <t>Price_2026-01-25 03:18</t>
         </is>
       </c>
-      <c r="KL1" s="1" t="inlineStr">
+      <c r="KL1" t="inlineStr">
         <is>
           <t>Price_2026-01-26 03:17</t>
         </is>
       </c>
-      <c r="KM1" s="1" t="inlineStr">
+      <c r="KM1" t="inlineStr">
         <is>
           <t>Price_2026-01-27 03:17</t>
         </is>
       </c>
-      <c r="KN1" s="1" t="inlineStr">
+      <c r="KN1" t="inlineStr">
         <is>
           <t>Price_2026-01-28 03:17</t>
         </is>
       </c>
-      <c r="KO1" s="1" t="inlineStr">
+      <c r="KO1" t="inlineStr">
         <is>
           <t>Price_2026-01-29 03:17</t>
         </is>
       </c>
-      <c r="KP1" s="1" t="inlineStr">
+      <c r="KP1" t="inlineStr">
         <is>
           <t>Price_2026-01-30 03:16</t>
         </is>
       </c>
-      <c r="KQ1" s="1" t="inlineStr">
+      <c r="KQ1" t="inlineStr">
         <is>
           <t>Price_2026-01-31 03:17</t>
         </is>
       </c>
-      <c r="KR1" s="1" t="inlineStr">
+      <c r="KR1" t="inlineStr">
         <is>
           <t>Price_2026-02-01 03:17</t>
         </is>
       </c>
-      <c r="KS1" s="1" t="inlineStr">
+      <c r="KS1" t="inlineStr">
         <is>
           <t>Price_2026-02-02 03:17</t>
         </is>
       </c>
-      <c r="KT1" s="1" t="inlineStr">
+      <c r="KT1" t="inlineStr">
         <is>
           <t>Price_2026-02-03 03:17</t>
         </is>
       </c>
-      <c r="KU1" s="1" t="inlineStr">
+      <c r="KU1" t="inlineStr">
         <is>
           <t>Price_2026-02-04 03:17</t>
         </is>
       </c>
-      <c r="KV1" s="1" t="inlineStr">
+      <c r="KV1" t="inlineStr">
         <is>
           <t>Price_2026-02-05 03:17</t>
         </is>
       </c>
-      <c r="KW1" s="1" t="inlineStr">
+      <c r="KW1" t="inlineStr">
         <is>
           <t>Price_2026-02-06 03:18</t>
         </is>
       </c>
-      <c r="KX1" s="1" t="inlineStr">
+      <c r="KX1" t="inlineStr">
         <is>
           <t>Price_2026-02-07 03:18</t>
         </is>
       </c>
-      <c r="KY1" s="1" t="inlineStr">
+      <c r="KY1" t="inlineStr">
         <is>
           <t>Price_2026-02-08 03:17</t>
         </is>
       </c>
-      <c r="KZ1" s="1" t="inlineStr">
+      <c r="KZ1" t="inlineStr">
         <is>
           <t>Price_2026-02-09 03:17</t>
         </is>
       </c>
-      <c r="LA1" s="1" t="inlineStr">
+      <c r="LA1" t="inlineStr">
         <is>
           <t>Price_2026-02-10 03:17</t>
         </is>
       </c>
-      <c r="LB1" s="1" t="inlineStr">
+      <c r="LB1" t="inlineStr">
         <is>
           <t>Price_2026-02-11 03:17</t>
         </is>
       </c>
-      <c r="LC1" s="1" t="inlineStr">
+      <c r="LC1" t="inlineStr">
         <is>
           <t>Price_2026-02-12 03:18</t>
         </is>
       </c>
-      <c r="LD1" s="1" t="inlineStr">
+      <c r="LD1" t="inlineStr">
         <is>
           <t>Price_2026-02-13 03:17</t>
         </is>
       </c>
-      <c r="LE1" s="1" t="inlineStr">
+      <c r="LE1" t="inlineStr">
         <is>
           <t>Price_2026-02-14 03:17</t>
         </is>
       </c>
-      <c r="LF1" s="1" t="inlineStr">
+      <c r="LF1" t="inlineStr">
         <is>
           <t>Price_2026-02-15 03:17</t>
         </is>
       </c>
-      <c r="LG1" s="1" t="inlineStr">
+      <c r="LG1" t="inlineStr">
         <is>
           <t>Price_2026-02-16 03:17</t>
         </is>
       </c>
-      <c r="LH1" s="1" t="inlineStr">
+      <c r="LH1" t="inlineStr">
         <is>
           <t>Price_2026-02-17 03:17</t>
         </is>
       </c>
-      <c r="LI1" s="1" t="inlineStr">
+      <c r="LI1" t="inlineStr">
         <is>
           <t>Price_2026-02-18 03:17</t>
         </is>
       </c>
-      <c r="LJ1" s="1" t="inlineStr">
+      <c r="LJ1" t="inlineStr">
         <is>
           <t>Price_2026-02-19 03:18</t>
         </is>
       </c>
-      <c r="LK1" s="1" t="inlineStr">
+      <c r="LK1" t="inlineStr">
         <is>
           <t>Price_2026-02-20 03:17</t>
         </is>
       </c>
-      <c r="LL1" s="1" t="inlineStr">
+      <c r="LL1" t="inlineStr">
         <is>
           <t>Price_2026-02-22 03:17</t>
         </is>
       </c>
-      <c r="LM1" s="1" t="inlineStr">
+      <c r="LM1" t="inlineStr">
         <is>
           <t>Price_2026-02-23 03:17</t>
         </is>
       </c>
-      <c r="LN1" s="1" t="inlineStr">
+      <c r="LN1" t="inlineStr">
         <is>
           <t>Price_2026-02-24 03:17</t>
         </is>
       </c>
-      <c r="LO1" s="1" t="inlineStr">
+      <c r="LO1" t="inlineStr">
         <is>
           <t>Price_2026-02-25 03:17</t>
         </is>
       </c>
-      <c r="LP1" s="1" t="inlineStr">
+      <c r="LP1" t="inlineStr">
         <is>
           <t>Price_2026-02-26 03:17</t>
         </is>
       </c>
-      <c r="LQ1" s="1" t="inlineStr">
+      <c r="LQ1" t="inlineStr">
         <is>
           <t>Price_2026-02-27 03:17</t>
         </is>
       </c>
-      <c r="LR1" s="1" t="inlineStr">
+      <c r="LR1" t="inlineStr">
         <is>
           <t>Price_2026-02-28 03:17</t>
         </is>
       </c>
-      <c r="LS1" s="1" t="inlineStr">
+      <c r="LS1" t="inlineStr">
         <is>
           <t>Price_2026-03-01 03:17</t>
         </is>
       </c>
-      <c r="LT1" s="1" t="inlineStr">
+      <c r="LT1" t="inlineStr">
         <is>
           <t>Price_2026-03-02 03:17</t>
         </is>
       </c>
-      <c r="LU1" s="1" t="inlineStr">
+      <c r="LU1" t="inlineStr">
         <is>
           <t>Price_2026-03-03 03:17</t>
         </is>
       </c>
-      <c r="LV1" s="1" t="inlineStr">
+      <c r="LV1" t="inlineStr">
         <is>
           <t>Price_2026-03-04 03:17</t>
         </is>
       </c>
-      <c r="LW1" s="1" t="inlineStr">
+      <c r="LW1" t="inlineStr">
         <is>
           <t>Price_2026-03-05 03:16</t>
         </is>
       </c>
-      <c r="LX1" s="1" t="inlineStr">
+      <c r="LX1" t="inlineStr">
         <is>
           <t>Price_2026-03-06 03:17</t>
         </is>
       </c>
-      <c r="LY1" s="1" t="inlineStr">
+      <c r="LY1" t="inlineStr">
         <is>
           <t>Price_2026-03-07 03:17</t>
         </is>
       </c>
-      <c r="LZ1" s="1" t="inlineStr">
+      <c r="LZ1" t="inlineStr">
         <is>
           <t>Price_2026-03-08 03:17</t>
         </is>
       </c>
-      <c r="MA1" s="1" t="inlineStr">
+      <c r="MA1" t="inlineStr">
         <is>
           <t>Price_2026-03-09 03:17</t>
         </is>
       </c>
-      <c r="MB1" s="1" t="inlineStr">
+      <c r="MB1" t="inlineStr">
         <is>
           <t>Price_2026-03-10 03:17</t>
         </is>
       </c>
-      <c r="MC1" s="1" t="inlineStr">
+      <c r="MC1" t="inlineStr">
         <is>
           <t>Price_2026-03-11 03:17</t>
         </is>
       </c>
-      <c r="MD1" s="1" t="inlineStr">
+      <c r="MD1" t="inlineStr">
         <is>
           <t>Price_2026-03-12 03:17</t>
         </is>
       </c>
-      <c r="ME1" s="1" t="inlineStr">
+      <c r="ME1" t="inlineStr">
         <is>
           <t>Price_2026-03-13 03:17</t>
         </is>
       </c>
-      <c r="MF1" s="1" t="inlineStr">
+      <c r="MF1" t="inlineStr">
         <is>
           <t>Price_2026-03-14 03:17</t>
         </is>
       </c>
-      <c r="MG1" s="1" t="inlineStr">
+      <c r="MG1" t="inlineStr">
         <is>
           <t>Price_2026-03-15 03:17</t>
         </is>
       </c>
-      <c r="MH1" s="1" t="inlineStr">
+      <c r="MH1" t="inlineStr">
         <is>
           <t>Price_2026-03-16 03:17</t>
         </is>
       </c>
-      <c r="MI1" s="1" t="inlineStr">
+      <c r="MI1" t="inlineStr">
         <is>
           <t>Price_2026-03-17 03:17</t>
         </is>
       </c>
-      <c r="MJ1" s="1" t="inlineStr">
+      <c r="MJ1" t="inlineStr">
         <is>
           <t>Price_2026-03-18 03:17</t>
         </is>
       </c>
-      <c r="MK1" s="1" t="inlineStr">
+      <c r="MK1" t="inlineStr">
         <is>
           <t>Price_2026-03-19 03:17</t>
         </is>
       </c>
-      <c r="ML1" s="1" t="inlineStr">
+      <c r="ML1" t="inlineStr">
         <is>
           <t>Price_2026-03-20 03:17</t>
         </is>
       </c>
-      <c r="MM1" s="1" t="inlineStr">
+      <c r="MM1" t="inlineStr">
         <is>
           <t>Price_2026-03-21 03:19</t>
         </is>
       </c>
-      <c r="MN1" s="1" t="inlineStr">
+      <c r="MN1" t="inlineStr">
         <is>
           <t>Price_2026-03-22 03:17</t>
         </is>
       </c>
-      <c r="MO1" s="1" t="inlineStr">
+      <c r="MO1" t="inlineStr">
         <is>
           <t>Price_2026-03-23 03:18</t>
         </is>
       </c>
-      <c r="MP1" s="1" t="inlineStr">
+      <c r="MP1" t="inlineStr">
         <is>
           <t>Price_2026-03-24 03:17</t>
         </is>
       </c>
-      <c r="MQ1" s="1" t="inlineStr">
+      <c r="MQ1" t="inlineStr">
         <is>
           <t>Price_2026-03-25 03:17</t>
         </is>
       </c>
-      <c r="MR1" s="1" t="inlineStr">
+      <c r="MR1" t="inlineStr">
         <is>
           <t>Price_2026-03-26 03:17</t>
         </is>
       </c>
-      <c r="MS1" s="1" t="inlineStr">
+      <c r="MS1" t="inlineStr">
         <is>
           <t>Price_2026-03-27 03:17</t>
         </is>
       </c>
-      <c r="MT1" s="1" t="inlineStr">
+      <c r="MT1" t="inlineStr">
         <is>
           <t>Price_2026-03-28 03:17</t>
         </is>
       </c>
-      <c r="MU1" s="1" t="inlineStr">
+      <c r="MU1" t="inlineStr">
         <is>
           <t>Price_2026-03-29 03:21</t>
         </is>
       </c>
-      <c r="MV1" s="1" t="inlineStr">
+      <c r="MV1" t="inlineStr">
         <is>
           <t>Price_2026-03-30 03:17</t>
         </is>
       </c>
-      <c r="MW1" s="1" t="inlineStr">
+      <c r="MW1" t="inlineStr">
         <is>
           <t>Price_2026-03-31 03:17</t>
         </is>
       </c>
-      <c r="MX1" s="1" t="inlineStr">
+      <c r="MX1" t="inlineStr">
         <is>
           <t>Price_2026-04-01 03:17</t>
         </is>
       </c>
-      <c r="MY1" s="1" t="inlineStr">
+      <c r="MY1" t="inlineStr">
         <is>
           <t>Price_2026-04-02 03:17</t>
         </is>
       </c>
-      <c r="MZ1" s="1" t="inlineStr">
+      <c r="MZ1" t="inlineStr">
         <is>
           <t>Price_2026-04-03 03:17</t>
         </is>
       </c>
-      <c r="NA1" s="1" t="inlineStr">
+      <c r="NA1" t="inlineStr">
         <is>
           <t>Price_2026-04-04 03:17</t>
         </is>
       </c>
-      <c r="NB1" s="1" t="inlineStr">
+      <c r="NB1" t="inlineStr">
         <is>
           <t>Price_2026-04-05 03:17</t>
         </is>
       </c>
-      <c r="NC1" s="1" t="inlineStr">
+      <c r="NC1" t="inlineStr">
         <is>
           <t>Price_2026-04-06 03:17</t>
         </is>
       </c>
-      <c r="ND1" s="1" t="inlineStr">
+      <c r="ND1" t="inlineStr">
         <is>
           <t>Price_2026-04-07 03:17</t>
         </is>
       </c>
-      <c r="NE1" s="1" t="inlineStr">
+      <c r="NE1" t="inlineStr">
         <is>
           <t>Price_2026-04-08 03:17</t>
         </is>
       </c>
-      <c r="NF1" s="1" t="inlineStr">
+      <c r="NF1" t="inlineStr">
         <is>
           <t>Price_2026-04-09 03:17</t>
         </is>
       </c>
-      <c r="NG1" s="1" t="inlineStr">
+      <c r="NG1" t="inlineStr">
         <is>
           <t>Price_2026-04-10 03:17</t>
         </is>
       </c>
-      <c r="NH1" s="1" t="inlineStr">
+      <c r="NH1" t="inlineStr">
         <is>
           <t>Price_2026-04-11 03:17</t>
         </is>
       </c>
-      <c r="NI1" s="1" t="inlineStr">
+      <c r="NI1" t="inlineStr">
         <is>
           <t>Price_2026-04-12 03:17</t>
         </is>
       </c>
-      <c r="NJ1" s="1" t="inlineStr">
+      <c r="NJ1" t="inlineStr">
         <is>
           <t>Price_2026-04-13 03:17</t>
         </is>
       </c>
-      <c r="NK1" s="1" t="inlineStr">
+      <c r="NK1" t="inlineStr">
         <is>
           <t>Price_2026-04-14 03:17</t>
         </is>
       </c>
-      <c r="NL1" s="1" t="inlineStr">
+      <c r="NL1" t="inlineStr">
         <is>
           <t>Price_2026-04-15 03:17</t>
         </is>
       </c>
-      <c r="NM1" s="1" t="inlineStr">
+      <c r="NM1" t="inlineStr">
         <is>
           <t>Price_2026-04-16 03:17</t>
         </is>
       </c>
-      <c r="NN1" s="1" t="inlineStr">
+      <c r="NN1" t="inlineStr">
         <is>
           <t>Price_2026-04-17 03:17</t>
         </is>
       </c>
-      <c r="NO1" s="1" t="inlineStr">
+      <c r="NO1" t="inlineStr">
         <is>
           <t>Price_2026-04-18 03:17</t>
         </is>
       </c>
-      <c r="NP1" s="1" t="inlineStr">
+      <c r="NP1" t="inlineStr">
         <is>
           <t>Price_2026-04-19 03:17</t>
         </is>
       </c>
-      <c r="NQ1" s="1" t="inlineStr">
+      <c r="NQ1" t="inlineStr">
         <is>
           <t>Price_2026-04-20 03:17</t>
         </is>
       </c>
-      <c r="NR1" s="1" t="inlineStr">
+      <c r="NR1" t="inlineStr">
         <is>
           <t>Price_2026-04-21 03:17</t>
         </is>
       </c>
-      <c r="NS1" s="1" t="inlineStr">
+      <c r="NS1" t="inlineStr">
         <is>
           <t>Price_2026-04-22 03:18</t>
         </is>
       </c>
-      <c r="NT1" s="1" t="inlineStr">
+      <c r="NT1" t="inlineStr">
         <is>
           <t>Price_2026-04-23 03:17</t>
         </is>
       </c>
-      <c r="NU1" s="1" t="inlineStr">
+      <c r="NU1" t="inlineStr">
         <is>
           <t>Price_2026-04-24 03:18</t>
         </is>
       </c>
-      <c r="NV1" s="1" t="inlineStr">
+      <c r="NV1" t="inlineStr">
         <is>
           <t>Price_2026-04-25 03:17</t>
         </is>
       </c>
-      <c r="NW1" s="1" t="inlineStr">
+      <c r="NW1" t="inlineStr">
         <is>
           <t>Price_2026-04-26 03:16</t>
         </is>
       </c>
-      <c r="NX1" s="1" t="inlineStr">
+      <c r="NX1" t="inlineStr">
         <is>
           <t>Price_2026-04-27 03:17</t>
         </is>
       </c>
-      <c r="NY1" s="1" t="inlineStr">
+      <c r="NY1" t="inlineStr">
         <is>
           <t>Price_2026-04-28 03:17</t>
         </is>
       </c>
-      <c r="NZ1" s="1" t="inlineStr">
+      <c r="NZ1" t="inlineStr">
         <is>
           <t>Price_2026-04-29 03:17</t>
         </is>
       </c>
-      <c r="OA1" s="1" t="inlineStr">
+      <c r="OA1" t="inlineStr">
         <is>
           <t>Price_2026-04-30 03:18</t>
         </is>
       </c>
-      <c r="OB1" s="1" t="inlineStr">
+      <c r="OB1" t="inlineStr">
         <is>
           <t>Price_2026-05-01 03:17</t>
         </is>
       </c>
-      <c r="OC1" s="1" t="inlineStr">
+      <c r="OC1" t="inlineStr">
         <is>
           <t>Price_2026-05-02 03:18</t>
         </is>
       </c>
-      <c r="OD1" s="1" t="inlineStr">
+      <c r="OD1" t="inlineStr">
         <is>
           <t>Price_2026-05-03 03:17</t>
         </is>
       </c>
-      <c r="OE1" s="1" t="inlineStr">
+      <c r="OE1" t="inlineStr">
         <is>
           <t>Price_2026-05-04 03:17</t>
         </is>
       </c>
-      <c r="OF1" s="1" t="inlineStr">
+      <c r="OF1" t="inlineStr">
         <is>
           <t>Price_2026-05-05 03:17</t>
         </is>
       </c>
-      <c r="OG1" s="1" t="inlineStr">
+      <c r="OG1" t="inlineStr">
         <is>
           <t>Price_2026-05-06 03:17</t>
         </is>
       </c>
-      <c r="OH1" s="1" t="inlineStr">
+      <c r="OH1" t="inlineStr">
         <is>
           <t>Price_2026-05-07 03:17</t>
         </is>
       </c>
-      <c r="OI1" s="1" t="inlineStr">
+      <c r="OI1" t="inlineStr">
         <is>
           <t>Price_2026-05-08 03:18</t>
         </is>
       </c>
-      <c r="OJ1" s="1" t="inlineStr">
+      <c r="OJ1" t="inlineStr">
         <is>
           <t>Price_2026-05-09 03:17</t>
         </is>
       </c>
-      <c r="OK1" s="1" t="inlineStr">
+      <c r="OK1" t="inlineStr">
         <is>
           <t>Price_2026-05-10 03:18</t>
         </is>
       </c>
-      <c r="OL1" s="1" t="inlineStr">
+      <c r="OL1" t="inlineStr">
         <is>
           <t>Price_2026-05-11 03:18</t>
         </is>
       </c>
-      <c r="OM1" s="1" t="inlineStr">
+      <c r="OM1" t="inlineStr">
         <is>
           <t>Price_2026-05-12 03:17</t>
         </is>
       </c>
-      <c r="ON1" s="1" t="inlineStr">
+      <c r="ON1" t="inlineStr">
         <is>
           <t>Price_2026-05-13 03:18</t>
         </is>
       </c>
-      <c r="OO1" s="1" t="inlineStr">
+      <c r="OO1" t="inlineStr">
         <is>
           <t>Price_2026-05-14 03:17</t>
         </is>
       </c>
-      <c r="OP1" s="1" t="inlineStr">
+      <c r="OP1" t="inlineStr">
         <is>
           <t>Price_2026-05-15 03:17</t>
         </is>
       </c>
-      <c r="OQ1" s="1" t="inlineStr">
+      <c r="OQ1" t="inlineStr">
         <is>
           <t>Price_2026-05-16 03:18</t>
         </is>
       </c>
-      <c r="OR1" s="1" t="inlineStr">
+      <c r="OR1" t="inlineStr">
         <is>
           <t>Price_2026-05-17 03:17</t>
         </is>
       </c>
-      <c r="OS1" s="1" t="inlineStr">
+      <c r="OS1" t="inlineStr">
         <is>
           <t>Price_2026-05-18 03:17</t>
         </is>
       </c>
-      <c r="OT1" s="1" t="inlineStr">
+      <c r="OT1" t="inlineStr">
         <is>
           <t>Price_2026-05-19 03:18</t>
         </is>
       </c>
-      <c r="OU1" s="1" t="inlineStr">
+      <c r="OU1" t="inlineStr">
         <is>
           <t>Price_2026-05-29 08:26</t>
+        </is>
+      </c>
+      <c r="OV1" t="inlineStr">
+        <is>
+          <t>Price_2026-05-29 15:02</t>
         </is>
       </c>
     </row>
@@ -4537,6 +4530,11 @@
         </is>
       </c>
       <c r="OU2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="OV2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -6434,6 +6432,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="OV3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8367,6 +8370,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="OV4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10424,6 +10432,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="OV5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12481,6 +12494,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="OV6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14538,6 +14556,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="OV7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -16595,6 +16618,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="OV8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -18652,6 +18680,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="OV9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -20709,6 +20742,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="OV10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -22766,6 +22804,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="OV11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -24823,6 +24866,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="OV12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -26880,6 +26928,11 @@
           <t>$7.99</t>
         </is>
       </c>
+      <c r="OV13" t="inlineStr">
+        <is>
+          <t>$7.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -28937,6 +28990,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="OV14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -30990,6 +31048,11 @@
         </is>
       </c>
       <c r="OU15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="OV15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -32451,6 +32514,11 @@
           <t>$13.61</t>
         </is>
       </c>
+      <c r="OV16" t="inlineStr">
+        <is>
+          <t>$13.61</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -34508,6 +34576,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="OV17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -36565,6 +36638,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="OV18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -38622,6 +38700,11 @@
           <t>$1.89</t>
         </is>
       </c>
+      <c r="OV19" t="inlineStr">
+        <is>
+          <t>$1.89</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -40679,6 +40762,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="OV20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -42736,6 +42824,11 @@
           <t>$1.27</t>
         </is>
       </c>
+      <c r="OV21" t="inlineStr">
+        <is>
+          <t>$1.27</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -44789,6 +44882,11 @@
         </is>
       </c>
       <c r="OU22" t="inlineStr">
+        <is>
+          <t>3.999</t>
+        </is>
+      </c>
+      <c r="OV22" t="inlineStr">
         <is>
           <t>3.999</t>
         </is>
@@ -46858,6 +46956,11 @@
         </is>
       </c>
       <c r="OU23" t="inlineStr">
+        <is>
+          <t>$3.98</t>
+        </is>
+      </c>
+      <c r="OV23" t="inlineStr">
         <is>
           <t>$3.98</t>
         </is>
@@ -48691,6 +48794,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="OV24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:OV24"/>
+  <dimension ref="A1:OW24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2477,6 +2477,11 @@
           <t>Price_2026-05-29 15:02</t>
         </is>
       </c>
+      <c r="OW1" t="inlineStr">
+        <is>
+          <t>Price_2026-05-30 10:08</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4535,6 +4540,11 @@
         </is>
       </c>
       <c r="OV2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="OW2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -6437,6 +6447,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="OW3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8375,6 +8390,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="OW4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10437,6 +10457,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="OW5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12499,6 +12524,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="OW6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14561,6 +14591,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="OW7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -16623,6 +16658,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="OW8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -18685,6 +18725,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="OW9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -20747,6 +20792,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="OW10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -22809,6 +22859,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="OW11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -24871,6 +24926,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="OW12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -26933,6 +26993,11 @@
           <t>$7.99</t>
         </is>
       </c>
+      <c r="OW13" t="inlineStr">
+        <is>
+          <t>$7.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -28995,6 +29060,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="OW14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -31053,6 +31123,11 @@
         </is>
       </c>
       <c r="OV15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="OW15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -32519,6 +32594,11 @@
           <t>$13.61</t>
         </is>
       </c>
+      <c r="OW16" t="inlineStr">
+        <is>
+          <t>$13.61</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -34581,6 +34661,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="OW17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -36643,6 +36728,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="OW18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -38705,6 +38795,11 @@
           <t>$1.89</t>
         </is>
       </c>
+      <c r="OW19" t="inlineStr">
+        <is>
+          <t>$1.89</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -40767,6 +40862,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="OW20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -42829,6 +42929,11 @@
           <t>$1.27</t>
         </is>
       </c>
+      <c r="OW21" t="inlineStr">
+        <is>
+          <t>$1.27</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -44889,6 +44994,11 @@
       <c r="OV22" t="inlineStr">
         <is>
           <t>3.999</t>
+        </is>
+      </c>
+      <c r="OW22" t="inlineStr">
+        <is>
+          <t>3.949</t>
         </is>
       </c>
     </row>
@@ -46961,6 +47071,11 @@
         </is>
       </c>
       <c r="OV23" t="inlineStr">
+        <is>
+          <t>$3.98</t>
+        </is>
+      </c>
+      <c r="OW23" t="inlineStr">
         <is>
           <t>$3.98</t>
         </is>
@@ -48799,6 +48914,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="OW24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:OW24"/>
+  <dimension ref="A1:OX24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2482,6 +2482,11 @@
           <t>Price_2026-05-30 10:08</t>
         </is>
       </c>
+      <c r="OX1" t="inlineStr">
+        <is>
+          <t>Price_2026-05-31 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4545,6 +4550,11 @@
         </is>
       </c>
       <c r="OW2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="OX2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -6452,6 +6462,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="OX3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8395,6 +8410,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="OX4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10462,6 +10482,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="OX5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12529,6 +12554,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="OX6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14596,6 +14626,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="OX7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -16663,6 +16698,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="OX8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -18730,6 +18770,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="OX9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -20797,6 +20842,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="OX10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -22864,6 +22914,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="OX11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -24931,6 +24986,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="OX12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -26998,6 +27058,11 @@
           <t>$7.99</t>
         </is>
       </c>
+      <c r="OX13" t="inlineStr">
+        <is>
+          <t>$7.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -29065,6 +29130,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="OX14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -31128,6 +31198,11 @@
         </is>
       </c>
       <c r="OW15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="OX15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -32599,6 +32674,11 @@
           <t>$13.61</t>
         </is>
       </c>
+      <c r="OX16" t="inlineStr">
+        <is>
+          <t>$13.61</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -34666,6 +34746,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="OX17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -36733,6 +36818,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="OX18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -38800,6 +38890,11 @@
           <t>$1.89</t>
         </is>
       </c>
+      <c r="OX19" t="inlineStr">
+        <is>
+          <t>$1.89</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -40867,6 +40962,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="OX20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -42934,6 +43034,11 @@
           <t>$1.27</t>
         </is>
       </c>
+      <c r="OX21" t="inlineStr">
+        <is>
+          <t>$1.27</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -44999,6 +45104,11 @@
       <c r="OW22" t="inlineStr">
         <is>
           <t>3.949</t>
+        </is>
+      </c>
+      <c r="OX22" t="inlineStr">
+        <is>
+          <t>3.859</t>
         </is>
       </c>
     </row>
@@ -47076,6 +47186,11 @@
         </is>
       </c>
       <c r="OW23" t="inlineStr">
+        <is>
+          <t>$3.98</t>
+        </is>
+      </c>
+      <c r="OX23" t="inlineStr">
         <is>
           <t>$3.98</t>
         </is>
@@ -48919,6 +49034,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="OX24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:OX24"/>
+  <dimension ref="A1:OY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2487,6 +2487,11 @@
           <t>Price_2026-05-31 10:23</t>
         </is>
       </c>
+      <c r="OY1" t="inlineStr">
+        <is>
+          <t>Price_2026-06-01 13:44</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4555,6 +4560,11 @@
         </is>
       </c>
       <c r="OX2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="OY2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -6467,6 +6477,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="OY3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8415,6 +8430,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="OY4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10487,6 +10507,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="OY5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12559,6 +12584,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="OY6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14631,6 +14661,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="OY7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -16703,6 +16738,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="OY8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -18775,6 +18815,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="OY9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -20847,6 +20892,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="OY10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -22919,6 +22969,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="OY11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -24991,6 +25046,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="OY12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -27063,6 +27123,11 @@
           <t>$7.99</t>
         </is>
       </c>
+      <c r="OY13" t="inlineStr">
+        <is>
+          <t>$7.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -29135,6 +29200,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="OY14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -31205,6 +31275,11 @@
       <c r="OX15" t="inlineStr">
         <is>
           <t>$3.99</t>
+        </is>
+      </c>
+      <c r="OY15" t="inlineStr">
+        <is>
+          <t>$3.49</t>
         </is>
       </c>
     </row>
@@ -32679,6 +32754,11 @@
           <t>$13.61</t>
         </is>
       </c>
+      <c r="OY16" t="inlineStr">
+        <is>
+          <t>$13.61</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -34751,6 +34831,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="OY17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -36823,6 +36908,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="OY18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -38895,6 +38985,11 @@
           <t>$1.89</t>
         </is>
       </c>
+      <c r="OY19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -40967,6 +41062,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="OY20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -43039,6 +43139,11 @@
           <t>$1.27</t>
         </is>
       </c>
+      <c r="OY21" t="inlineStr">
+        <is>
+          <t>$1.27</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -45109,6 +45214,11 @@
       <c r="OX22" t="inlineStr">
         <is>
           <t>3.859</t>
+        </is>
+      </c>
+      <c r="OY22" t="inlineStr">
+        <is>
+          <t>3.839</t>
         </is>
       </c>
     </row>
@@ -47191,6 +47301,11 @@
         </is>
       </c>
       <c r="OX23" t="inlineStr">
+        <is>
+          <t>$3.98</t>
+        </is>
+      </c>
+      <c r="OY23" t="inlineStr">
         <is>
           <t>$3.98</t>
         </is>
@@ -49039,6 +49154,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="OY24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:OY24"/>
+  <dimension ref="A1:OZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2492,6 +2492,11 @@
           <t>Price_2026-06-01 13:44</t>
         </is>
       </c>
+      <c r="OZ1" t="inlineStr">
+        <is>
+          <t>Price_2026-06-02 12:12</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4565,6 +4570,11 @@
         </is>
       </c>
       <c r="OY2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="OZ2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -6482,6 +6492,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="OZ3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8435,6 +8450,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="OZ4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10512,6 +10532,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="OZ5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12589,6 +12614,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="OZ6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14666,6 +14696,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="OZ7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -16743,6 +16778,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="OZ8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -18820,6 +18860,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="OZ9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -20897,6 +20942,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="OZ10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -22974,6 +23024,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="OZ11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -25051,6 +25106,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="OZ12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -27128,6 +27188,11 @@
           <t>$7.99</t>
         </is>
       </c>
+      <c r="OZ13" t="inlineStr">
+        <is>
+          <t>$7.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -29205,6 +29270,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="OZ14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -31278,6 +31348,11 @@
         </is>
       </c>
       <c r="OY15" t="inlineStr">
+        <is>
+          <t>$3.49</t>
+        </is>
+      </c>
+      <c r="OZ15" t="inlineStr">
         <is>
           <t>$3.49</t>
         </is>
@@ -32759,6 +32834,11 @@
           <t>$13.61</t>
         </is>
       </c>
+      <c r="OZ16" t="inlineStr">
+        <is>
+          <t>$13.61</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -34836,6 +34916,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="OZ17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -36913,6 +36998,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="OZ18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -38990,6 +39080,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="OZ19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -41067,6 +41162,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="OZ20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -43144,6 +43244,11 @@
           <t>$1.27</t>
         </is>
       </c>
+      <c r="OZ21" t="inlineStr">
+        <is>
+          <t>$1.27</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -45219,6 +45324,11 @@
       <c r="OY22" t="inlineStr">
         <is>
           <t>3.839</t>
+        </is>
+      </c>
+      <c r="OZ22" t="inlineStr">
+        <is>
+          <t>3.819</t>
         </is>
       </c>
     </row>
@@ -47306,6 +47416,11 @@
         </is>
       </c>
       <c r="OY23" t="inlineStr">
+        <is>
+          <t>$3.98</t>
+        </is>
+      </c>
+      <c r="OZ23" t="inlineStr">
         <is>
           <t>$3.98</t>
         </is>
@@ -49159,6 +49274,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="OZ24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:OZ24"/>
+  <dimension ref="A1:PA24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2497,6 +2497,11 @@
           <t>Price_2026-06-02 12:12</t>
         </is>
       </c>
+      <c r="PA1" t="inlineStr">
+        <is>
+          <t>Price_2026-06-03 12:50</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4575,6 +4580,11 @@
         </is>
       </c>
       <c r="OZ2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="PA2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -6497,6 +6507,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="PA3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8455,6 +8470,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="PA4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10537,6 +10557,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="PA5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12619,6 +12644,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="PA6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14701,6 +14731,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="PA7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -16783,6 +16818,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="PA8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -18865,6 +18905,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="PA9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -20947,6 +20992,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="PA10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -23029,6 +23079,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="PA11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -25111,6 +25166,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="PA12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -27193,6 +27253,11 @@
           <t>$7.99</t>
         </is>
       </c>
+      <c r="PA13" t="inlineStr">
+        <is>
+          <t>$7.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -29275,6 +29340,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="PA14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -31353,6 +31423,11 @@
         </is>
       </c>
       <c r="OZ15" t="inlineStr">
+        <is>
+          <t>$3.49</t>
+        </is>
+      </c>
+      <c r="PA15" t="inlineStr">
         <is>
           <t>$3.49</t>
         </is>
@@ -32839,6 +32914,11 @@
           <t>$13.61</t>
         </is>
       </c>
+      <c r="PA16" t="inlineStr">
+        <is>
+          <t>$13.61</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -34921,6 +35001,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="PA17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -37003,6 +37088,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="PA18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -39085,6 +39175,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="PA19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -41167,6 +41262,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="PA20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -43249,6 +43349,11 @@
           <t>$1.27</t>
         </is>
       </c>
+      <c r="PA21" t="inlineStr">
+        <is>
+          <t>$1.27</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -45329,6 +45434,11 @@
       <c r="OZ22" t="inlineStr">
         <is>
           <t>3.819</t>
+        </is>
+      </c>
+      <c r="PA22" t="inlineStr">
+        <is>
+          <t>3.779</t>
         </is>
       </c>
     </row>
@@ -47421,6 +47531,11 @@
         </is>
       </c>
       <c r="OZ23" t="inlineStr">
+        <is>
+          <t>$3.98</t>
+        </is>
+      </c>
+      <c r="PA23" t="inlineStr">
         <is>
           <t>$3.98</t>
         </is>
@@ -49279,6 +49394,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="PA24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:PA24"/>
+  <dimension ref="A1:PB24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2502,6 +2502,11 @@
           <t>Price_2026-06-03 12:50</t>
         </is>
       </c>
+      <c r="PB1" t="inlineStr">
+        <is>
+          <t>Price_2026-06-04 11:09</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4585,6 +4590,11 @@
         </is>
       </c>
       <c r="PA2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="PB2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -6512,6 +6522,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="PB3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8475,6 +8490,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="PB4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10562,6 +10582,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="PB5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12649,6 +12674,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="PB6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14736,6 +14766,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="PB7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -16823,6 +16858,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="PB8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -18910,6 +18950,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="PB9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -20997,6 +21042,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="PB10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -23084,6 +23134,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="PB11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -25171,6 +25226,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="PB12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -27258,6 +27318,11 @@
           <t>$7.99</t>
         </is>
       </c>
+      <c r="PB13" t="inlineStr">
+        <is>
+          <t>$7.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -29345,6 +29410,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="PB14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -31428,6 +31498,11 @@
         </is>
       </c>
       <c r="PA15" t="inlineStr">
+        <is>
+          <t>$3.49</t>
+        </is>
+      </c>
+      <c r="PB15" t="inlineStr">
         <is>
           <t>$3.49</t>
         </is>
@@ -32919,6 +32994,11 @@
           <t>$13.61</t>
         </is>
       </c>
+      <c r="PB16" t="inlineStr">
+        <is>
+          <t>$13.61</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -35006,6 +35086,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="PB17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -37093,6 +37178,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="PB18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -39180,6 +39270,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="PB19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -41267,6 +41362,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="PB20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -43354,6 +43454,11 @@
           <t>$1.27</t>
         </is>
       </c>
+      <c r="PB21" t="inlineStr">
+        <is>
+          <t>$1.27</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -45437,6 +45542,11 @@
         </is>
       </c>
       <c r="PA22" t="inlineStr">
+        <is>
+          <t>3.779</t>
+        </is>
+      </c>
+      <c r="PB22" t="inlineStr">
         <is>
           <t>3.779</t>
         </is>
@@ -47536,6 +47646,11 @@
         </is>
       </c>
       <c r="PA23" t="inlineStr">
+        <is>
+          <t>$3.98</t>
+        </is>
+      </c>
+      <c r="PB23" t="inlineStr">
         <is>
           <t>$3.98</t>
         </is>
@@ -49399,6 +49514,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="PB24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:PB24"/>
+  <dimension ref="A1:PC24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2507,6 +2507,11 @@
           <t>Price_2026-06-04 11:09</t>
         </is>
       </c>
+      <c r="PC1" t="inlineStr">
+        <is>
+          <t>Price_2026-06-05 11:35</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4595,6 +4600,11 @@
         </is>
       </c>
       <c r="PB2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="PC2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -6527,6 +6537,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="PC3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8495,6 +8510,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="PC4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10587,6 +10607,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="PC5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12679,6 +12704,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="PC6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14771,6 +14801,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="PC7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -16863,6 +16898,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="PC8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -18955,6 +18995,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="PC9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21047,6 +21092,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="PC10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -23139,6 +23189,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="PC11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -25231,6 +25286,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="PC12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -27323,6 +27383,11 @@
           <t>$7.99</t>
         </is>
       </c>
+      <c r="PC13" t="inlineStr">
+        <is>
+          <t>$7.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -29415,6 +29480,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="PC14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -31503,6 +31573,11 @@
         </is>
       </c>
       <c r="PB15" t="inlineStr">
+        <is>
+          <t>$3.49</t>
+        </is>
+      </c>
+      <c r="PC15" t="inlineStr">
         <is>
           <t>$3.49</t>
         </is>
@@ -32999,6 +33074,11 @@
           <t>$13.61</t>
         </is>
       </c>
+      <c r="PC16" t="inlineStr">
+        <is>
+          <t>$13.61</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -35091,6 +35171,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="PC17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -37183,6 +37268,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="PC18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -39275,6 +39365,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="PC19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -41367,6 +41462,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="PC20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -43459,6 +43559,11 @@
           <t>$1.27</t>
         </is>
       </c>
+      <c r="PC21" t="inlineStr">
+        <is>
+          <t>$1.27</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -45547,6 +45652,11 @@
         </is>
       </c>
       <c r="PB22" t="inlineStr">
+        <is>
+          <t>3.779</t>
+        </is>
+      </c>
+      <c r="PC22" t="inlineStr">
         <is>
           <t>3.779</t>
         </is>
@@ -47651,6 +47761,11 @@
         </is>
       </c>
       <c r="PB23" t="inlineStr">
+        <is>
+          <t>$3.98</t>
+        </is>
+      </c>
+      <c r="PC23" t="inlineStr">
         <is>
           <t>$3.98</t>
         </is>
@@ -49519,6 +49634,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="PC24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:PC24"/>
+  <dimension ref="A1:PD24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2512,6 +2512,11 @@
           <t>Price_2026-06-05 11:35</t>
         </is>
       </c>
+      <c r="PD1" t="inlineStr">
+        <is>
+          <t>Price_2026-06-06 10:11</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4605,6 +4610,11 @@
         </is>
       </c>
       <c r="PC2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="PD2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -6542,6 +6552,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="PD3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8515,6 +8530,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="PD4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10612,6 +10632,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="PD5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12709,6 +12734,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="PD6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14806,6 +14836,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="PD7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -16903,6 +16938,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="PD8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19000,6 +19040,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="PD9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21097,6 +21142,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="PD10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -23194,6 +23244,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="PD11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -25291,6 +25346,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="PD12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -27388,6 +27448,11 @@
           <t>$7.99</t>
         </is>
       </c>
+      <c r="PD13" t="inlineStr">
+        <is>
+          <t>$7.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -29485,6 +29550,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="PD14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -31578,6 +31648,11 @@
         </is>
       </c>
       <c r="PC15" t="inlineStr">
+        <is>
+          <t>$3.49</t>
+        </is>
+      </c>
+      <c r="PD15" t="inlineStr">
         <is>
           <t>$3.49</t>
         </is>
@@ -33079,6 +33154,11 @@
           <t>$13.61</t>
         </is>
       </c>
+      <c r="PD16" t="inlineStr">
+        <is>
+          <t>$13.61</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -35176,6 +35256,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="PD17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -37273,6 +37358,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="PD18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -39370,6 +39460,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="PD19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -41467,6 +41562,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="PD20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -43564,6 +43664,11 @@
           <t>$1.27</t>
         </is>
       </c>
+      <c r="PD21" t="inlineStr">
+        <is>
+          <t>$1.27</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -45659,6 +45764,11 @@
       <c r="PC22" t="inlineStr">
         <is>
           <t>3.779</t>
+        </is>
+      </c>
+      <c r="PD22" t="inlineStr">
+        <is>
+          <t>3.749</t>
         </is>
       </c>
     </row>
@@ -47766,6 +47876,11 @@
         </is>
       </c>
       <c r="PC23" t="inlineStr">
+        <is>
+          <t>$3.98</t>
+        </is>
+      </c>
+      <c r="PD23" t="inlineStr">
         <is>
           <t>$3.98</t>
         </is>
@@ -49639,6 +49754,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="PD24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:PD24"/>
+  <dimension ref="A1:PE24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2517,6 +2517,11 @@
           <t>Price_2026-06-06 10:11</t>
         </is>
       </c>
+      <c r="PE1" t="inlineStr">
+        <is>
+          <t>Price_2026-06-07 10:37</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4615,6 +4620,11 @@
         </is>
       </c>
       <c r="PD2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="PE2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -6557,6 +6567,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="PE3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8535,6 +8550,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="PE4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10637,6 +10657,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="PE5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12739,6 +12764,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="PE6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14841,6 +14871,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="PE7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -16943,6 +16978,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="PE8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19045,6 +19085,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="PE9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21147,6 +21192,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="PE10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -23249,6 +23299,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="PE11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -25351,6 +25406,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="PE12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -27453,6 +27513,11 @@
           <t>$7.99</t>
         </is>
       </c>
+      <c r="PE13" t="inlineStr">
+        <is>
+          <t>$7.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -29555,6 +29620,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="PE14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -31653,6 +31723,11 @@
         </is>
       </c>
       <c r="PD15" t="inlineStr">
+        <is>
+          <t>$3.49</t>
+        </is>
+      </c>
+      <c r="PE15" t="inlineStr">
         <is>
           <t>$3.49</t>
         </is>
@@ -33159,6 +33234,11 @@
           <t>$13.61</t>
         </is>
       </c>
+      <c r="PE16" t="inlineStr">
+        <is>
+          <t>$13.61</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -35261,6 +35341,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="PE17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -37363,6 +37448,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="PE18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -39465,6 +39555,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="PE19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -41567,6 +41662,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="PE20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -43669,6 +43769,11 @@
           <t>$1.27</t>
         </is>
       </c>
+      <c r="PE21" t="inlineStr">
+        <is>
+          <t>$1.27</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -45769,6 +45874,11 @@
       <c r="PD22" t="inlineStr">
         <is>
           <t>3.749</t>
+        </is>
+      </c>
+      <c r="PE22" t="inlineStr">
+        <is>
+          <t>3.699</t>
         </is>
       </c>
     </row>
@@ -47881,6 +47991,11 @@
         </is>
       </c>
       <c r="PD23" t="inlineStr">
+        <is>
+          <t>$3.98</t>
+        </is>
+      </c>
+      <c r="PE23" t="inlineStr">
         <is>
           <t>$3.98</t>
         </is>
@@ -49759,6 +49874,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="PE24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:PE24"/>
+  <dimension ref="A1:PF24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2522,6 +2522,11 @@
           <t>Price_2026-06-07 10:37</t>
         </is>
       </c>
+      <c r="PF1" t="inlineStr">
+        <is>
+          <t>Price_2026-06-08 12:37</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4625,6 +4630,11 @@
         </is>
       </c>
       <c r="PE2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="PF2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -6572,6 +6582,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="PF3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8555,6 +8570,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="PF4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10662,6 +10682,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="PF5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12769,6 +12794,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="PF6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14876,6 +14906,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="PF7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -16983,6 +17018,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="PF8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19090,6 +19130,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="PF9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21197,6 +21242,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="PF10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -23304,6 +23354,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="PF11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -25411,6 +25466,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="PF12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -27518,6 +27578,11 @@
           <t>$7.99</t>
         </is>
       </c>
+      <c r="PF13" t="inlineStr">
+        <is>
+          <t>$7.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -29625,6 +29690,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="PF14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -31730,6 +31800,11 @@
       <c r="PE15" t="inlineStr">
         <is>
           <t>$3.49</t>
+        </is>
+      </c>
+      <c r="PF15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
         </is>
       </c>
     </row>
@@ -33239,6 +33314,11 @@
           <t>$13.61</t>
         </is>
       </c>
+      <c r="PF16" t="inlineStr">
+        <is>
+          <t>$13.61</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -35346,6 +35426,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="PF17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -37453,6 +37538,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="PF18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -39560,6 +39650,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="PF19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -41667,6 +41762,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="PF20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -43774,6 +43874,11 @@
           <t>$1.27</t>
         </is>
       </c>
+      <c r="PF21" t="inlineStr">
+        <is>
+          <t>$1.27</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -45877,6 +45982,11 @@
         </is>
       </c>
       <c r="PE22" t="inlineStr">
+        <is>
+          <t>3.699</t>
+        </is>
+      </c>
+      <c r="PF22" t="inlineStr">
         <is>
           <t>3.699</t>
         </is>
@@ -47996,6 +48106,11 @@
         </is>
       </c>
       <c r="PE23" t="inlineStr">
+        <is>
+          <t>$3.98</t>
+        </is>
+      </c>
+      <c r="PF23" t="inlineStr">
         <is>
           <t>$3.98</t>
         </is>
@@ -49879,6 +49994,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="PF24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:PF24"/>
+  <dimension ref="A1:PG24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2527,6 +2527,11 @@
           <t>Price_2026-06-08 12:37</t>
         </is>
       </c>
+      <c r="PG1" t="inlineStr">
+        <is>
+          <t>Price_2026-06-09 11:10</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4635,6 +4640,11 @@
         </is>
       </c>
       <c r="PF2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="PG2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -6587,6 +6597,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="PG3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8575,6 +8590,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="PG4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10687,6 +10707,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="PG5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12799,6 +12824,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="PG6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14911,6 +14941,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="PG7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17023,6 +17058,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="PG8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19135,6 +19175,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="PG9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21247,6 +21292,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="PG10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -23359,6 +23409,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="PG11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -25471,6 +25526,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="PG12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -27583,6 +27643,11 @@
           <t>$7.99</t>
         </is>
       </c>
+      <c r="PG13" t="inlineStr">
+        <is>
+          <t>$7.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -29695,6 +29760,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="PG14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -31803,6 +31873,11 @@
         </is>
       </c>
       <c r="PF15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="PG15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -33319,6 +33394,11 @@
           <t>$13.61</t>
         </is>
       </c>
+      <c r="PG16" t="inlineStr">
+        <is>
+          <t>$13.61</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -35431,6 +35511,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="PG17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -37543,6 +37628,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="PG18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -39655,6 +39745,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="PG19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -41767,6 +41862,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="PG20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -43879,6 +43979,11 @@
           <t>$1.27</t>
         </is>
       </c>
+      <c r="PG21" t="inlineStr">
+        <is>
+          <t>$1.27</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -45987,6 +46092,11 @@
         </is>
       </c>
       <c r="PF22" t="inlineStr">
+        <is>
+          <t>3.699</t>
+        </is>
+      </c>
+      <c r="PG22" t="inlineStr">
         <is>
           <t>3.699</t>
         </is>
@@ -48111,6 +48221,11 @@
         </is>
       </c>
       <c r="PF23" t="inlineStr">
+        <is>
+          <t>$3.98</t>
+        </is>
+      </c>
+      <c r="PG23" t="inlineStr">
         <is>
           <t>$3.98</t>
         </is>
@@ -49999,6 +50114,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="PG24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:PG24"/>
+  <dimension ref="A1:PH24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2532,6 +2532,11 @@
           <t>Price_2026-06-09 11:10</t>
         </is>
       </c>
+      <c r="PH1" t="inlineStr">
+        <is>
+          <t>Price_2026-06-10 11:47</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4645,6 +4650,11 @@
         </is>
       </c>
       <c r="PG2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="PH2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -6602,6 +6612,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="PH3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8595,6 +8610,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="PH4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10712,6 +10732,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="PH5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12829,6 +12854,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="PH6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14946,6 +14976,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="PH7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17063,6 +17098,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="PH8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19180,6 +19220,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="PH9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21297,6 +21342,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="PH10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -23414,6 +23464,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="PH11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -25531,6 +25586,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="PH12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -27648,6 +27708,11 @@
           <t>$7.99</t>
         </is>
       </c>
+      <c r="PH13" t="inlineStr">
+        <is>
+          <t>$7.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -29765,6 +29830,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="PH14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -31878,6 +31948,11 @@
         </is>
       </c>
       <c r="PG15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="PH15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -33399,6 +33474,11 @@
           <t>$13.61</t>
         </is>
       </c>
+      <c r="PH16" t="inlineStr">
+        <is>
+          <t>$13.61</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -35516,6 +35596,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="PH17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -37633,6 +37718,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="PH18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -39750,6 +39840,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="PH19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -41867,6 +41962,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="PH20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -43984,6 +44084,11 @@
           <t>$1.27</t>
         </is>
       </c>
+      <c r="PH21" t="inlineStr">
+        <is>
+          <t>$1.27</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -46099,6 +46204,11 @@
       <c r="PG22" t="inlineStr">
         <is>
           <t>3.699</t>
+        </is>
+      </c>
+      <c r="PH22" t="inlineStr">
+        <is>
+          <t>3.599</t>
         </is>
       </c>
     </row>
@@ -48226,6 +48336,11 @@
         </is>
       </c>
       <c r="PG23" t="inlineStr">
+        <is>
+          <t>$3.98</t>
+        </is>
+      </c>
+      <c r="PH23" t="inlineStr">
         <is>
           <t>$3.98</t>
         </is>
@@ -50119,6 +50234,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="PH24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:PH24"/>
+  <dimension ref="A1:PI24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2537,6 +2537,11 @@
           <t>Price_2026-06-10 11:47</t>
         </is>
       </c>
+      <c r="PI1" t="inlineStr">
+        <is>
+          <t>Price_2026-06-11 12:18</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4655,6 +4660,11 @@
         </is>
       </c>
       <c r="PH2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="PI2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -6617,6 +6627,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="PI3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8615,6 +8630,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="PI4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10737,6 +10757,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="PI5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12859,6 +12884,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="PI6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14981,6 +15011,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="PI7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17103,6 +17138,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="PI8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19225,6 +19265,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="PI9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21347,6 +21392,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="PI10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -23469,6 +23519,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="PI11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -25591,6 +25646,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="PI12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -27713,6 +27773,11 @@
           <t>$7.99</t>
         </is>
       </c>
+      <c r="PI13" t="inlineStr">
+        <is>
+          <t>$7.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -29835,6 +29900,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="PI14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -31953,6 +32023,11 @@
         </is>
       </c>
       <c r="PH15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="PI15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -33479,6 +33554,11 @@
           <t>$13.61</t>
         </is>
       </c>
+      <c r="PI16" t="inlineStr">
+        <is>
+          <t>$13.61</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -35601,6 +35681,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="PI17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -37723,6 +37808,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="PI18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -39845,6 +39935,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="PI19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -41967,6 +42062,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="PI20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -44089,6 +44189,11 @@
           <t>$1.27</t>
         </is>
       </c>
+      <c r="PI21" t="inlineStr">
+        <is>
+          <t>$1.27</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -46209,6 +46314,11 @@
       <c r="PH22" t="inlineStr">
         <is>
           <t>3.599</t>
+        </is>
+      </c>
+      <c r="PI22" t="inlineStr">
+        <is>
+          <t>3.579</t>
         </is>
       </c>
     </row>
@@ -48341,6 +48451,11 @@
         </is>
       </c>
       <c r="PH23" t="inlineStr">
+        <is>
+          <t>$3.98</t>
+        </is>
+      </c>
+      <c r="PI23" t="inlineStr">
         <is>
           <t>$3.98</t>
         </is>
@@ -50239,6 +50354,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="PI24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:PI24"/>
+  <dimension ref="A1:PJ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2542,6 +2542,11 @@
           <t>Price_2026-06-11 12:18</t>
         </is>
       </c>
+      <c r="PJ1" t="inlineStr">
+        <is>
+          <t>Price_2026-06-12 11:52</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4665,6 +4670,11 @@
         </is>
       </c>
       <c r="PI2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="PJ2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -6632,6 +6642,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="PJ3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8635,6 +8650,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="PJ4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10762,6 +10782,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="PJ5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12889,6 +12914,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="PJ6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15016,6 +15046,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="PJ7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17143,6 +17178,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="PJ8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19270,6 +19310,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="PJ9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21397,6 +21442,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="PJ10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -23524,6 +23574,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="PJ11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -25651,6 +25706,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="PJ12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -27778,6 +27838,11 @@
           <t>$7.99</t>
         </is>
       </c>
+      <c r="PJ13" t="inlineStr">
+        <is>
+          <t>$7.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -29905,6 +29970,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="PJ14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -32028,6 +32098,11 @@
         </is>
       </c>
       <c r="PI15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="PJ15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -33559,6 +33634,11 @@
           <t>$13.61</t>
         </is>
       </c>
+      <c r="PJ16" t="inlineStr">
+        <is>
+          <t>$13.61</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -35686,6 +35766,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="PJ17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -37813,6 +37898,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="PJ18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -39940,6 +40030,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="PJ19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -42067,6 +42162,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="PJ20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -44194,6 +44294,11 @@
           <t>$1.27</t>
         </is>
       </c>
+      <c r="PJ21" t="inlineStr">
+        <is>
+          <t>$1.27</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -46317,6 +46422,11 @@
         </is>
       </c>
       <c r="PI22" t="inlineStr">
+        <is>
+          <t>3.579</t>
+        </is>
+      </c>
+      <c r="PJ22" t="inlineStr">
         <is>
           <t>3.579</t>
         </is>
@@ -48456,6 +48566,11 @@
         </is>
       </c>
       <c r="PI23" t="inlineStr">
+        <is>
+          <t>$3.98</t>
+        </is>
+      </c>
+      <c r="PJ23" t="inlineStr">
         <is>
           <t>$3.98</t>
         </is>
@@ -50359,6 +50474,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="PJ24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:PJ24"/>
+  <dimension ref="A1:PK24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2547,6 +2547,11 @@
           <t>Price_2026-06-12 11:52</t>
         </is>
       </c>
+      <c r="PK1" t="inlineStr">
+        <is>
+          <t>Price_2026-06-13 10:36</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4675,6 +4680,11 @@
         </is>
       </c>
       <c r="PJ2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="PK2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -6647,6 +6657,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="PK3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8655,6 +8670,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="PK4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10787,6 +10807,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="PK5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12919,6 +12944,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="PK6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15051,6 +15081,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="PK7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17183,6 +17218,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="PK8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19315,6 +19355,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="PK9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21447,6 +21492,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="PK10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -23579,6 +23629,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="PK11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -25711,6 +25766,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="PK12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -27843,6 +27903,11 @@
           <t>$7.99</t>
         </is>
       </c>
+      <c r="PK13" t="inlineStr">
+        <is>
+          <t>$7.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -29975,6 +30040,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="PK14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -32103,6 +32173,11 @@
         </is>
       </c>
       <c r="PJ15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="PK15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -33639,6 +33714,11 @@
           <t>$13.61</t>
         </is>
       </c>
+      <c r="PK16" t="inlineStr">
+        <is>
+          <t>$13.61</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -35771,6 +35851,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="PK17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -37903,6 +37988,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="PK18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -40035,6 +40125,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="PK19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -42167,6 +42262,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="PK20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -44299,6 +44399,11 @@
           <t>$1.27</t>
         </is>
       </c>
+      <c r="PK21" t="inlineStr">
+        <is>
+          <t>$1.27</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -46427,6 +46532,11 @@
         </is>
       </c>
       <c r="PJ22" t="inlineStr">
+        <is>
+          <t>3.579</t>
+        </is>
+      </c>
+      <c r="PK22" t="inlineStr">
         <is>
           <t>3.579</t>
         </is>
@@ -48571,6 +48681,11 @@
         </is>
       </c>
       <c r="PJ23" t="inlineStr">
+        <is>
+          <t>$3.98</t>
+        </is>
+      </c>
+      <c r="PK23" t="inlineStr">
         <is>
           <t>$3.98</t>
         </is>
@@ -50479,6 +50594,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="PK24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:PK24"/>
+  <dimension ref="A1:PL24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2552,6 +2552,11 @@
           <t>Price_2026-06-13 10:36</t>
         </is>
       </c>
+      <c r="PL1" t="inlineStr">
+        <is>
+          <t>Price_2026-06-14 10:57</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4685,6 +4690,11 @@
         </is>
       </c>
       <c r="PK2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="PL2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -6662,6 +6672,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="PL3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8675,6 +8690,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="PL4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10812,6 +10832,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="PL5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12949,6 +12974,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="PL6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15086,6 +15116,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="PL7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17223,6 +17258,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="PL8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19360,6 +19400,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="PL9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21497,6 +21542,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="PL10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -23634,6 +23684,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="PL11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -25771,6 +25826,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="PL12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -27908,6 +27968,11 @@
           <t>$7.99</t>
         </is>
       </c>
+      <c r="PL13" t="inlineStr">
+        <is>
+          <t>$7.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -30045,6 +30110,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="PL14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -32178,6 +32248,11 @@
         </is>
       </c>
       <c r="PK15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="PL15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -33719,6 +33794,11 @@
           <t>$13.61</t>
         </is>
       </c>
+      <c r="PL16" t="inlineStr">
+        <is>
+          <t>$13.61</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -35856,6 +35936,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="PL17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -37993,6 +38078,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="PL18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -40130,6 +40220,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="PL19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -42267,6 +42362,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="PL20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -44404,6 +44504,11 @@
           <t>$1.27</t>
         </is>
       </c>
+      <c r="PL21" t="inlineStr">
+        <is>
+          <t>$1.27</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -46537,6 +46642,11 @@
         </is>
       </c>
       <c r="PK22" t="inlineStr">
+        <is>
+          <t>3.579</t>
+        </is>
+      </c>
+      <c r="PL22" t="inlineStr">
         <is>
           <t>3.579</t>
         </is>
@@ -48686,6 +48796,11 @@
         </is>
       </c>
       <c r="PK23" t="inlineStr">
+        <is>
+          <t>$3.98</t>
+        </is>
+      </c>
+      <c r="PL23" t="inlineStr">
         <is>
           <t>$3.98</t>
         </is>
@@ -50599,6 +50714,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="PL24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:PL24"/>
+  <dimension ref="A1:PM24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2557,6 +2557,11 @@
           <t>Price_2026-06-14 10:57</t>
         </is>
       </c>
+      <c r="PM1" t="inlineStr">
+        <is>
+          <t>Price_2026-06-15 14:03</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4695,6 +4700,11 @@
         </is>
       </c>
       <c r="PL2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="PM2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -6677,6 +6687,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="PM3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8695,6 +8710,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="PM4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10837,6 +10857,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="PM5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12979,6 +13004,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="PM6" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15121,6 +15151,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="PM7" t="inlineStr">
+        <is>
+          <t>$6.88</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17263,6 +17298,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="PM8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19405,6 +19445,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="PM9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21547,6 +21592,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="PM10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -23689,6 +23739,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="PM11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -25831,6 +25886,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="PM12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -27973,6 +28033,11 @@
           <t>$7.99</t>
         </is>
       </c>
+      <c r="PM13" t="inlineStr">
+        <is>
+          <t>$7.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -30115,6 +30180,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="PM14" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -32253,6 +32323,11 @@
         </is>
       </c>
       <c r="PL15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="PM15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -33799,6 +33874,11 @@
           <t>$13.61</t>
         </is>
       </c>
+      <c r="PM16" t="inlineStr">
+        <is>
+          <t>$13.61</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -35941,6 +36021,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="PM17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -38083,6 +38168,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="PM18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -40225,6 +40315,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="PM19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -42367,6 +42462,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="PM20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -44509,6 +44609,11 @@
           <t>$1.27</t>
         </is>
       </c>
+      <c r="PM21" t="inlineStr">
+        <is>
+          <t>$1.27</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -46647,6 +46752,11 @@
         </is>
       </c>
       <c r="PL22" t="inlineStr">
+        <is>
+          <t>3.579</t>
+        </is>
+      </c>
+      <c r="PM22" t="inlineStr">
         <is>
           <t>3.579</t>
         </is>
@@ -48801,6 +48911,11 @@
         </is>
       </c>
       <c r="PL23" t="inlineStr">
+        <is>
+          <t>$3.98</t>
+        </is>
+      </c>
+      <c r="PM23" t="inlineStr">
         <is>
           <t>$3.98</t>
         </is>
@@ -50719,6 +50834,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="PM24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:PM24"/>
+  <dimension ref="A1:PN24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2562,6 +2562,11 @@
           <t>Price_2026-06-15 14:03</t>
         </is>
       </c>
+      <c r="PN1" t="inlineStr">
+        <is>
+          <t>Price_2026-06-16 13:01</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4705,6 +4710,11 @@
         </is>
       </c>
       <c r="PM2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="PN2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -6692,6 +6702,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="PN3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8715,6 +8730,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="PN4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10862,6 +10882,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="PN5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13009,6 +13034,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="PN6" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15156,6 +15186,11 @@
           <t>$6.88</t>
         </is>
       </c>
+      <c r="PN7" t="inlineStr">
+        <is>
+          <t>$6.88</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17303,6 +17338,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="PN8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19450,6 +19490,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="PN9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21597,6 +21642,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="PN10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -23744,6 +23794,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="PN11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -25891,6 +25946,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="PN12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -28038,6 +28098,11 @@
           <t>$7.99</t>
         </is>
       </c>
+      <c r="PN13" t="inlineStr">
+        <is>
+          <t>$7.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -30185,6 +30250,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="PN14" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -32328,6 +32398,11 @@
         </is>
       </c>
       <c r="PM15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="PN15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -33879,6 +33954,11 @@
           <t>$13.61</t>
         </is>
       </c>
+      <c r="PN16" t="inlineStr">
+        <is>
+          <t>$13.61</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -36026,6 +36106,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="PN17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -38173,6 +38258,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="PN18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -40320,6 +40410,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="PN19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -42467,6 +42562,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="PN20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -44614,6 +44714,11 @@
           <t>$1.27</t>
         </is>
       </c>
+      <c r="PN21" t="inlineStr">
+        <is>
+          <t>$1.27</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -46757,6 +46862,11 @@
         </is>
       </c>
       <c r="PM22" t="inlineStr">
+        <is>
+          <t>3.579</t>
+        </is>
+      </c>
+      <c r="PN22" t="inlineStr">
         <is>
           <t>3.579</t>
         </is>
@@ -48916,6 +49026,11 @@
         </is>
       </c>
       <c r="PM23" t="inlineStr">
+        <is>
+          <t>$3.98</t>
+        </is>
+      </c>
+      <c r="PN23" t="inlineStr">
         <is>
           <t>$3.98</t>
         </is>
@@ -50839,6 +50954,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="PN24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:PN24"/>
+  <dimension ref="A1:PO24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2567,6 +2567,11 @@
           <t>Price_2026-06-16 13:01</t>
         </is>
       </c>
+      <c r="PO1" t="inlineStr">
+        <is>
+          <t>Price_2026-06-17 12:24</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4715,6 +4720,11 @@
         </is>
       </c>
       <c r="PN2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="PO2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -6707,6 +6717,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="PO3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8735,6 +8750,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="PO4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10887,6 +10907,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="PO5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13039,6 +13064,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="PO6" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15191,6 +15221,11 @@
           <t>$6.88</t>
         </is>
       </c>
+      <c r="PO7" t="inlineStr">
+        <is>
+          <t>$6.88</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17343,6 +17378,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="PO8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19495,6 +19535,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="PO9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21647,6 +21692,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="PO10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -23799,6 +23849,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="PO11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -25951,6 +26006,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="PO12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -28103,6 +28163,11 @@
           <t>$7.99</t>
         </is>
       </c>
+      <c r="PO13" t="inlineStr">
+        <is>
+          <t>$7.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -30255,6 +30320,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="PO14" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -32403,6 +32473,11 @@
         </is>
       </c>
       <c r="PN15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="PO15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -33959,6 +34034,11 @@
           <t>$13.61</t>
         </is>
       </c>
+      <c r="PO16" t="inlineStr">
+        <is>
+          <t>$13.61</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -36111,6 +36191,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="PO17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -38263,6 +38348,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="PO18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -40415,6 +40505,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="PO19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -42567,6 +42662,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="PO20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -44719,6 +44819,11 @@
           <t>$1.27</t>
         </is>
       </c>
+      <c r="PO21" t="inlineStr">
+        <is>
+          <t>$1.27</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -46869,6 +46974,11 @@
       <c r="PN22" t="inlineStr">
         <is>
           <t>3.579</t>
+        </is>
+      </c>
+      <c r="PO22" t="inlineStr">
+        <is>
+          <t>3.549</t>
         </is>
       </c>
     </row>
@@ -49033,6 +49143,11 @@
       <c r="PN23" t="inlineStr">
         <is>
           <t>$3.98</t>
+        </is>
+      </c>
+      <c r="PO23" t="inlineStr">
+        <is>
+          <t>Not found</t>
         </is>
       </c>
     </row>
@@ -50959,6 +51074,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="PO24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:PO24"/>
+  <dimension ref="A1:PP24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2572,6 +2572,11 @@
           <t>Price_2026-06-17 12:24</t>
         </is>
       </c>
+      <c r="PP1" t="inlineStr">
+        <is>
+          <t>Price_2026-06-18 11:59</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4725,6 +4730,11 @@
         </is>
       </c>
       <c r="PO2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="PP2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -6722,6 +6732,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="PP3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8755,6 +8770,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="PP4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10912,6 +10932,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="PP5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13069,6 +13094,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="PP6" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15226,6 +15256,11 @@
           <t>$6.88</t>
         </is>
       </c>
+      <c r="PP7" t="inlineStr">
+        <is>
+          <t>$6.88</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17383,6 +17418,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="PP8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19540,6 +19580,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="PP9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21697,6 +21742,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="PP10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -23854,6 +23904,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="PP11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -26011,6 +26066,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="PP12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -28168,6 +28228,11 @@
           <t>$7.99</t>
         </is>
       </c>
+      <c r="PP13" t="inlineStr">
+        <is>
+          <t>$7.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -30325,6 +30390,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="PP14" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -32478,6 +32548,11 @@
         </is>
       </c>
       <c r="PO15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="PP15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -34039,6 +34114,11 @@
           <t>$13.61</t>
         </is>
       </c>
+      <c r="PP16" t="inlineStr">
+        <is>
+          <t>$13.61</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -36196,6 +36276,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="PP17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -38353,6 +38438,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="PP18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -40510,6 +40600,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="PP19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -42667,6 +42762,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="PP20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -44824,6 +44924,11 @@
           <t>$1.27</t>
         </is>
       </c>
+      <c r="PP21" t="inlineStr">
+        <is>
+          <t>$1.27</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -46979,6 +47084,11 @@
       <c r="PO22" t="inlineStr">
         <is>
           <t>3.549</t>
+        </is>
+      </c>
+      <c r="PP22" t="inlineStr">
+        <is>
+          <t>3.529</t>
         </is>
       </c>
     </row>
@@ -49148,6 +49258,11 @@
       <c r="PO23" t="inlineStr">
         <is>
           <t>Not found</t>
+        </is>
+      </c>
+      <c r="PP23" t="inlineStr">
+        <is>
+          <t>$3.98</t>
         </is>
       </c>
     </row>
@@ -51079,6 +51194,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="PP24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:PP24"/>
+  <dimension ref="A1:PQ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2577,6 +2577,11 @@
           <t>Price_2026-06-18 11:59</t>
         </is>
       </c>
+      <c r="PQ1" t="inlineStr">
+        <is>
+          <t>Price_2026-06-19 12:14</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4735,6 +4740,11 @@
         </is>
       </c>
       <c r="PP2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="PQ2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -6737,6 +6747,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="PQ3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8775,6 +8790,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="PQ4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10937,6 +10957,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="PQ5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13099,6 +13124,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="PQ6" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15261,6 +15291,11 @@
           <t>$6.88</t>
         </is>
       </c>
+      <c r="PQ7" t="inlineStr">
+        <is>
+          <t>$6.88</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17423,6 +17458,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="PQ8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19585,6 +19625,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="PQ9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21747,6 +21792,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="PQ10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -23909,6 +23959,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="PQ11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -26071,6 +26126,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="PQ12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -28233,6 +28293,11 @@
           <t>$7.99</t>
         </is>
       </c>
+      <c r="PQ13" t="inlineStr">
+        <is>
+          <t>$7.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -30395,6 +30460,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="PQ14" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -32553,6 +32623,11 @@
         </is>
       </c>
       <c r="PP15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="PQ15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -34119,6 +34194,11 @@
           <t>$13.61</t>
         </is>
       </c>
+      <c r="PQ16" t="inlineStr">
+        <is>
+          <t>$13.61</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -36281,6 +36361,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="PQ17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -38443,6 +38528,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="PQ18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -40605,6 +40695,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="PQ19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -42767,6 +42862,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="PQ20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -44929,6 +45029,11 @@
           <t>$1.27</t>
         </is>
       </c>
+      <c r="PQ21" t="inlineStr">
+        <is>
+          <t>$1.27</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -47089,6 +47194,11 @@
       <c r="PP22" t="inlineStr">
         <is>
           <t>3.529</t>
+        </is>
+      </c>
+      <c r="PQ22" t="inlineStr">
+        <is>
+          <t>3.499</t>
         </is>
       </c>
     </row>
@@ -49263,6 +49373,11 @@
       <c r="PP23" t="inlineStr">
         <is>
           <t>$3.98</t>
+        </is>
+      </c>
+      <c r="PQ23" t="inlineStr">
+        <is>
+          <t>Not found</t>
         </is>
       </c>
     </row>
@@ -51199,6 +51314,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="PQ24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:PQ24"/>
+  <dimension ref="A1:PR24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2582,6 +2582,11 @@
           <t>Price_2026-06-19 12:14</t>
         </is>
       </c>
+      <c r="PR1" t="inlineStr">
+        <is>
+          <t>Price_2026-06-20 10:41</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4745,6 +4750,11 @@
         </is>
       </c>
       <c r="PQ2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="PR2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -6752,6 +6762,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="PR3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8795,6 +8810,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="PR4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10962,6 +10982,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="PR5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13129,6 +13154,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="PR6" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15296,6 +15326,11 @@
           <t>$6.88</t>
         </is>
       </c>
+      <c r="PR7" t="inlineStr">
+        <is>
+          <t>$6.88</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17463,6 +17498,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="PR8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19630,6 +19670,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="PR9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21797,6 +21842,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="PR10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -23964,6 +24014,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="PR11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -26131,6 +26186,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="PR12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -28298,6 +28358,11 @@
           <t>$7.99</t>
         </is>
       </c>
+      <c r="PR13" t="inlineStr">
+        <is>
+          <t>$7.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -30465,6 +30530,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="PR14" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -32628,6 +32698,11 @@
         </is>
       </c>
       <c r="PQ15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="PR15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -34199,6 +34274,11 @@
           <t>$13.61</t>
         </is>
       </c>
+      <c r="PR16" t="inlineStr">
+        <is>
+          <t>$13.61</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -36366,6 +36446,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="PR17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -38533,6 +38618,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="PR18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -40700,6 +40790,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="PR19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -42867,6 +42962,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="PR20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -45034,6 +45134,11 @@
           <t>$1.27</t>
         </is>
       </c>
+      <c r="PR21" t="inlineStr">
+        <is>
+          <t>$1.27</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -47199,6 +47304,11 @@
       <c r="PQ22" t="inlineStr">
         <is>
           <t>3.499</t>
+        </is>
+      </c>
+      <c r="PR22" t="inlineStr">
+        <is>
+          <t>3.479</t>
         </is>
       </c>
     </row>
@@ -49376,6 +49486,11 @@
         </is>
       </c>
       <c r="PQ23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="PR23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -51319,6 +51434,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="PR24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:PR24"/>
+  <dimension ref="A1:PS24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2587,6 +2587,11 @@
           <t>Price_2026-06-20 10:41</t>
         </is>
       </c>
+      <c r="PS1" t="inlineStr">
+        <is>
+          <t>Price_2026-06-21 11:24</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4757,6 +4762,11 @@
       <c r="PR2" t="inlineStr">
         <is>
           <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="PS2" t="inlineStr">
+        <is>
+          <t>Not found</t>
         </is>
       </c>
     </row>
@@ -6767,6 +6777,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="PS3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8815,6 +8830,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="PS4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10987,6 +11007,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="PS5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13159,6 +13184,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="PS6" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15331,6 +15361,11 @@
           <t>$6.88</t>
         </is>
       </c>
+      <c r="PS7" t="inlineStr">
+        <is>
+          <t>$6.88</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17503,6 +17538,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="PS8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19675,6 +19715,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="PS9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21847,6 +21892,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="PS10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -24019,6 +24069,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="PS11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -26191,6 +26246,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="PS12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -28363,6 +28423,11 @@
           <t>$7.99</t>
         </is>
       </c>
+      <c r="PS13" t="inlineStr">
+        <is>
+          <t>$7.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -30535,6 +30600,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="PS14" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -32703,6 +32773,11 @@
         </is>
       </c>
       <c r="PR15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="PS15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -34279,6 +34354,11 @@
           <t>$13.61</t>
         </is>
       </c>
+      <c r="PS16" t="inlineStr">
+        <is>
+          <t>$13.61</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -36451,6 +36531,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="PS17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -38623,6 +38708,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="PS18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -40795,6 +40885,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="PS19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -42967,6 +43062,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="PS20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -45139,6 +45239,11 @@
           <t>$1.27</t>
         </is>
       </c>
+      <c r="PS21" t="inlineStr">
+        <is>
+          <t>$1.27</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -47309,6 +47414,11 @@
       <c r="PR22" t="inlineStr">
         <is>
           <t>3.479</t>
+        </is>
+      </c>
+      <c r="PS22" t="inlineStr">
+        <is>
+          <t>3.449</t>
         </is>
       </c>
     </row>
@@ -49491,6 +49601,11 @@
         </is>
       </c>
       <c r="PR23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="PS23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -51439,6 +51554,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="PS24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:PS24"/>
+  <dimension ref="A1:PT24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2592,6 +2592,11 @@
           <t>Price_2026-06-21 11:24</t>
         </is>
       </c>
+      <c r="PT1" t="inlineStr">
+        <is>
+          <t>Price_2026-06-22 13:43</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4767,6 +4772,11 @@
       <c r="PS2" t="inlineStr">
         <is>
           <t>Not found</t>
+        </is>
+      </c>
+      <c r="PT2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
         </is>
       </c>
     </row>
@@ -6782,6 +6792,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="PT3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8835,6 +8850,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="PT4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11012,6 +11032,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="PT5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13189,6 +13214,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="PT6" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15366,6 +15396,11 @@
           <t>$6.88</t>
         </is>
       </c>
+      <c r="PT7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17543,6 +17578,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="PT8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19720,6 +19760,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="PT9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21897,6 +21942,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="PT10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -24074,6 +24124,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="PT11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -26251,6 +26306,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="PT12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -28428,6 +28488,11 @@
           <t>$7.99</t>
         </is>
       </c>
+      <c r="PT13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -30605,6 +30670,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="PT14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -32778,6 +32848,11 @@
         </is>
       </c>
       <c r="PS15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="PT15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -34359,6 +34434,11 @@
           <t>$13.61</t>
         </is>
       </c>
+      <c r="PT16" t="inlineStr">
+        <is>
+          <t>$13.61</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -36536,6 +36616,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="PT17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -38713,6 +38798,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="PT18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -40890,6 +40980,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="PT19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -43067,6 +43162,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="PT20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -45244,6 +45344,11 @@
           <t>$1.27</t>
         </is>
       </c>
+      <c r="PT21" t="inlineStr">
+        <is>
+          <t>$1.27</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -47417,6 +47522,11 @@
         </is>
       </c>
       <c r="PS22" t="inlineStr">
+        <is>
+          <t>3.449</t>
+        </is>
+      </c>
+      <c r="PT22" t="inlineStr">
         <is>
           <t>3.449</t>
         </is>
@@ -49608,6 +49718,11 @@
       <c r="PS23" t="inlineStr">
         <is>
           <t>Not found</t>
+        </is>
+      </c>
+      <c r="PT23" t="inlineStr">
+        <is>
+          <t>$3.98</t>
         </is>
       </c>
     </row>
@@ -51559,6 +51674,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="PT24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:PT24"/>
+  <dimension ref="A1:PU24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2597,6 +2597,11 @@
           <t>Price_2026-06-22 13:43</t>
         </is>
       </c>
+      <c r="PU1" t="inlineStr">
+        <is>
+          <t>Price_2026-06-23 11:23</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4775,6 +4780,11 @@
         </is>
       </c>
       <c r="PT2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="PU2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -6797,6 +6807,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="PU3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8855,6 +8870,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="PU4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11037,6 +11057,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="PU5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13219,6 +13244,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="PU6" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15401,6 +15431,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="PU7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17583,6 +17618,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="PU8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19765,6 +19805,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="PU9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21947,6 +21992,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="PU10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -24129,6 +24179,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="PU11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -26311,6 +26366,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="PU12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -28493,6 +28553,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="PU13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -30675,6 +30740,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="PU14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -32853,6 +32923,11 @@
         </is>
       </c>
       <c r="PT15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="PU15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -34439,6 +34514,11 @@
           <t>$13.61</t>
         </is>
       </c>
+      <c r="PU16" t="inlineStr">
+        <is>
+          <t>$15.49</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -36621,6 +36701,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="PU17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -38803,6 +38888,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="PU18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -40985,6 +41075,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="PU19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -43167,6 +43262,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="PU20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -45349,6 +45449,11 @@
           <t>$1.27</t>
         </is>
       </c>
+      <c r="PU21" t="inlineStr">
+        <is>
+          <t>$1.27</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -47529,6 +47634,11 @@
       <c r="PT22" t="inlineStr">
         <is>
           <t>3.449</t>
+        </is>
+      </c>
+      <c r="PU22" t="inlineStr">
+        <is>
+          <t>3.399</t>
         </is>
       </c>
     </row>
@@ -49721,6 +49831,11 @@
         </is>
       </c>
       <c r="PT23" t="inlineStr">
+        <is>
+          <t>$3.98</t>
+        </is>
+      </c>
+      <c r="PU23" t="inlineStr">
         <is>
           <t>$3.98</t>
         </is>
@@ -51679,6 +51794,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="PU24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:PU24"/>
+  <dimension ref="A1:PV24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2602,6 +2602,11 @@
           <t>Price_2026-06-23 11:23</t>
         </is>
       </c>
+      <c r="PV1" t="inlineStr">
+        <is>
+          <t>Price_2026-06-24 10:56</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4785,6 +4790,11 @@
         </is>
       </c>
       <c r="PU2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="PV2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -6812,6 +6822,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="PV3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8875,6 +8890,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="PV4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11062,6 +11082,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="PV5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13249,6 +13274,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="PV6" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15436,6 +15466,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="PV7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17623,6 +17658,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="PV8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19810,6 +19850,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="PV9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21997,6 +22042,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="PV10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -24184,6 +24234,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="PV11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -26371,6 +26426,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="PV12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -28558,6 +28618,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="PV13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -30745,6 +30810,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="PV14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -32928,6 +32998,11 @@
         </is>
       </c>
       <c r="PU15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="PV15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -34519,6 +34594,11 @@
           <t>$15.49</t>
         </is>
       </c>
+      <c r="PV16" t="inlineStr">
+        <is>
+          <t>$15.49</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -36706,6 +36786,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="PV17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -38893,6 +38978,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="PV18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -41080,6 +41170,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="PV19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -43267,6 +43362,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="PV20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -45454,6 +45554,11 @@
           <t>$1.27</t>
         </is>
       </c>
+      <c r="PV21" t="inlineStr">
+        <is>
+          <t>$1.27</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -47639,6 +47744,11 @@
       <c r="PU22" t="inlineStr">
         <is>
           <t>3.399</t>
+        </is>
+      </c>
+      <c r="PV22" t="inlineStr">
+        <is>
+          <t>3.499</t>
         </is>
       </c>
     </row>
@@ -49836,6 +49946,11 @@
         </is>
       </c>
       <c r="PU23" t="inlineStr">
+        <is>
+          <t>$3.98</t>
+        </is>
+      </c>
+      <c r="PV23" t="inlineStr">
         <is>
           <t>$3.98</t>
         </is>
@@ -51799,6 +51914,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="PV24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:PV24"/>
+  <dimension ref="A1:PW24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2607,6 +2607,11 @@
           <t>Price_2026-06-24 10:56</t>
         </is>
       </c>
+      <c r="PW1" t="inlineStr">
+        <is>
+          <t>Price_2026-06-25 10:49</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4795,6 +4800,11 @@
         </is>
       </c>
       <c r="PV2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="PW2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -6827,6 +6837,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="PW3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8895,6 +8910,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="PW4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11087,6 +11107,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="PW5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13279,6 +13304,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="PW6" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15471,6 +15501,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="PW7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17663,6 +17698,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="PW8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19855,6 +19895,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="PW9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22047,6 +22092,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="PW10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -24239,6 +24289,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="PW11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -26431,6 +26486,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="PW12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -28623,6 +28683,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="PW13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -30815,6 +30880,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="PW14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -33003,6 +33073,11 @@
         </is>
       </c>
       <c r="PV15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="PW15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -34599,6 +34674,11 @@
           <t>$15.49</t>
         </is>
       </c>
+      <c r="PW16" t="inlineStr">
+        <is>
+          <t>$15.49</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -36791,6 +36871,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="PW17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -38983,6 +39068,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="PW18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -41175,6 +41265,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="PW19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -43367,6 +43462,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="PW20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -45559,6 +45659,11 @@
           <t>$1.27</t>
         </is>
       </c>
+      <c r="PW21" t="inlineStr">
+        <is>
+          <t>$1.27</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -47747,6 +47852,11 @@
         </is>
       </c>
       <c r="PV22" t="inlineStr">
+        <is>
+          <t>3.499</t>
+        </is>
+      </c>
+      <c r="PW22" t="inlineStr">
         <is>
           <t>3.499</t>
         </is>
@@ -49951,6 +50061,11 @@
         </is>
       </c>
       <c r="PV23" t="inlineStr">
+        <is>
+          <t>$3.98</t>
+        </is>
+      </c>
+      <c r="PW23" t="inlineStr">
         <is>
           <t>$3.98</t>
         </is>
@@ -51919,6 +52034,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="PW24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:PW24"/>
+  <dimension ref="A1:PX24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2612,6 +2612,11 @@
           <t>Price_2026-06-25 10:49</t>
         </is>
       </c>
+      <c r="PX1" t="inlineStr">
+        <is>
+          <t>Price_2026-06-26 10:58</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4805,6 +4810,11 @@
         </is>
       </c>
       <c r="PW2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="PX2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -6842,6 +6852,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="PX3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8915,6 +8930,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="PX4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11112,6 +11132,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="PX5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13309,6 +13334,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="PX6" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15506,6 +15536,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="PX7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17703,6 +17738,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="PX8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19900,6 +19940,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="PX9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22097,6 +22142,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="PX10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -24294,6 +24344,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="PX11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -26491,6 +26546,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="PX12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -28688,6 +28748,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="PX13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -30885,6 +30950,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="PX14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -33078,6 +33148,11 @@
         </is>
       </c>
       <c r="PW15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="PX15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -34679,6 +34754,11 @@
           <t>$15.49</t>
         </is>
       </c>
+      <c r="PX16" t="inlineStr">
+        <is>
+          <t>$15.49</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -36876,6 +36956,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="PX17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -39073,6 +39158,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="PX18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -41270,6 +41360,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="PX19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -43467,6 +43562,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="PX20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -45664,6 +45764,11 @@
           <t>$1.27</t>
         </is>
       </c>
+      <c r="PX21" t="inlineStr">
+        <is>
+          <t>$1.27</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -47857,6 +47962,11 @@
         </is>
       </c>
       <c r="PW22" t="inlineStr">
+        <is>
+          <t>3.499</t>
+        </is>
+      </c>
+      <c r="PX22" t="inlineStr">
         <is>
           <t>3.499</t>
         </is>
@@ -50066,6 +50176,11 @@
         </is>
       </c>
       <c r="PW23" t="inlineStr">
+        <is>
+          <t>$3.98</t>
+        </is>
+      </c>
+      <c r="PX23" t="inlineStr">
         <is>
           <t>$3.98</t>
         </is>
@@ -52039,6 +52154,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="PX24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:PX24"/>
+  <dimension ref="A1:PY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2617,6 +2617,11 @@
           <t>Price_2026-06-26 10:58</t>
         </is>
       </c>
+      <c r="PY1" t="inlineStr">
+        <is>
+          <t>Price_2026-06-27 10:14</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4815,6 +4820,11 @@
         </is>
       </c>
       <c r="PX2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="PY2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -6857,6 +6867,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="PY3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8935,6 +8950,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="PY4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11137,6 +11157,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="PY5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13339,6 +13364,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="PY6" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15541,6 +15571,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="PY7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17743,6 +17778,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="PY8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19945,6 +19985,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="PY9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22147,6 +22192,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="PY10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -24349,6 +24399,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="PY11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -26551,6 +26606,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="PY12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -28753,6 +28813,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="PY13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -30955,6 +31020,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="PY14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -33153,6 +33223,11 @@
         </is>
       </c>
       <c r="PX15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="PY15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -34759,6 +34834,11 @@
           <t>$15.49</t>
         </is>
       </c>
+      <c r="PY16" t="inlineStr">
+        <is>
+          <t>$15.49</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -36961,6 +37041,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="PY17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -39163,6 +39248,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="PY18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -41365,6 +41455,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="PY19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -43567,6 +43662,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="PY20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -45769,6 +45869,11 @@
           <t>$1.27</t>
         </is>
       </c>
+      <c r="PY21" t="inlineStr">
+        <is>
+          <t>$1.27</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -47969,6 +48074,11 @@
       <c r="PX22" t="inlineStr">
         <is>
           <t>3.499</t>
+        </is>
+      </c>
+      <c r="PY22" t="inlineStr">
+        <is>
+          <t>3.449</t>
         </is>
       </c>
     </row>
@@ -50181,6 +50291,11 @@
         </is>
       </c>
       <c r="PX23" t="inlineStr">
+        <is>
+          <t>$3.98</t>
+        </is>
+      </c>
+      <c r="PY23" t="inlineStr">
         <is>
           <t>$3.98</t>
         </is>
@@ -52159,6 +52274,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="PY24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:PY24"/>
+  <dimension ref="A1:PZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2622,6 +2622,11 @@
           <t>Price_2026-06-27 10:14</t>
         </is>
       </c>
+      <c r="PZ1" t="inlineStr">
+        <is>
+          <t>Price_2026-06-28 10:35</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4825,6 +4830,11 @@
         </is>
       </c>
       <c r="PY2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="PZ2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -6872,6 +6882,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="PZ3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8955,6 +8970,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="PZ4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11162,6 +11182,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="PZ5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13369,6 +13394,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="PZ6" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15576,6 +15606,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="PZ7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17783,6 +17818,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="PZ8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19990,6 +20030,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="PZ9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22197,6 +22242,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="PZ10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -24404,6 +24454,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="PZ11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -26611,6 +26666,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="PZ12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -28818,6 +28878,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="PZ13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -31025,6 +31090,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="PZ14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -33228,6 +33298,11 @@
         </is>
       </c>
       <c r="PY15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="PZ15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -34839,6 +34914,11 @@
           <t>$15.49</t>
         </is>
       </c>
+      <c r="PZ16" t="inlineStr">
+        <is>
+          <t>$15.49</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -37046,6 +37126,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="PZ17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -39253,6 +39338,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="PZ18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -41460,6 +41550,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="PZ19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -43667,6 +43762,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="PZ20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -45874,6 +45974,11 @@
           <t>$1.27</t>
         </is>
       </c>
+      <c r="PZ21" t="inlineStr">
+        <is>
+          <t>$1.27</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -48077,6 +48182,11 @@
         </is>
       </c>
       <c r="PY22" t="inlineStr">
+        <is>
+          <t>3.449</t>
+        </is>
+      </c>
+      <c r="PZ22" t="inlineStr">
         <is>
           <t>3.449</t>
         </is>
@@ -50296,6 +50406,11 @@
         </is>
       </c>
       <c r="PY23" t="inlineStr">
+        <is>
+          <t>$3.98</t>
+        </is>
+      </c>
+      <c r="PZ23" t="inlineStr">
         <is>
           <t>$3.98</t>
         </is>
@@ -52279,6 +52394,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="PZ24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:PZ24"/>
+  <dimension ref="A1:QA24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2627,6 +2627,11 @@
           <t>Price_2026-06-28 10:35</t>
         </is>
       </c>
+      <c r="QA1" t="inlineStr">
+        <is>
+          <t>Price_2026-06-29 12:39</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4835,6 +4840,11 @@
         </is>
       </c>
       <c r="PZ2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="QA2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -6887,6 +6897,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="QA3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8975,6 +8990,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="QA4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11187,6 +11207,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="QA5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13399,6 +13424,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="QA6" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15611,6 +15641,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="QA7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17823,6 +17858,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="QA8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20035,6 +20075,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="QA9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22247,6 +22292,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="QA10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -24459,6 +24509,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="QA11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -26671,6 +26726,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="QA12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -28883,6 +28943,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="QA13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -31095,6 +31160,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="QA14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -33303,6 +33373,11 @@
         </is>
       </c>
       <c r="PZ15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="QA15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -34919,6 +34994,11 @@
           <t>$15.49</t>
         </is>
       </c>
+      <c r="QA16" t="inlineStr">
+        <is>
+          <t>$15.49</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -37131,6 +37211,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="QA17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -39343,6 +39428,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="QA18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -41555,6 +41645,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="QA19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -43767,6 +43862,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="QA20" t="inlineStr">
+        <is>
+          <t>$4.48</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -45979,6 +46079,11 @@
           <t>$1.27</t>
         </is>
       </c>
+      <c r="QA21" t="inlineStr">
+        <is>
+          <t>$1.27</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -48189,6 +48294,11 @@
       <c r="PZ22" t="inlineStr">
         <is>
           <t>3.449</t>
+        </is>
+      </c>
+      <c r="QA22" t="inlineStr">
+        <is>
+          <t>3.399</t>
         </is>
       </c>
     </row>
@@ -50411,6 +50521,11 @@
         </is>
       </c>
       <c r="PZ23" t="inlineStr">
+        <is>
+          <t>$3.98</t>
+        </is>
+      </c>
+      <c r="QA23" t="inlineStr">
         <is>
           <t>$3.98</t>
         </is>
@@ -52399,6 +52514,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="QA24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:QA24"/>
+  <dimension ref="A1:QB24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2632,6 +2632,11 @@
           <t>Price_2026-06-29 12:39</t>
         </is>
       </c>
+      <c r="QB1" t="inlineStr">
+        <is>
+          <t>Price_2026-06-30 11:05</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4845,6 +4850,11 @@
         </is>
       </c>
       <c r="QA2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="QB2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -6902,6 +6912,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="QB3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8995,6 +9010,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="QB4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11212,6 +11232,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="QB5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13429,6 +13454,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="QB6" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15646,6 +15676,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="QB7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17863,6 +17898,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="QB8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20080,6 +20120,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="QB9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22297,6 +22342,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="QB10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -24514,6 +24564,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="QB11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -26731,6 +26786,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="QB12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -28948,6 +29008,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="QB13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -31165,6 +31230,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="QB14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -33378,6 +33448,11 @@
         </is>
       </c>
       <c r="QA15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="QB15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -34999,6 +35074,11 @@
           <t>$15.49</t>
         </is>
       </c>
+      <c r="QB16" t="inlineStr">
+        <is>
+          <t>$15.49</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -37216,6 +37296,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="QB17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -39433,6 +39518,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="QB18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -41650,6 +41740,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="QB19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -43867,6 +43962,11 @@
           <t>$4.48</t>
         </is>
       </c>
+      <c r="QB20" t="inlineStr">
+        <is>
+          <t>$4.48</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -46084,6 +46184,11 @@
           <t>$1.27</t>
         </is>
       </c>
+      <c r="QB21" t="inlineStr">
+        <is>
+          <t>$1.27</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -48299,6 +48404,11 @@
       <c r="QA22" t="inlineStr">
         <is>
           <t>3.399</t>
+        </is>
+      </c>
+      <c r="QB22" t="inlineStr">
+        <is>
+          <t>Not found</t>
         </is>
       </c>
     </row>
@@ -50526,6 +50636,11 @@
         </is>
       </c>
       <c r="QA23" t="inlineStr">
+        <is>
+          <t>$3.98</t>
+        </is>
+      </c>
+      <c r="QB23" t="inlineStr">
         <is>
           <t>$3.98</t>
         </is>
@@ -52519,6 +52634,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="QB24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:QB24"/>
+  <dimension ref="A1:QC24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2637,6 +2637,11 @@
           <t>Price_2026-06-30 11:05</t>
         </is>
       </c>
+      <c r="QC1" t="inlineStr">
+        <is>
+          <t>Price_2026-07-01 11:31</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4855,6 +4860,11 @@
         </is>
       </c>
       <c r="QB2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="QC2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -6917,6 +6927,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="QC3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9015,6 +9030,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="QC4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11237,6 +11257,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="QC5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13459,6 +13484,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="QC6" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15681,6 +15711,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="QC7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17903,6 +17938,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="QC8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20125,6 +20165,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="QC9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22347,6 +22392,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="QC10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -24569,6 +24619,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="QC11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -26791,6 +26846,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="QC12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -29013,6 +29073,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="QC13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -31235,6 +31300,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="QC14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -33453,6 +33523,11 @@
         </is>
       </c>
       <c r="QB15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="QC15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -35079,6 +35154,11 @@
           <t>$15.49</t>
         </is>
       </c>
+      <c r="QC16" t="inlineStr">
+        <is>
+          <t>$15.49</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -37301,6 +37381,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="QC17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -39523,6 +39608,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="QC18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -41745,6 +41835,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="QC19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -43967,6 +44062,11 @@
           <t>$4.48</t>
         </is>
       </c>
+      <c r="QC20" t="inlineStr">
+        <is>
+          <t>$4.48</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -46189,6 +46289,11 @@
           <t>$1.27</t>
         </is>
       </c>
+      <c r="QC21" t="inlineStr">
+        <is>
+          <t>$1.27</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -48409,6 +48514,11 @@
       <c r="QB22" t="inlineStr">
         <is>
           <t>Not found</t>
+        </is>
+      </c>
+      <c r="QC22" t="inlineStr">
+        <is>
+          <t>3.599</t>
         </is>
       </c>
     </row>
@@ -50643,6 +50753,11 @@
       <c r="QB23" t="inlineStr">
         <is>
           <t>$3.98</t>
+        </is>
+      </c>
+      <c r="QC23" t="inlineStr">
+        <is>
+          <t>$3.54</t>
         </is>
       </c>
     </row>
@@ -52639,6 +52754,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="QC24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:QC24"/>
+  <dimension ref="A1:QD24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2642,6 +2642,11 @@
           <t>Price_2026-07-01 11:31</t>
         </is>
       </c>
+      <c r="QD1" t="inlineStr">
+        <is>
+          <t>Price_2026-07-02 10:45</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4865,6 +4870,11 @@
         </is>
       </c>
       <c r="QC2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="QD2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -6932,6 +6942,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="QD3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9035,6 +9050,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="QD4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11262,6 +11282,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="QD5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13489,6 +13514,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="QD6" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15716,6 +15746,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="QD7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17943,6 +17978,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="QD8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20170,6 +20210,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="QD9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22397,6 +22442,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="QD10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -24624,6 +24674,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="QD11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -26851,6 +26906,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="QD12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -29078,6 +29138,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="QD13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -31305,6 +31370,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="QD14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -33528,6 +33598,11 @@
         </is>
       </c>
       <c r="QC15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="QD15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -35159,6 +35234,11 @@
           <t>$15.49</t>
         </is>
       </c>
+      <c r="QD16" t="inlineStr">
+        <is>
+          <t>$15.49</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -37386,6 +37466,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="QD17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -39613,6 +39698,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="QD18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -41840,6 +41930,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="QD19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -44067,6 +44162,11 @@
           <t>$4.48</t>
         </is>
       </c>
+      <c r="QD20" t="inlineStr">
+        <is>
+          <t>$4.48</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -46294,6 +46394,11 @@
           <t>$1.27</t>
         </is>
       </c>
+      <c r="QD21" t="inlineStr">
+        <is>
+          <t>$1.27</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -48517,6 +48622,11 @@
         </is>
       </c>
       <c r="QC22" t="inlineStr">
+        <is>
+          <t>3.599</t>
+        </is>
+      </c>
+      <c r="QD22" t="inlineStr">
         <is>
           <t>3.599</t>
         </is>
@@ -50758,6 +50868,11 @@
       <c r="QC23" t="inlineStr">
         <is>
           <t>$3.54</t>
+        </is>
+      </c>
+      <c r="QD23" t="inlineStr">
+        <is>
+          <t>Not found</t>
         </is>
       </c>
     </row>
@@ -52759,6 +52874,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="QD24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:QD24"/>
+  <dimension ref="A1:QE24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2647,6 +2647,11 @@
           <t>Price_2026-07-02 10:45</t>
         </is>
       </c>
+      <c r="QE1" t="inlineStr">
+        <is>
+          <t>Price_2026-07-03 10:42</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4875,6 +4880,11 @@
         </is>
       </c>
       <c r="QD2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="QE2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -6947,6 +6957,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="QE3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9055,6 +9070,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="QE4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11287,6 +11307,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="QE5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13519,6 +13544,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="QE6" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15751,6 +15781,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="QE7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17983,6 +18018,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="QE8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20215,6 +20255,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="QE9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22447,6 +22492,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="QE10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -24679,6 +24729,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="QE11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -26911,6 +26966,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="QE12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -29143,6 +29203,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="QE13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -31375,6 +31440,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="QE14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -33603,6 +33673,11 @@
         </is>
       </c>
       <c r="QD15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="QE15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -35239,6 +35314,11 @@
           <t>$15.49</t>
         </is>
       </c>
+      <c r="QE16" t="inlineStr">
+        <is>
+          <t>$15.49</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -37471,6 +37551,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="QE17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -39703,6 +39788,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="QE18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -41935,6 +42025,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="QE19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -44167,6 +44262,11 @@
           <t>$4.48</t>
         </is>
       </c>
+      <c r="QE20" t="inlineStr">
+        <is>
+          <t>$4.48</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -46399,6 +46499,11 @@
           <t>$1.27</t>
         </is>
       </c>
+      <c r="QE21" t="inlineStr">
+        <is>
+          <t>$1.27</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -48627,6 +48732,11 @@
         </is>
       </c>
       <c r="QD22" t="inlineStr">
+        <is>
+          <t>3.599</t>
+        </is>
+      </c>
+      <c r="QE22" t="inlineStr">
         <is>
           <t>3.599</t>
         </is>
@@ -50871,6 +50981,11 @@
         </is>
       </c>
       <c r="QD23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="QE23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -52879,6 +52994,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="QE24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:QE24"/>
+  <dimension ref="A1:QF24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2652,6 +2652,11 @@
           <t>Price_2026-07-03 10:42</t>
         </is>
       </c>
+      <c r="QF1" t="inlineStr">
+        <is>
+          <t>Price_2026-07-04 10:16</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4885,6 +4890,11 @@
         </is>
       </c>
       <c r="QE2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="QF2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -6962,6 +6972,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="QF3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9075,6 +9090,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="QF4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11312,6 +11332,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="QF5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13549,6 +13574,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="QF6" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15786,6 +15816,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="QF7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -18023,6 +18058,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="QF8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20260,6 +20300,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="QF9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22497,6 +22542,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="QF10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -24734,6 +24784,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="QF11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -26971,6 +27026,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="QF12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -29208,6 +29268,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="QF13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -31445,6 +31510,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="QF14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -33678,6 +33748,11 @@
         </is>
       </c>
       <c r="QE15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="QF15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -35319,6 +35394,11 @@
           <t>$15.49</t>
         </is>
       </c>
+      <c r="QF16" t="inlineStr">
+        <is>
+          <t>$15.49</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -37556,6 +37636,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="QF17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -39793,6 +39878,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="QF18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -42030,6 +42120,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="QF19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -44267,6 +44362,11 @@
           <t>$4.48</t>
         </is>
       </c>
+      <c r="QF20" t="inlineStr">
+        <is>
+          <t>$4.48</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -46504,6 +46604,11 @@
           <t>$1.27</t>
         </is>
       </c>
+      <c r="QF21" t="inlineStr">
+        <is>
+          <t>$1.27</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -48737,6 +48842,11 @@
         </is>
       </c>
       <c r="QE22" t="inlineStr">
+        <is>
+          <t>3.599</t>
+        </is>
+      </c>
+      <c r="QF22" t="inlineStr">
         <is>
           <t>3.599</t>
         </is>
@@ -50986,6 +51096,11 @@
         </is>
       </c>
       <c r="QE23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="QF23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -52999,6 +53114,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="QF24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:QF24"/>
+  <dimension ref="A1:QG24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2657,6 +2657,11 @@
           <t>Price_2026-07-04 10:16</t>
         </is>
       </c>
+      <c r="QG1" t="inlineStr">
+        <is>
+          <t>Price_2026-07-05 10:20</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4895,6 +4900,11 @@
         </is>
       </c>
       <c r="QF2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="QG2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -6977,6 +6987,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="QG3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9095,6 +9110,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="QG4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11337,6 +11357,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="QG5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13579,6 +13604,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="QG6" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15821,6 +15851,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="QG7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -18063,6 +18098,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="QG8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20305,6 +20345,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="QG9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22547,6 +22592,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="QG10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -24789,6 +24839,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="QG11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -27031,6 +27086,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="QG12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -29273,6 +29333,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="QG13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -31515,6 +31580,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="QG14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -33753,6 +33823,11 @@
         </is>
       </c>
       <c r="QF15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="QG15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -35399,6 +35474,11 @@
           <t>$15.49</t>
         </is>
       </c>
+      <c r="QG16" t="inlineStr">
+        <is>
+          <t>$15.49</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -37641,6 +37721,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="QG17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -39883,6 +39968,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="QG18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -42125,6 +42215,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="QG19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -44367,6 +44462,11 @@
           <t>$4.48</t>
         </is>
       </c>
+      <c r="QG20" t="inlineStr">
+        <is>
+          <t>$4.48</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -46609,6 +46709,11 @@
           <t>$1.27</t>
         </is>
       </c>
+      <c r="QG21" t="inlineStr">
+        <is>
+          <t>$1.27</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -48849,6 +48954,11 @@
       <c r="QF22" t="inlineStr">
         <is>
           <t>3.599</t>
+        </is>
+      </c>
+      <c r="QG22" t="inlineStr">
+        <is>
+          <t>3.499</t>
         </is>
       </c>
     </row>
@@ -51101,6 +51211,11 @@
         </is>
       </c>
       <c r="QF23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="QG23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -53119,6 +53234,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="QG24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:QG24"/>
+  <dimension ref="A1:QH24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2662,6 +2662,11 @@
           <t>Price_2026-07-05 10:20</t>
         </is>
       </c>
+      <c r="QH1" t="inlineStr">
+        <is>
+          <t>Price_2026-07-06 12:12</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4905,6 +4910,11 @@
         </is>
       </c>
       <c r="QG2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="QH2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -6992,6 +7002,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="QH3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9115,6 +9130,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="QH4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11362,6 +11382,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="QH5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13609,6 +13634,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="QH6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15856,6 +15886,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="QH7" t="inlineStr">
+        <is>
+          <t>$8.49</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -18103,6 +18138,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="QH8" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20350,6 +20390,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="QH9" t="inlineStr">
+        <is>
+          <t>$1.96</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22597,6 +22642,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="QH10" t="inlineStr">
+        <is>
+          <t>$2.75</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -24844,6 +24894,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="QH11" t="inlineStr">
+        <is>
+          <t>$3.37</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -27091,6 +27146,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="QH12" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -29338,6 +29398,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="QH13" t="inlineStr">
+        <is>
+          <t>$7.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -31585,6 +31650,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="QH14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -33830,6 +33900,11 @@
       <c r="QG15" t="inlineStr">
         <is>
           <t>$3.99</t>
+        </is>
+      </c>
+      <c r="QH15" t="inlineStr">
+        <is>
+          <t>$4.49</t>
         </is>
       </c>
     </row>
@@ -35479,6 +35554,11 @@
           <t>$15.49</t>
         </is>
       </c>
+      <c r="QH16" t="inlineStr">
+        <is>
+          <t>$12.99</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -37726,6 +37806,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="QH17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -39973,6 +40058,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="QH18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -42220,6 +42310,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="QH19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -44467,6 +44562,11 @@
           <t>$4.48</t>
         </is>
       </c>
+      <c r="QH20" t="inlineStr">
+        <is>
+          <t>$4.48</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -46714,6 +46814,11 @@
           <t>$1.27</t>
         </is>
       </c>
+      <c r="QH21" t="inlineStr">
+        <is>
+          <t>$1.27</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -48957,6 +49062,11 @@
         </is>
       </c>
       <c r="QG22" t="inlineStr">
+        <is>
+          <t>3.499</t>
+        </is>
+      </c>
+      <c r="QH22" t="inlineStr">
         <is>
           <t>3.499</t>
         </is>
@@ -51216,6 +51326,11 @@
         </is>
       </c>
       <c r="QG23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="QH23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -53239,6 +53354,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="QH24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:QH24"/>
+  <dimension ref="A1:QI24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2667,6 +2667,11 @@
           <t>Price_2026-07-06 12:12</t>
         </is>
       </c>
+      <c r="QI1" t="inlineStr">
+        <is>
+          <t>Price_2026-07-07 11:03</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4915,6 +4920,11 @@
         </is>
       </c>
       <c r="QH2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="QI2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7007,6 +7017,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="QI3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9135,6 +9150,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="QI4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11387,6 +11407,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="QI5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13639,6 +13664,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="QI6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15891,6 +15921,11 @@
           <t>$8.49</t>
         </is>
       </c>
+      <c r="QI7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -18143,6 +18178,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="QI8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20395,6 +20435,11 @@
           <t>$1.96</t>
         </is>
       </c>
+      <c r="QI9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22647,6 +22692,11 @@
           <t>$2.75</t>
         </is>
       </c>
+      <c r="QI10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -24899,6 +24949,11 @@
           <t>$3.37</t>
         </is>
       </c>
+      <c r="QI11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -27151,6 +27206,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="QI12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -29403,6 +29463,11 @@
           <t>$7.99</t>
         </is>
       </c>
+      <c r="QI13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -31655,6 +31720,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="QI14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -33905,6 +33975,11 @@
       <c r="QH15" t="inlineStr">
         <is>
           <t>$4.49</t>
+        </is>
+      </c>
+      <c r="QI15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
         </is>
       </c>
     </row>
@@ -35559,6 +35634,11 @@
           <t>$12.99</t>
         </is>
       </c>
+      <c r="QI16" t="inlineStr">
+        <is>
+          <t>$12.99</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -37811,6 +37891,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="QI17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -40063,6 +40148,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="QI18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -42315,6 +42405,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="QI19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -44567,6 +44662,11 @@
           <t>$4.48</t>
         </is>
       </c>
+      <c r="QI20" t="inlineStr">
+        <is>
+          <t>$4.88</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -46819,6 +46919,11 @@
           <t>$1.27</t>
         </is>
       </c>
+      <c r="QI21" t="inlineStr">
+        <is>
+          <t>$1.27</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -49067,6 +49172,11 @@
         </is>
       </c>
       <c r="QH22" t="inlineStr">
+        <is>
+          <t>3.499</t>
+        </is>
+      </c>
+      <c r="QI22" t="inlineStr">
         <is>
           <t>3.499</t>
         </is>
@@ -51331,6 +51441,11 @@
         </is>
       </c>
       <c r="QH23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="QI23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -53359,6 +53474,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="QI24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:QI24"/>
+  <dimension ref="A1:QJ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2672,6 +2672,11 @@
           <t>Price_2026-07-07 11:03</t>
         </is>
       </c>
+      <c r="QJ1" t="inlineStr">
+        <is>
+          <t>Price_2026-07-08 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4925,6 +4930,11 @@
         </is>
       </c>
       <c r="QI2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="QJ2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7022,6 +7032,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="QJ3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9155,6 +9170,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="QJ4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11412,6 +11432,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="QJ5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13669,6 +13694,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="QJ6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15926,6 +15956,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="QJ7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -18183,6 +18218,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="QJ8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20440,6 +20480,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="QJ9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22697,6 +22742,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="QJ10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -24954,6 +25004,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="QJ11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -27211,6 +27266,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="QJ12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -29468,6 +29528,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="QJ13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -31725,6 +31790,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="QJ14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -33978,6 +34048,11 @@
         </is>
       </c>
       <c r="QI15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="QJ15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -35639,6 +35714,11 @@
           <t>$12.99</t>
         </is>
       </c>
+      <c r="QJ16" t="inlineStr">
+        <is>
+          <t>$12.99</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -37896,6 +37976,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="QJ17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -40153,6 +40238,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="QJ18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -42410,6 +42500,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="QJ19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -44667,6 +44762,11 @@
           <t>$4.88</t>
         </is>
       </c>
+      <c r="QJ20" t="inlineStr">
+        <is>
+          <t>$4.88</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -46924,6 +47024,11 @@
           <t>$1.27</t>
         </is>
       </c>
+      <c r="QJ21" t="inlineStr">
+        <is>
+          <t>$1.27</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -49177,6 +49282,11 @@
         </is>
       </c>
       <c r="QI22" t="inlineStr">
+        <is>
+          <t>3.499</t>
+        </is>
+      </c>
+      <c r="QJ22" t="inlineStr">
         <is>
           <t>3.499</t>
         </is>
@@ -51446,6 +51556,11 @@
         </is>
       </c>
       <c r="QI23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="QJ23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -53479,6 +53594,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="QJ24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:QJ24"/>
+  <dimension ref="A1:QK24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2677,6 +2677,11 @@
           <t>Price_2026-07-08 10:23</t>
         </is>
       </c>
+      <c r="QK1" t="inlineStr">
+        <is>
+          <t>Price_2026-07-09 11:02</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4935,6 +4940,11 @@
         </is>
       </c>
       <c r="QJ2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="QK2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7037,6 +7047,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="QK3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9175,6 +9190,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="QK4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11437,6 +11457,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="QK5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13699,6 +13724,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="QK6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15961,6 +15991,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="QK7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -18223,6 +18258,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="QK8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20485,6 +20525,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="QK9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22747,6 +22792,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="QK10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -25009,6 +25059,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="QK11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -27271,6 +27326,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="QK12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -29533,6 +29593,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="QK13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -31795,6 +31860,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="QK14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -34053,6 +34123,11 @@
         </is>
       </c>
       <c r="QJ15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="QK15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -35719,6 +35794,11 @@
           <t>$12.99</t>
         </is>
       </c>
+      <c r="QK16" t="inlineStr">
+        <is>
+          <t>$12.99</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -37981,6 +38061,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="QK17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -40243,6 +40328,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="QK18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -42505,6 +42595,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="QK19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -44767,6 +44862,11 @@
           <t>$4.88</t>
         </is>
       </c>
+      <c r="QK20" t="inlineStr">
+        <is>
+          <t>$4.88</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -47029,6 +47129,11 @@
           <t>$1.27</t>
         </is>
       </c>
+      <c r="QK21" t="inlineStr">
+        <is>
+          <t>$1.27</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -49289,6 +49394,11 @@
       <c r="QJ22" t="inlineStr">
         <is>
           <t>3.499</t>
+        </is>
+      </c>
+      <c r="QK22" t="inlineStr">
+        <is>
+          <t>3.899</t>
         </is>
       </c>
     </row>
@@ -51561,6 +51671,11 @@
         </is>
       </c>
       <c r="QJ23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="QK23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -53599,6 +53714,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="QK24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:QK24"/>
+  <dimension ref="A1:QL24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2682,6 +2682,11 @@
           <t>Price_2026-07-09 11:02</t>
         </is>
       </c>
+      <c r="QL1" t="inlineStr">
+        <is>
+          <t>Price_2026-07-10 11:00</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4945,6 +4950,11 @@
         </is>
       </c>
       <c r="QK2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="QL2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7052,6 +7062,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="QL3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9195,6 +9210,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="QL4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11462,6 +11482,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="QL5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13729,6 +13754,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="QL6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15996,6 +16026,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="QL7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -18263,6 +18298,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="QL8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20530,6 +20570,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="QL9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22797,6 +22842,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="QL10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -25064,6 +25114,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="QL11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -27331,6 +27386,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="QL12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -29598,6 +29658,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="QL13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -31865,6 +31930,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="QL14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -34128,6 +34198,11 @@
         </is>
       </c>
       <c r="QK15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="QL15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -35799,6 +35874,11 @@
           <t>$12.99</t>
         </is>
       </c>
+      <c r="QL16" t="inlineStr">
+        <is>
+          <t>$12.99</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -38066,6 +38146,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="QL17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -40333,6 +40418,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="QL18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -42600,6 +42690,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="QL19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -44867,6 +44962,11 @@
           <t>$4.88</t>
         </is>
       </c>
+      <c r="QL20" t="inlineStr">
+        <is>
+          <t>$4.88</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -47134,6 +47234,11 @@
           <t>$1.27</t>
         </is>
       </c>
+      <c r="QL21" t="inlineStr">
+        <is>
+          <t>$1.27</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -49397,6 +49502,11 @@
         </is>
       </c>
       <c r="QK22" t="inlineStr">
+        <is>
+          <t>3.899</t>
+        </is>
+      </c>
+      <c r="QL22" t="inlineStr">
         <is>
           <t>3.899</t>
         </is>
@@ -51676,6 +51786,11 @@
         </is>
       </c>
       <c r="QK23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="QL23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -53719,6 +53834,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="QL24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:QL24"/>
+  <dimension ref="A1:QM24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2687,6 +2687,11 @@
           <t>Price_2026-07-10 11:00</t>
         </is>
       </c>
+      <c r="QM1" t="inlineStr">
+        <is>
+          <t>Price_2026-07-11 09:35</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4955,6 +4960,11 @@
         </is>
       </c>
       <c r="QL2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="QM2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7067,6 +7077,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="QM3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9215,6 +9230,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="QM4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11487,6 +11507,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="QM5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13759,6 +13784,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="QM6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16031,6 +16061,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="QM7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -18303,6 +18338,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="QM8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20575,6 +20615,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="QM9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22847,6 +22892,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="QM10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -25119,6 +25169,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="QM11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -27391,6 +27446,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="QM12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -29663,6 +29723,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="QM13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -31935,6 +32000,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="QM14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -34203,6 +34273,11 @@
         </is>
       </c>
       <c r="QL15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="QM15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -35879,6 +35954,11 @@
           <t>$12.99</t>
         </is>
       </c>
+      <c r="QM16" t="inlineStr">
+        <is>
+          <t>$12.99</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -38151,6 +38231,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="QM17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -40423,6 +40508,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="QM18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -42695,6 +42785,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="QM19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -44967,6 +45062,11 @@
           <t>$4.88</t>
         </is>
       </c>
+      <c r="QM20" t="inlineStr">
+        <is>
+          <t>$4.88</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -47239,6 +47339,11 @@
           <t>$1.27</t>
         </is>
       </c>
+      <c r="QM21" t="inlineStr">
+        <is>
+          <t>$1.27</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -49507,6 +49612,11 @@
         </is>
       </c>
       <c r="QL22" t="inlineStr">
+        <is>
+          <t>3.899</t>
+        </is>
+      </c>
+      <c r="QM22" t="inlineStr">
         <is>
           <t>3.899</t>
         </is>
@@ -51791,6 +51901,11 @@
         </is>
       </c>
       <c r="QL23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="QM23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -53839,6 +53954,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="QM24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:QM24"/>
+  <dimension ref="A1:QN24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2692,6 +2692,11 @@
           <t>Price_2026-07-11 09:35</t>
         </is>
       </c>
+      <c r="QN1" t="inlineStr">
+        <is>
+          <t>Price_2026-07-12 09:58</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4965,6 +4970,11 @@
         </is>
       </c>
       <c r="QM2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="QN2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7082,6 +7092,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="QN3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9235,6 +9250,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="QN4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11512,6 +11532,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="QN5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13789,6 +13814,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="QN6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16066,6 +16096,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="QN7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -18343,6 +18378,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="QN8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20620,6 +20660,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="QN9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22897,6 +22942,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="QN10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -25174,6 +25224,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="QN11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -27451,6 +27506,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="QN12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -29728,6 +29788,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="QN13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -32005,6 +32070,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="QN14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -34278,6 +34348,11 @@
         </is>
       </c>
       <c r="QM15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="QN15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -35959,6 +36034,11 @@
           <t>$12.99</t>
         </is>
       </c>
+      <c r="QN16" t="inlineStr">
+        <is>
+          <t>$12.99</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -38236,6 +38316,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="QN17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -40513,6 +40598,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="QN18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -42790,6 +42880,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="QN19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -45067,6 +45162,11 @@
           <t>$4.88</t>
         </is>
       </c>
+      <c r="QN20" t="inlineStr">
+        <is>
+          <t>$4.88</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -47344,6 +47444,11 @@
           <t>$1.27</t>
         </is>
       </c>
+      <c r="QN21" t="inlineStr">
+        <is>
+          <t>$1.27</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -49619,6 +49724,11 @@
       <c r="QM22" t="inlineStr">
         <is>
           <t>3.899</t>
+        </is>
+      </c>
+      <c r="QN22" t="inlineStr">
+        <is>
+          <t>3.799</t>
         </is>
       </c>
     </row>
@@ -51906,6 +52016,11 @@
         </is>
       </c>
       <c r="QM23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="QN23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -53959,6 +54074,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="QN24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:QN24"/>
+  <dimension ref="A1:QO24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2697,6 +2697,11 @@
           <t>Price_2026-07-12 09:58</t>
         </is>
       </c>
+      <c r="QO1" t="inlineStr">
+        <is>
+          <t>Price_2026-07-13 11:08</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4975,6 +4980,11 @@
         </is>
       </c>
       <c r="QN2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="QO2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7097,6 +7107,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="QO3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9255,6 +9270,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="QO4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11537,6 +11557,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="QO5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13819,6 +13844,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="QO6" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16101,6 +16131,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="QO7" t="inlineStr">
+        <is>
+          <t>$6.68</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -18383,6 +18418,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="QO8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20665,6 +20705,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="QO9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22947,6 +22992,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="QO10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -25229,6 +25279,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="QO11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -27511,6 +27566,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="QO12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -29793,6 +29853,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="QO13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -32075,6 +32140,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="QO14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -34353,6 +34423,11 @@
         </is>
       </c>
       <c r="QN15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="QO15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -36039,6 +36114,11 @@
           <t>$12.99</t>
         </is>
       </c>
+      <c r="QO16" t="inlineStr">
+        <is>
+          <t>$12.99</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -38321,6 +38401,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="QO17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -40603,6 +40688,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="QO18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -42885,6 +42975,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="QO19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -45167,6 +45262,11 @@
           <t>$4.88</t>
         </is>
       </c>
+      <c r="QO20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -47449,6 +47549,11 @@
           <t>$1.27</t>
         </is>
       </c>
+      <c r="QO21" t="inlineStr">
+        <is>
+          <t>$1.27</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -49727,6 +49832,11 @@
         </is>
       </c>
       <c r="QN22" t="inlineStr">
+        <is>
+          <t>3.799</t>
+        </is>
+      </c>
+      <c r="QO22" t="inlineStr">
         <is>
           <t>3.799</t>
         </is>
@@ -52021,6 +52131,11 @@
         </is>
       </c>
       <c r="QN23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="QO23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -54079,6 +54194,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="QO24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:QO24"/>
+  <dimension ref="A1:QP24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2702,6 +2702,11 @@
           <t>Price_2026-07-13 11:08</t>
         </is>
       </c>
+      <c r="QP1" t="inlineStr">
+        <is>
+          <t>Price_2026-07-14 10:05</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4985,6 +4990,11 @@
         </is>
       </c>
       <c r="QO2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="QP2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7112,6 +7122,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="QP3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9275,6 +9290,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="QP4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11562,6 +11582,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="QP5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13849,6 +13874,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="QP6" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16136,6 +16166,11 @@
           <t>$6.68</t>
         </is>
       </c>
+      <c r="QP7" t="inlineStr">
+        <is>
+          <t>$6.68</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -18423,6 +18458,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="QP8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20710,6 +20750,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="QP9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22997,6 +23042,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="QP10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -25284,6 +25334,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="QP11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -27571,6 +27626,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="QP12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -29858,6 +29918,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="QP13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -32145,6 +32210,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="QP14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -34428,6 +34498,11 @@
         </is>
       </c>
       <c r="QO15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="QP15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -36119,6 +36194,11 @@
           <t>$12.99</t>
         </is>
       </c>
+      <c r="QP16" t="inlineStr">
+        <is>
+          <t>$12.99</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -38406,6 +38486,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="QP17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -40693,6 +40778,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="QP18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -42980,6 +43070,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="QP19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -45267,6 +45362,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="QP20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -47554,6 +47654,11 @@
           <t>$1.27</t>
         </is>
       </c>
+      <c r="QP21" t="inlineStr">
+        <is>
+          <t>$1.27</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -49839,6 +49944,11 @@
       <c r="QO22" t="inlineStr">
         <is>
           <t>3.799</t>
+        </is>
+      </c>
+      <c r="QP22" t="inlineStr">
+        <is>
+          <t>3.749</t>
         </is>
       </c>
     </row>
@@ -52136,6 +52246,11 @@
         </is>
       </c>
       <c r="QO23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="QP23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -54199,6 +54314,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="QP24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:QP24"/>
+  <dimension ref="A1:QQ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2707,6 +2707,11 @@
           <t>Price_2026-07-14 10:05</t>
         </is>
       </c>
+      <c r="QQ1" t="inlineStr">
+        <is>
+          <t>Price_2026-07-15 10:09</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4995,6 +5000,11 @@
         </is>
       </c>
       <c r="QP2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="QQ2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7127,6 +7137,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="QQ3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9295,6 +9310,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="QQ4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11587,6 +11607,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="QQ5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13879,6 +13904,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="QQ6" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16171,6 +16201,11 @@
           <t>$6.68</t>
         </is>
       </c>
+      <c r="QQ7" t="inlineStr">
+        <is>
+          <t>$6.68</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -18463,6 +18498,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="QQ8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20755,6 +20795,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="QQ9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -23047,6 +23092,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="QQ10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -25339,6 +25389,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="QQ11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -27631,6 +27686,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="QQ12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -29923,6 +29983,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="QQ13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -32215,6 +32280,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="QQ14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -34503,6 +34573,11 @@
         </is>
       </c>
       <c r="QP15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="QQ15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -36199,6 +36274,11 @@
           <t>$12.99</t>
         </is>
       </c>
+      <c r="QQ16" t="inlineStr">
+        <is>
+          <t>$12.99</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -38491,6 +38571,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="QQ17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -40783,6 +40868,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="QQ18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -43075,6 +43165,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="QQ19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -45367,6 +45462,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="QQ20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -47659,6 +47759,11 @@
           <t>$1.27</t>
         </is>
       </c>
+      <c r="QQ21" t="inlineStr">
+        <is>
+          <t>$1.27</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -49949,6 +50054,11 @@
       <c r="QP22" t="inlineStr">
         <is>
           <t>3.749</t>
+        </is>
+      </c>
+      <c r="QQ22" t="inlineStr">
+        <is>
+          <t>3.999</t>
         </is>
       </c>
     </row>
@@ -52251,6 +52361,11 @@
         </is>
       </c>
       <c r="QP23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="QQ23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -54319,6 +54434,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="QQ24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:QQ24"/>
+  <dimension ref="A1:QR24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2712,6 +2712,11 @@
           <t>Price_2026-07-15 10:09</t>
         </is>
       </c>
+      <c r="QR1" t="inlineStr">
+        <is>
+          <t>Price_2026-07-16 10:15</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5005,6 +5010,11 @@
         </is>
       </c>
       <c r="QQ2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="QR2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7142,6 +7152,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="QR3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9315,6 +9330,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="QR4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11612,6 +11632,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="QR5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13909,6 +13934,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="QR6" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16206,6 +16236,11 @@
           <t>$6.68</t>
         </is>
       </c>
+      <c r="QR7" t="inlineStr">
+        <is>
+          <t>$6.68</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -18503,6 +18538,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="QR8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20800,6 +20840,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="QR9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -23097,6 +23142,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="QR10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -25394,6 +25444,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="QR11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -27691,6 +27746,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="QR12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -29988,6 +30048,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="QR13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -32285,6 +32350,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="QR14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -34578,6 +34648,11 @@
         </is>
       </c>
       <c r="QQ15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="QR15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -36279,6 +36354,11 @@
           <t>$12.99</t>
         </is>
       </c>
+      <c r="QR16" t="inlineStr">
+        <is>
+          <t>$12.99</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -38576,6 +38656,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="QR17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -40873,6 +40958,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="QR18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -43170,6 +43260,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="QR19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -45467,6 +45562,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="QR20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -47764,6 +47864,11 @@
           <t>$1.27</t>
         </is>
       </c>
+      <c r="QR21" t="inlineStr">
+        <is>
+          <t>$0.99</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -50057,6 +50162,11 @@
         </is>
       </c>
       <c r="QQ22" t="inlineStr">
+        <is>
+          <t>3.999</t>
+        </is>
+      </c>
+      <c r="QR22" t="inlineStr">
         <is>
           <t>3.999</t>
         </is>
@@ -52366,6 +52476,11 @@
         </is>
       </c>
       <c r="QQ23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="QR23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -54439,6 +54554,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="QR24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:QR24"/>
+  <dimension ref="A1:QS24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2717,6 +2717,11 @@
           <t>Price_2026-07-16 10:15</t>
         </is>
       </c>
+      <c r="QS1" t="inlineStr">
+        <is>
+          <t>Price_2026-07-17 10:04</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5015,6 +5020,11 @@
         </is>
       </c>
       <c r="QR2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="QS2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7157,6 +7167,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="QS3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9335,6 +9350,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="QS4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11637,6 +11657,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="QS5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13939,6 +13964,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="QS6" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16241,6 +16271,11 @@
           <t>$6.68</t>
         </is>
       </c>
+      <c r="QS7" t="inlineStr">
+        <is>
+          <t>$6.68</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -18543,6 +18578,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="QS8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20845,6 +20885,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="QS9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -23147,6 +23192,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="QS10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -25449,6 +25499,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="QS11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -27751,6 +27806,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="QS12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -30053,6 +30113,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="QS13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -32355,6 +32420,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="QS14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -34653,6 +34723,11 @@
         </is>
       </c>
       <c r="QR15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="QS15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -36359,6 +36434,11 @@
           <t>$12.99</t>
         </is>
       </c>
+      <c r="QS16" t="inlineStr">
+        <is>
+          <t>$12.99</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -38661,6 +38741,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="QS17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -40963,6 +41048,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="QS18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -43265,6 +43355,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="QS19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -45567,6 +45662,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="QS20" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -47869,6 +47969,11 @@
           <t>$0.99</t>
         </is>
       </c>
+      <c r="QS21" t="inlineStr">
+        <is>
+          <t>$0.99</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -50169,6 +50274,11 @@
       <c r="QR22" t="inlineStr">
         <is>
           <t>3.999</t>
+        </is>
+      </c>
+      <c r="QS22" t="inlineStr">
+        <is>
+          <t>3.799</t>
         </is>
       </c>
     </row>
@@ -52481,6 +52591,11 @@
         </is>
       </c>
       <c r="QR23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="QS23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -54559,6 +54674,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="QS24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:QS24"/>
+  <dimension ref="A1:QT24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,6 +2722,11 @@
           <t>Price_2026-07-17 10:04</t>
         </is>
       </c>
+      <c r="QT1" t="inlineStr">
+        <is>
+          <t>Price_2026-07-18 09:31</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5025,6 +5030,11 @@
         </is>
       </c>
       <c r="QS2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="QT2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7172,6 +7182,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="QT3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9355,6 +9370,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="QT4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11662,6 +11682,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="QT5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13969,6 +13994,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="QT6" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16276,6 +16306,11 @@
           <t>$6.68</t>
         </is>
       </c>
+      <c r="QT7" t="inlineStr">
+        <is>
+          <t>$6.68</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -18583,6 +18618,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="QT8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20890,6 +20930,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="QT9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -23197,6 +23242,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="QT10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -25504,6 +25554,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="QT11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -27811,6 +27866,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="QT12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -30118,6 +30178,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="QT13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -32425,6 +32490,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="QT14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -34728,6 +34798,11 @@
         </is>
       </c>
       <c r="QS15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="QT15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -36439,6 +36514,11 @@
           <t>$12.99</t>
         </is>
       </c>
+      <c r="QT16" t="inlineStr">
+        <is>
+          <t>$12.99</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -38746,6 +38826,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="QT17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -41053,6 +41138,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="QT18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -43360,6 +43450,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="QT19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -45667,6 +45762,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="QT20" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -47974,6 +48074,11 @@
           <t>$0.99</t>
         </is>
       </c>
+      <c r="QT21" t="inlineStr">
+        <is>
+          <t>$0.99</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -50277,6 +50382,11 @@
         </is>
       </c>
       <c r="QS22" t="inlineStr">
+        <is>
+          <t>3.799</t>
+        </is>
+      </c>
+      <c r="QT22" t="inlineStr">
         <is>
           <t>3.799</t>
         </is>
@@ -52596,6 +52706,11 @@
         </is>
       </c>
       <c r="QS23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="QT23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -54679,6 +54794,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="QT24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:QT24"/>
+  <dimension ref="A1:QU24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2727,6 +2727,11 @@
           <t>Price_2026-07-18 09:31</t>
         </is>
       </c>
+      <c r="QU1" t="inlineStr">
+        <is>
+          <t>Price_2026-07-19 09:59</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5035,6 +5040,11 @@
         </is>
       </c>
       <c r="QT2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="QU2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7187,6 +7197,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="QU3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9375,6 +9390,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="QU4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11687,6 +11707,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="QU5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13999,6 +14024,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="QU6" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16311,6 +16341,11 @@
           <t>$6.68</t>
         </is>
       </c>
+      <c r="QU7" t="inlineStr">
+        <is>
+          <t>$6.68</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -18623,6 +18658,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="QU8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20935,6 +20975,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="QU9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -23247,6 +23292,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="QU10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -25559,6 +25609,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="QU11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -27871,6 +27926,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="QU12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -30183,6 +30243,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="QU13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -32495,6 +32560,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="QU14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -34803,6 +34873,11 @@
         </is>
       </c>
       <c r="QT15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="QU15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -36519,6 +36594,11 @@
           <t>$12.99</t>
         </is>
       </c>
+      <c r="QU16" t="inlineStr">
+        <is>
+          <t>$12.99</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -38831,6 +38911,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="QU17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -41143,6 +41228,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="QU18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -43455,6 +43545,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="QU19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -45767,6 +45862,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="QU20" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -48079,6 +48179,11 @@
           <t>$0.99</t>
         </is>
       </c>
+      <c r="QU21" t="inlineStr">
+        <is>
+          <t>$0.99</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -50387,6 +50492,11 @@
         </is>
       </c>
       <c r="QT22" t="inlineStr">
+        <is>
+          <t>3.799</t>
+        </is>
+      </c>
+      <c r="QU22" t="inlineStr">
         <is>
           <t>3.799</t>
         </is>
@@ -52711,6 +52821,11 @@
         </is>
       </c>
       <c r="QT23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="QU23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -54799,6 +54914,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="QU24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:QU24"/>
+  <dimension ref="A1:QV24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2732,6 +2732,11 @@
           <t>Price_2026-07-19 09:59</t>
         </is>
       </c>
+      <c r="QV1" t="inlineStr">
+        <is>
+          <t>Price_2026-07-20 10:59</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5045,6 +5050,11 @@
         </is>
       </c>
       <c r="QU2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="QV2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7202,6 +7212,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="QV3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9395,6 +9410,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="QV4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11712,6 +11732,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="QV5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14029,6 +14054,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="QV6" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16346,6 +16376,11 @@
           <t>$6.68</t>
         </is>
       </c>
+      <c r="QV7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -18663,6 +18698,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="QV8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -20980,6 +21020,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="QV9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -23297,6 +23342,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="QV10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -25614,6 +25664,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="QV11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -27931,6 +27986,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="QV12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -30248,6 +30308,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="QV13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -32565,6 +32630,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="QV14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -34878,6 +34948,11 @@
         </is>
       </c>
       <c r="QU15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="QV15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -36599,6 +36674,11 @@
           <t>$12.99</t>
         </is>
       </c>
+      <c r="QV16" t="inlineStr">
+        <is>
+          <t>$12.99</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -38916,6 +38996,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="QV17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -41233,6 +41318,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="QV18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -43550,6 +43640,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="QV19" t="inlineStr">
+        <is>
+          <t>$1.88</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -45867,6 +45962,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="QV20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -48184,6 +48284,11 @@
           <t>$0.99</t>
         </is>
       </c>
+      <c r="QV21" t="inlineStr">
+        <is>
+          <t>$0.99</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -50497,6 +50602,11 @@
         </is>
       </c>
       <c r="QU22" t="inlineStr">
+        <is>
+          <t>3.799</t>
+        </is>
+      </c>
+      <c r="QV22" t="inlineStr">
         <is>
           <t>3.799</t>
         </is>
@@ -52826,6 +52936,11 @@
         </is>
       </c>
       <c r="QU23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="QV23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -54919,6 +55034,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="QV24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:QV24"/>
+  <dimension ref="A1:QW24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2737,6 +2737,11 @@
           <t>Price_2026-07-20 10:59</t>
         </is>
       </c>
+      <c r="QW1" t="inlineStr">
+        <is>
+          <t>Price_2026-07-21 10:33</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5055,6 +5060,11 @@
         </is>
       </c>
       <c r="QV2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="QW2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7217,6 +7227,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="QW3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9415,6 +9430,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="QW4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11737,6 +11757,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="QW5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14059,6 +14084,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="QW6" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16381,6 +16411,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="QW7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -18703,6 +18738,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="QW8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21025,6 +21065,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="QW9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -23347,6 +23392,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="QW10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -25669,6 +25719,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="QW11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -27991,6 +28046,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="QW12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -30313,6 +30373,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="QW13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -32635,6 +32700,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="QW14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -34953,6 +35023,11 @@
         </is>
       </c>
       <c r="QV15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="QW15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -36679,6 +36754,11 @@
           <t>$12.99</t>
         </is>
       </c>
+      <c r="QW16" t="inlineStr">
+        <is>
+          <t>$12.99</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -39001,6 +39081,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="QW17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -41323,6 +41408,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="QW18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -43645,6 +43735,11 @@
           <t>$1.88</t>
         </is>
       </c>
+      <c r="QW19" t="inlineStr">
+        <is>
+          <t>$1.88</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -45967,6 +46062,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="QW20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -48289,6 +48389,11 @@
           <t>$0.99</t>
         </is>
       </c>
+      <c r="QW21" t="inlineStr">
+        <is>
+          <t>$0.99</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -50609,6 +50714,11 @@
       <c r="QV22" t="inlineStr">
         <is>
           <t>3.799</t>
+        </is>
+      </c>
+      <c r="QW22" t="inlineStr">
+        <is>
+          <t>3.779</t>
         </is>
       </c>
     </row>
@@ -52941,6 +53051,11 @@
         </is>
       </c>
       <c r="QV23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="QW23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -55039,6 +55154,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="QW24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:QW24"/>
+  <dimension ref="A1:QX24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2742,6 +2742,11 @@
           <t>Price_2026-07-21 10:33</t>
         </is>
       </c>
+      <c r="QX1" t="inlineStr">
+        <is>
+          <t>Price_2026-07-22 10:32</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5065,6 +5070,11 @@
         </is>
       </c>
       <c r="QW2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="QX2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7232,6 +7242,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="QX3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9435,6 +9450,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="QX4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11762,6 +11782,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="QX5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14089,6 +14114,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="QX6" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16416,6 +16446,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="QX7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -18743,6 +18778,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="QX8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21070,6 +21110,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="QX9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -23397,6 +23442,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="QX10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -25724,6 +25774,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="QX11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -28051,6 +28106,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="QX12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -30378,6 +30438,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="QX13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -32705,6 +32770,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="QX14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -35028,6 +35098,11 @@
         </is>
       </c>
       <c r="QW15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="QX15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -36759,6 +36834,11 @@
           <t>$12.99</t>
         </is>
       </c>
+      <c r="QX16" t="inlineStr">
+        <is>
+          <t>$12.99</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -39086,6 +39166,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="QX17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -41413,6 +41498,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="QX18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -43740,6 +43830,11 @@
           <t>$1.88</t>
         </is>
       </c>
+      <c r="QX19" t="inlineStr">
+        <is>
+          <t>$1.88</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -46067,6 +46162,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="QX20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -48394,6 +48494,11 @@
           <t>$0.99</t>
         </is>
       </c>
+      <c r="QX21" t="inlineStr">
+        <is>
+          <t>$0.99</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -50717,6 +50822,11 @@
         </is>
       </c>
       <c r="QW22" t="inlineStr">
+        <is>
+          <t>3.779</t>
+        </is>
+      </c>
+      <c r="QX22" t="inlineStr">
         <is>
           <t>3.779</t>
         </is>
@@ -53056,6 +53166,11 @@
         </is>
       </c>
       <c r="QW23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="QX23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -55159,6 +55274,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="QX24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:QX24"/>
+  <dimension ref="A1:QY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2747,6 +2747,11 @@
           <t>Price_2026-07-22 10:32</t>
         </is>
       </c>
+      <c r="QY1" t="inlineStr">
+        <is>
+          <t>Price_2026-07-23 10:28</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5075,6 +5080,11 @@
         </is>
       </c>
       <c r="QX2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="QY2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7247,6 +7257,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="QY3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9455,6 +9470,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="QY4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11787,6 +11807,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="QY5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14119,6 +14144,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="QY6" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16451,6 +16481,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="QY7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -18783,6 +18818,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="QY8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21115,6 +21155,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="QY9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -23447,6 +23492,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="QY10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -25779,6 +25829,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="QY11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -28111,6 +28166,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="QY12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -30443,6 +30503,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="QY13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -32775,6 +32840,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="QY14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -35103,6 +35173,11 @@
         </is>
       </c>
       <c r="QX15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="QY15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -36839,6 +36914,11 @@
           <t>$12.99</t>
         </is>
       </c>
+      <c r="QY16" t="inlineStr">
+        <is>
+          <t>$12.99</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -39171,6 +39251,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="QY17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -41503,6 +41588,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="QY18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -43835,6 +43925,11 @@
           <t>$1.88</t>
         </is>
       </c>
+      <c r="QY19" t="inlineStr">
+        <is>
+          <t>$1.88</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -46167,6 +46262,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="QY20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -48499,6 +48599,11 @@
           <t>$0.99</t>
         </is>
       </c>
+      <c r="QY21" t="inlineStr">
+        <is>
+          <t>$0.99</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -50827,6 +50932,11 @@
         </is>
       </c>
       <c r="QX22" t="inlineStr">
+        <is>
+          <t>3.779</t>
+        </is>
+      </c>
+      <c r="QY22" t="inlineStr">
         <is>
           <t>3.779</t>
         </is>
@@ -53171,6 +53281,11 @@
         </is>
       </c>
       <c r="QX23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="QY23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -55279,6 +55394,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="QY24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:QY24"/>
+  <dimension ref="A1:QZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2752,6 +2752,11 @@
           <t>Price_2026-07-23 10:28</t>
         </is>
       </c>
+      <c r="QZ1" t="inlineStr">
+        <is>
+          <t>Price_2026-07-24 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5085,6 +5090,11 @@
         </is>
       </c>
       <c r="QY2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="QZ2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7262,6 +7272,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="QZ3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9475,6 +9490,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="QZ4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11812,6 +11832,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="QZ5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14149,6 +14174,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="QZ6" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16486,6 +16516,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="QZ7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -18823,6 +18858,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="QZ8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21160,6 +21200,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="QZ9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -23497,6 +23542,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="QZ10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -25834,6 +25884,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="QZ11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -28171,6 +28226,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="QZ12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -30508,6 +30568,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="QZ13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -32845,6 +32910,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="QZ14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -35178,6 +35248,11 @@
         </is>
       </c>
       <c r="QY15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="QZ15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -36919,6 +36994,11 @@
           <t>$12.99</t>
         </is>
       </c>
+      <c r="QZ16" t="inlineStr">
+        <is>
+          <t>$12.99</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -39256,6 +39336,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="QZ17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -41593,6 +41678,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="QZ18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -43930,6 +44020,11 @@
           <t>$1.88</t>
         </is>
       </c>
+      <c r="QZ19" t="inlineStr">
+        <is>
+          <t>$1.88</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -46267,6 +46362,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="QZ20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -48604,6 +48704,11 @@
           <t>$0.99</t>
         </is>
       </c>
+      <c r="QZ21" t="inlineStr">
+        <is>
+          <t>$0.99</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -50939,6 +51044,11 @@
       <c r="QY22" t="inlineStr">
         <is>
           <t>3.779</t>
+        </is>
+      </c>
+      <c r="QZ22" t="inlineStr">
+        <is>
+          <t>3.749</t>
         </is>
       </c>
     </row>
@@ -53286,6 +53396,11 @@
         </is>
       </c>
       <c r="QY23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="QZ23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -55399,6 +55514,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="QZ24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:QZ24"/>
+  <dimension ref="A1:RA24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2757,6 +2757,11 @@
           <t>Price_2026-07-24 10:23</t>
         </is>
       </c>
+      <c r="RA1" t="inlineStr">
+        <is>
+          <t>Price_2026-07-25 09:53</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5095,6 +5100,11 @@
         </is>
       </c>
       <c r="QZ2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="RA2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7277,6 +7287,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="RA3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9495,6 +9510,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="RA4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11837,6 +11857,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="RA5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14179,6 +14204,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="RA6" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16521,6 +16551,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="RA7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -18863,6 +18898,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="RA8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21205,6 +21245,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="RA9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -23547,6 +23592,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="RA10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -25889,6 +25939,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="RA11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -28231,6 +28286,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="RA12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -30573,6 +30633,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="RA13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -32915,6 +32980,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="RA14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -35253,6 +35323,11 @@
         </is>
       </c>
       <c r="QZ15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="RA15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -36999,6 +37074,11 @@
           <t>$12.99</t>
         </is>
       </c>
+      <c r="RA16" t="inlineStr">
+        <is>
+          <t>$12.99</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -39341,6 +39421,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="RA17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -41683,6 +41768,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="RA18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -44025,6 +44115,11 @@
           <t>$1.88</t>
         </is>
       </c>
+      <c r="RA19" t="inlineStr">
+        <is>
+          <t>$1.88</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -46367,6 +46462,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="RA20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -48709,6 +48809,11 @@
           <t>$0.99</t>
         </is>
       </c>
+      <c r="RA21" t="inlineStr">
+        <is>
+          <t>$0.99</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -51047,6 +51152,11 @@
         </is>
       </c>
       <c r="QZ22" t="inlineStr">
+        <is>
+          <t>3.749</t>
+        </is>
+      </c>
+      <c r="RA22" t="inlineStr">
         <is>
           <t>3.749</t>
         </is>
@@ -53401,6 +53511,11 @@
         </is>
       </c>
       <c r="QZ23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="RA23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -55519,6 +55634,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="RA24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:RA24"/>
+  <dimension ref="A1:RB24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2762,6 +2762,11 @@
           <t>Price_2026-07-25 09:53</t>
         </is>
       </c>
+      <c r="RB1" t="inlineStr">
+        <is>
+          <t>Price_2026-07-26 10:07</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5105,6 +5110,11 @@
         </is>
       </c>
       <c r="RA2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="RB2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7292,6 +7302,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="RB3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9515,6 +9530,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="RB4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11862,6 +11882,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="RB5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14209,6 +14234,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="RB6" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16556,6 +16586,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="RB7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -18903,6 +18938,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="RB8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21250,6 +21290,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="RB9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -23597,6 +23642,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="RB10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -25944,6 +25994,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="RB11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -28291,6 +28346,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="RB12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -30638,6 +30698,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="RB13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -32985,6 +33050,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="RB14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -35328,6 +35398,11 @@
         </is>
       </c>
       <c r="RA15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="RB15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -37079,6 +37154,11 @@
           <t>$12.99</t>
         </is>
       </c>
+      <c r="RB16" t="inlineStr">
+        <is>
+          <t>$12.99</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -39426,6 +39506,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="RB17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -41773,6 +41858,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="RB18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -44120,6 +44210,11 @@
           <t>$1.88</t>
         </is>
       </c>
+      <c r="RB19" t="inlineStr">
+        <is>
+          <t>$1.88</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -46467,6 +46562,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="RB20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -48814,6 +48914,11 @@
           <t>$0.99</t>
         </is>
       </c>
+      <c r="RB21" t="inlineStr">
+        <is>
+          <t>$0.99</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -51157,6 +51262,11 @@
         </is>
       </c>
       <c r="RA22" t="inlineStr">
+        <is>
+          <t>3.749</t>
+        </is>
+      </c>
+      <c r="RB22" t="inlineStr">
         <is>
           <t>3.749</t>
         </is>
@@ -53516,6 +53626,11 @@
         </is>
       </c>
       <c r="RA23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="RB23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -55639,6 +55754,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="RB24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:RB24"/>
+  <dimension ref="A1:RC24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2767,6 +2767,11 @@
           <t>Price_2026-07-26 10:07</t>
         </is>
       </c>
+      <c r="RC1" t="inlineStr">
+        <is>
+          <t>Price_2026-07-27 11:27</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5115,6 +5120,11 @@
         </is>
       </c>
       <c r="RB2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="RC2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7307,6 +7317,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="RC3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9535,6 +9550,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="RC4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11887,6 +11907,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="RC5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14239,6 +14264,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="RC6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16591,6 +16621,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="RC7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -18943,6 +18978,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="RC8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21295,6 +21335,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="RC9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -23647,6 +23692,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="RC10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -25999,6 +26049,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="RC11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -28351,6 +28406,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="RC12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -30703,6 +30763,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="RC13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -33055,6 +33120,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="RC14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -35403,6 +35473,11 @@
         </is>
       </c>
       <c r="RB15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="RC15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -37159,6 +37234,11 @@
           <t>$12.99</t>
         </is>
       </c>
+      <c r="RC16" t="inlineStr">
+        <is>
+          <t>$12.99</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -39511,6 +39591,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="RC17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -41863,6 +41948,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="RC18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -44215,6 +44305,11 @@
           <t>$1.88</t>
         </is>
       </c>
+      <c r="RC19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -46567,6 +46662,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="RC20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -48919,6 +49019,11 @@
           <t>$0.99</t>
         </is>
       </c>
+      <c r="RC21" t="inlineStr">
+        <is>
+          <t>$0.99</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -51267,6 +51372,11 @@
         </is>
       </c>
       <c r="RB22" t="inlineStr">
+        <is>
+          <t>3.749</t>
+        </is>
+      </c>
+      <c r="RC22" t="inlineStr">
         <is>
           <t>3.749</t>
         </is>
@@ -53631,6 +53741,11 @@
         </is>
       </c>
       <c r="RB23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="RC23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -55759,6 +55874,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="RC24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:RC24"/>
+  <dimension ref="A1:RD24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2772,6 +2772,11 @@
           <t>Price_2026-07-27 11:27</t>
         </is>
       </c>
+      <c r="RD1" t="inlineStr">
+        <is>
+          <t>Price_2026-07-28 10:41</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5125,6 +5130,11 @@
         </is>
       </c>
       <c r="RC2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="RD2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7322,6 +7332,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="RD3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9555,6 +9570,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="RD4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11912,6 +11932,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="RD5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14269,6 +14294,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="RD6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16626,6 +16656,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="RD7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -18983,6 +19018,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="RD8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21340,6 +21380,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="RD9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -23697,6 +23742,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="RD10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -26054,6 +26104,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="RD11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -28411,6 +28466,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="RD12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -30768,6 +30828,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="RD13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -33125,6 +33190,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="RD14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -35478,6 +35548,11 @@
         </is>
       </c>
       <c r="RC15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="RD15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -37239,6 +37314,11 @@
           <t>$12.99</t>
         </is>
       </c>
+      <c r="RD16" t="inlineStr">
+        <is>
+          <t>$12.99</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -39596,6 +39676,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="RD17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -41953,6 +42038,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="RD18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -44310,6 +44400,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="RD19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -46667,6 +46762,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="RD20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -49024,6 +49124,11 @@
           <t>$0.99</t>
         </is>
       </c>
+      <c r="RD21" t="inlineStr">
+        <is>
+          <t>$0.99</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -51377,6 +51482,11 @@
         </is>
       </c>
       <c r="RC22" t="inlineStr">
+        <is>
+          <t>3.749</t>
+        </is>
+      </c>
+      <c r="RD22" t="inlineStr">
         <is>
           <t>3.749</t>
         </is>
@@ -53746,6 +53856,11 @@
         </is>
       </c>
       <c r="RC23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="RD23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -55879,6 +55994,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="RD24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:RD24"/>
+  <dimension ref="A1:RE24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2777,6 +2777,11 @@
           <t>Price_2026-07-28 10:41</t>
         </is>
       </c>
+      <c r="RE1" t="inlineStr">
+        <is>
+          <t>Price_2026-07-29 10:45</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5135,6 +5140,11 @@
         </is>
       </c>
       <c r="RD2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="RE2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7337,6 +7347,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="RE3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9575,6 +9590,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="RE4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11937,6 +11957,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="RE5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14299,6 +14324,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="RE6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16661,6 +16691,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="RE7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19023,6 +19058,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="RE8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21385,6 +21425,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="RE9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -23747,6 +23792,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="RE10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -26109,6 +26159,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="RE11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -28471,6 +28526,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="RE12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -30833,6 +30893,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="RE13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -33195,6 +33260,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="RE14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -35553,6 +35623,11 @@
         </is>
       </c>
       <c r="RD15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="RE15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -37319,6 +37394,11 @@
           <t>$12.99</t>
         </is>
       </c>
+      <c r="RE16" t="inlineStr">
+        <is>
+          <t>$12.99</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -39681,6 +39761,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="RE17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -42043,6 +42128,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="RE18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -44405,6 +44495,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="RE19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -46767,6 +46862,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="RE20" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -49129,6 +49229,11 @@
           <t>$0.99</t>
         </is>
       </c>
+      <c r="RE21" t="inlineStr">
+        <is>
+          <t>$0.99</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -51489,6 +51594,11 @@
       <c r="RD22" t="inlineStr">
         <is>
           <t>3.749</t>
+        </is>
+      </c>
+      <c r="RE22" t="inlineStr">
+        <is>
+          <t>3.899</t>
         </is>
       </c>
     </row>
@@ -53861,6 +53971,11 @@
         </is>
       </c>
       <c r="RD23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="RE23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -55999,6 +56114,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="RE24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:RE24"/>
+  <dimension ref="A1:RF24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2782,6 +2782,11 @@
           <t>Price_2026-07-29 10:45</t>
         </is>
       </c>
+      <c r="RF1" t="inlineStr">
+        <is>
+          <t>Price_2026-07-30 10:32</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5145,6 +5150,11 @@
         </is>
       </c>
       <c r="RE2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="RF2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7352,6 +7362,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="RF3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9595,6 +9610,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="RF4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11962,6 +11982,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="RF5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14329,6 +14354,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="RF6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16696,6 +16726,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="RF7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19063,6 +19098,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="RF8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21430,6 +21470,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="RF9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -23797,6 +23842,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="RF10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -26164,6 +26214,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="RF11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -28531,6 +28586,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="RF12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -30898,6 +30958,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="RF13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -33265,6 +33330,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="RF14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -35628,6 +35698,11 @@
         </is>
       </c>
       <c r="RE15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="RF15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -37399,6 +37474,11 @@
           <t>$12.99</t>
         </is>
       </c>
+      <c r="RF16" t="inlineStr">
+        <is>
+          <t>$12.99</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -39766,6 +39846,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="RF17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -42133,6 +42218,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="RF18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -44500,6 +44590,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="RF19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -46867,6 +46962,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="RF20" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -49234,6 +49334,11 @@
           <t>$0.99</t>
         </is>
       </c>
+      <c r="RF21" t="inlineStr">
+        <is>
+          <t>$0.99</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -51597,6 +51702,11 @@
         </is>
       </c>
       <c r="RE22" t="inlineStr">
+        <is>
+          <t>3.899</t>
+        </is>
+      </c>
+      <c r="RF22" t="inlineStr">
         <is>
           <t>3.899</t>
         </is>
@@ -53976,6 +54086,11 @@
         </is>
       </c>
       <c r="RE23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="RF23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -56119,6 +56234,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="RF24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:RF24"/>
+  <dimension ref="A1:RG24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2787,6 +2787,11 @@
           <t>Price_2026-07-30 10:32</t>
         </is>
       </c>
+      <c r="RG1" t="inlineStr">
+        <is>
+          <t>Price_2026-07-31 10:45</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5155,6 +5160,11 @@
         </is>
       </c>
       <c r="RF2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="RG2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7367,6 +7377,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="RG3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9615,6 +9630,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="RG4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11987,6 +12007,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="RG5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14359,6 +14384,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="RG6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16731,6 +16761,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="RG7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19103,6 +19138,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="RG8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21475,6 +21515,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="RG9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -23847,6 +23892,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="RG10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -26219,6 +26269,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="RG11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -28591,6 +28646,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="RG12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -30963,6 +31023,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="RG13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -33335,6 +33400,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="RG14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -35703,6 +35773,11 @@
         </is>
       </c>
       <c r="RF15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="RG15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -37479,6 +37554,11 @@
           <t>$12.99</t>
         </is>
       </c>
+      <c r="RG16" t="inlineStr">
+        <is>
+          <t>$12.99</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -39851,6 +39931,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="RG17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -42223,6 +42308,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="RG18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -44595,6 +44685,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="RG19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -46967,6 +47062,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="RG20" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -49339,6 +49439,11 @@
           <t>$0.99</t>
         </is>
       </c>
+      <c r="RG21" t="inlineStr">
+        <is>
+          <t>$0.99</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -51709,6 +51814,11 @@
       <c r="RF22" t="inlineStr">
         <is>
           <t>3.899</t>
+        </is>
+      </c>
+      <c r="RG22" t="inlineStr">
+        <is>
+          <t>3.849</t>
         </is>
       </c>
     </row>
@@ -54091,6 +54201,11 @@
         </is>
       </c>
       <c r="RF23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="RG23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -56239,6 +56354,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="RG24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:RG24"/>
+  <dimension ref="A1:RH24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2792,6 +2792,11 @@
           <t>Price_2026-07-31 10:45</t>
         </is>
       </c>
+      <c r="RH1" t="inlineStr">
+        <is>
+          <t>Price_2026-08-01 10:05</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5165,6 +5170,11 @@
         </is>
       </c>
       <c r="RG2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="RH2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7382,6 +7392,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="RH3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9635,6 +9650,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="RH4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12012,6 +12032,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="RH5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14389,6 +14414,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="RH6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16766,6 +16796,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="RH7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19143,6 +19178,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="RH8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21520,6 +21560,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="RH9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -23897,6 +23942,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="RH10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -26274,6 +26324,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="RH11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -28651,6 +28706,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="RH12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -31028,6 +31088,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="RH13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -33405,6 +33470,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="RH14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -35778,6 +35848,11 @@
         </is>
       </c>
       <c r="RG15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="RH15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -37559,6 +37634,11 @@
           <t>$12.99</t>
         </is>
       </c>
+      <c r="RH16" t="inlineStr">
+        <is>
+          <t>$12.99</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -39936,6 +40016,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="RH17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -42313,6 +42398,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="RH18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -44690,6 +44780,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="RH19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -47067,6 +47162,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="RH20" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -49444,6 +49544,11 @@
           <t>$0.99</t>
         </is>
       </c>
+      <c r="RH21" t="inlineStr">
+        <is>
+          <t>$0.99</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -51819,6 +51924,11 @@
       <c r="RG22" t="inlineStr">
         <is>
           <t>3.849</t>
+        </is>
+      </c>
+      <c r="RH22" t="inlineStr">
+        <is>
+          <t>3.799</t>
         </is>
       </c>
     </row>
@@ -54206,6 +54316,11 @@
         </is>
       </c>
       <c r="RG23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="RH23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -56359,6 +56474,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="RH24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:RH24"/>
+  <dimension ref="A1:RI24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2797,6 +2797,11 @@
           <t>Price_2026-08-01 10:05</t>
         </is>
       </c>
+      <c r="RI1" t="inlineStr">
+        <is>
+          <t>Price_2026-08-02 10:03</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5175,6 +5180,11 @@
         </is>
       </c>
       <c r="RH2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="RI2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7397,6 +7407,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="RI3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9655,6 +9670,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="RI4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12037,6 +12057,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="RI5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14419,6 +14444,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="RI6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16801,6 +16831,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="RI7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19183,6 +19218,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="RI8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21565,6 +21605,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="RI9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -23947,6 +23992,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="RI10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -26329,6 +26379,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="RI11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -28711,6 +28766,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="RI12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -31093,6 +31153,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="RI13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -33475,6 +33540,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="RI14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -35853,6 +35923,11 @@
         </is>
       </c>
       <c r="RH15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="RI15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -37639,6 +37714,11 @@
           <t>$12.99</t>
         </is>
       </c>
+      <c r="RI16" t="inlineStr">
+        <is>
+          <t>$12.99</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -40021,6 +40101,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="RI17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -42403,6 +42488,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="RI18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -44785,6 +44875,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="RI19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -47167,6 +47262,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="RI20" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -49549,6 +49649,11 @@
           <t>$0.99</t>
         </is>
       </c>
+      <c r="RI21" t="inlineStr">
+        <is>
+          <t>$0.99</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -51927,6 +52032,11 @@
         </is>
       </c>
       <c r="RH22" t="inlineStr">
+        <is>
+          <t>3.799</t>
+        </is>
+      </c>
+      <c r="RI22" t="inlineStr">
         <is>
           <t>3.799</t>
         </is>
@@ -54321,6 +54431,11 @@
         </is>
       </c>
       <c r="RH23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="RI23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -56479,6 +56594,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="RI24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:RI24"/>
+  <dimension ref="A1:RJ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2802,6 +2802,11 @@
           <t>Price_2026-08-02 10:03</t>
         </is>
       </c>
+      <c r="RJ1" t="inlineStr">
+        <is>
+          <t>Price_2026-08-03 11:29</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5185,6 +5190,11 @@
         </is>
       </c>
       <c r="RI2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="RJ2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7412,6 +7422,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="RJ3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9675,6 +9690,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="RJ4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12062,6 +12082,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="RJ5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14449,6 +14474,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="RJ6" t="inlineStr">
+        <is>
+          <t>$3.97</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16836,6 +16866,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="RJ7" t="inlineStr">
+        <is>
+          <t>$6.88</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19223,6 +19258,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="RJ8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21610,6 +21650,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="RJ9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -23997,6 +24042,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="RJ10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -26384,6 +26434,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="RJ11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -28771,6 +28826,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="RJ12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -31158,6 +31218,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="RJ13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -33545,6 +33610,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="RJ14" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -35928,6 +35998,11 @@
         </is>
       </c>
       <c r="RI15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="RJ15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -37719,6 +37794,11 @@
           <t>$12.99</t>
         </is>
       </c>
+      <c r="RJ16" t="inlineStr">
+        <is>
+          <t>$12.99</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -40106,6 +40186,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="RJ17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -42493,6 +42578,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="RJ18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -44880,6 +44970,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="RJ19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -47267,6 +47362,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="RJ20" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -49654,6 +49754,11 @@
           <t>$0.99</t>
         </is>
       </c>
+      <c r="RJ21" t="inlineStr">
+        <is>
+          <t>$0.99</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -52037,6 +52142,11 @@
         </is>
       </c>
       <c r="RI22" t="inlineStr">
+        <is>
+          <t>3.799</t>
+        </is>
+      </c>
+      <c r="RJ22" t="inlineStr">
         <is>
           <t>3.799</t>
         </is>
@@ -54436,6 +54546,11 @@
         </is>
       </c>
       <c r="RI23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="RJ23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -56599,6 +56714,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="RJ24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:RJ24"/>
+  <dimension ref="A1:RK24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2807,6 +2807,11 @@
           <t>Price_2026-08-03 11:29</t>
         </is>
       </c>
+      <c r="RK1" t="inlineStr">
+        <is>
+          <t>Price_2026-08-04 10:45</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5195,6 +5200,11 @@
         </is>
       </c>
       <c r="RJ2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="RK2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7427,6 +7437,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="RK3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9695,6 +9710,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="RK4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12087,6 +12107,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="RK5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14479,6 +14504,11 @@
           <t>$3.97</t>
         </is>
       </c>
+      <c r="RK6" t="inlineStr">
+        <is>
+          <t>$3.97</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16871,6 +16901,11 @@
           <t>$6.88</t>
         </is>
       </c>
+      <c r="RK7" t="inlineStr">
+        <is>
+          <t>$6.88</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19263,6 +19298,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="RK8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21655,6 +21695,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="RK9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24047,6 +24092,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="RK10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -26439,6 +26489,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="RK11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -28831,6 +28886,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="RK12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -31223,6 +31283,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="RK13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -33615,6 +33680,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="RK14" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -36003,6 +36073,11 @@
         </is>
       </c>
       <c r="RJ15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="RK15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -37799,6 +37874,11 @@
           <t>$12.99</t>
         </is>
       </c>
+      <c r="RK16" t="inlineStr">
+        <is>
+          <t>$12.99</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -40191,6 +40271,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="RK17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -42583,6 +42668,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="RK18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -44975,6 +45065,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="RK19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -47367,6 +47462,11 @@
           <t>$4.99</t>
         </is>
       </c>
+      <c r="RK20" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -49759,6 +49859,11 @@
           <t>$0.99</t>
         </is>
       </c>
+      <c r="RK21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -52149,6 +52254,11 @@
       <c r="RJ22" t="inlineStr">
         <is>
           <t>3.799</t>
+        </is>
+      </c>
+      <c r="RK22" t="inlineStr">
+        <is>
+          <t>3.749</t>
         </is>
       </c>
     </row>
@@ -54551,6 +54661,11 @@
         </is>
       </c>
       <c r="RJ23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="RK23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -56719,6 +56834,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="RK24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:RK24"/>
+  <dimension ref="A1:RL24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2812,6 +2812,11 @@
           <t>Price_2026-08-04 10:45</t>
         </is>
       </c>
+      <c r="RL1" t="inlineStr">
+        <is>
+          <t>Price_2026-08-05 10:41</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5205,6 +5210,11 @@
         </is>
       </c>
       <c r="RK2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="RL2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7442,6 +7452,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="RL3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9715,6 +9730,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="RL4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12112,6 +12132,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="RL5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14509,6 +14534,11 @@
           <t>$3.97</t>
         </is>
       </c>
+      <c r="RL6" t="inlineStr">
+        <is>
+          <t>$3.97</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16906,6 +16936,11 @@
           <t>$6.88</t>
         </is>
       </c>
+      <c r="RL7" t="inlineStr">
+        <is>
+          <t>$6.88</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19303,6 +19338,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="RL8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21700,6 +21740,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="RL9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24097,6 +24142,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="RL10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -26494,6 +26544,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="RL11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -28891,6 +28946,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="RL12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -31288,6 +31348,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="RL13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -33685,6 +33750,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="RL14" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -36078,6 +36148,11 @@
         </is>
       </c>
       <c r="RK15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="RL15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -37879,6 +37954,11 @@
           <t>$12.99</t>
         </is>
       </c>
+      <c r="RL16" t="inlineStr">
+        <is>
+          <t>$12.99</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -40276,6 +40356,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="RL17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -42673,6 +42758,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="RL18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -45070,6 +45160,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="RL19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -47467,6 +47562,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="RL20" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -49864,6 +49964,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="RL21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -52257,6 +52362,11 @@
         </is>
       </c>
       <c r="RK22" t="inlineStr">
+        <is>
+          <t>3.749</t>
+        </is>
+      </c>
+      <c r="RL22" t="inlineStr">
         <is>
           <t>3.749</t>
         </is>
@@ -54666,6 +54776,11 @@
         </is>
       </c>
       <c r="RK23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="RL23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -56839,6 +56954,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="RL24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:RL24"/>
+  <dimension ref="A1:RM24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2817,6 +2817,11 @@
           <t>Price_2026-08-05 10:41</t>
         </is>
       </c>
+      <c r="RM1" t="inlineStr">
+        <is>
+          <t>Price_2026-08-06 10:45</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5215,6 +5220,11 @@
         </is>
       </c>
       <c r="RL2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="RM2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7457,6 +7467,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="RM3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9735,6 +9750,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="RM4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12137,6 +12157,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="RM5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14539,6 +14564,11 @@
           <t>$3.97</t>
         </is>
       </c>
+      <c r="RM6" t="inlineStr">
+        <is>
+          <t>$3.97</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16941,6 +16971,11 @@
           <t>$6.88</t>
         </is>
       </c>
+      <c r="RM7" t="inlineStr">
+        <is>
+          <t>$6.88</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19343,6 +19378,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="RM8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21745,6 +21785,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="RM9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24147,6 +24192,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="RM10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -26549,6 +26599,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="RM11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -28951,6 +29006,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="RM12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -31353,6 +31413,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="RM13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -33755,6 +33820,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="RM14" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -36153,6 +36223,11 @@
         </is>
       </c>
       <c r="RL15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="RM15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -37959,6 +38034,11 @@
           <t>$12.99</t>
         </is>
       </c>
+      <c r="RM16" t="inlineStr">
+        <is>
+          <t>$12.99</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -40361,6 +40441,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="RM17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -42763,6 +42848,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="RM18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -45165,6 +45255,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="RM19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -47567,6 +47662,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="RM20" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -49969,6 +50069,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="RM21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -52367,6 +52472,11 @@
         </is>
       </c>
       <c r="RL22" t="inlineStr">
+        <is>
+          <t>3.749</t>
+        </is>
+      </c>
+      <c r="RM22" t="inlineStr">
         <is>
           <t>3.749</t>
         </is>
@@ -54781,6 +54891,11 @@
         </is>
       </c>
       <c r="RL23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="RM23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -56959,6 +57074,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="RM24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:RM24"/>
+  <dimension ref="A1:RN24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2822,6 +2822,11 @@
           <t>Price_2026-08-06 10:45</t>
         </is>
       </c>
+      <c r="RN1" t="inlineStr">
+        <is>
+          <t>Price_2026-08-07 09:05</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5225,6 +5230,11 @@
         </is>
       </c>
       <c r="RM2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="RN2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7472,6 +7482,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="RN3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9755,6 +9770,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="RN4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12162,6 +12182,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="RN5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14569,6 +14594,11 @@
           <t>$3.97</t>
         </is>
       </c>
+      <c r="RN6" t="inlineStr">
+        <is>
+          <t>$3.97</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16976,6 +17006,11 @@
           <t>$6.88</t>
         </is>
       </c>
+      <c r="RN7" t="inlineStr">
+        <is>
+          <t>$6.88</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19383,6 +19418,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="RN8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21790,6 +21830,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="RN9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24197,6 +24242,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="RN10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -26604,6 +26654,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="RN11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -29011,6 +29066,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="RN12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -31418,6 +31478,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="RN13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -33825,6 +33890,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="RN14" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -36228,6 +36298,11 @@
         </is>
       </c>
       <c r="RM15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="RN15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -38039,6 +38114,11 @@
           <t>$12.99</t>
         </is>
       </c>
+      <c r="RN16" t="inlineStr">
+        <is>
+          <t>$12.99</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -40446,6 +40526,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="RN17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -42853,6 +42938,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="RN18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -45260,6 +45350,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="RN19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -47667,6 +47762,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="RN20" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -50074,6 +50174,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="RN21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -52479,6 +52584,11 @@
       <c r="RM22" t="inlineStr">
         <is>
           <t>3.749</t>
+        </is>
+      </c>
+      <c r="RN22" t="inlineStr">
+        <is>
+          <t>3.699</t>
         </is>
       </c>
     </row>
@@ -54896,6 +55006,11 @@
         </is>
       </c>
       <c r="RM23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="RN23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -57079,6 +57194,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="RN24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:RN24"/>
+  <dimension ref="A1:RO24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2827,6 +2827,11 @@
           <t>Price_2026-08-07 09:05</t>
         </is>
       </c>
+      <c r="RO1" t="inlineStr">
+        <is>
+          <t>Price_2026-08-08 08:46</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5235,6 +5240,11 @@
         </is>
       </c>
       <c r="RN2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="RO2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7487,6 +7497,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="RO3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9775,6 +9790,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="RO4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12187,6 +12207,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="RO5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14599,6 +14624,11 @@
           <t>$3.97</t>
         </is>
       </c>
+      <c r="RO6" t="inlineStr">
+        <is>
+          <t>$3.97</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17011,6 +17041,11 @@
           <t>$6.88</t>
         </is>
       </c>
+      <c r="RO7" t="inlineStr">
+        <is>
+          <t>$6.88</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19423,6 +19458,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="RO8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21835,6 +21875,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="RO9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24247,6 +24292,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="RO10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -26659,6 +26709,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="RO11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -29071,6 +29126,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="RO12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -31483,6 +31543,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="RO13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -33895,6 +33960,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="RO14" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -36303,6 +36373,11 @@
         </is>
       </c>
       <c r="RN15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="RO15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -38119,6 +38194,11 @@
           <t>$12.99</t>
         </is>
       </c>
+      <c r="RO16" t="inlineStr">
+        <is>
+          <t>$12.99</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -40531,6 +40611,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="RO17" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -42943,6 +43028,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="RO18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -45355,6 +45445,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="RO19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -47767,6 +47862,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="RO20" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -50179,6 +50279,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="RO21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -52589,6 +52694,11 @@
       <c r="RN22" t="inlineStr">
         <is>
           <t>3.699</t>
+        </is>
+      </c>
+      <c r="RO22" t="inlineStr">
+        <is>
+          <t>3.679</t>
         </is>
       </c>
     </row>
@@ -55011,6 +55121,11 @@
         </is>
       </c>
       <c r="RN23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="RO23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -57199,6 +57314,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="RO24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:RO24"/>
+  <dimension ref="A1:RP24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2832,6 +2832,11 @@
           <t>Price_2026-08-08 08:46</t>
         </is>
       </c>
+      <c r="RP1" t="inlineStr">
+        <is>
+          <t>Price_2026-08-09 08:48</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5245,6 +5250,11 @@
         </is>
       </c>
       <c r="RO2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="RP2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7502,6 +7512,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="RP3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9795,6 +9810,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="RP4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12212,6 +12232,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="RP5" t="inlineStr">
+        <is>
+          <t>$5.32</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14629,6 +14654,11 @@
           <t>$3.97</t>
         </is>
       </c>
+      <c r="RP6" t="inlineStr">
+        <is>
+          <t>$3.97</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17046,6 +17076,11 @@
           <t>$6.88</t>
         </is>
       </c>
+      <c r="RP7" t="inlineStr">
+        <is>
+          <t>$6.88</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19463,6 +19498,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="RP8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21880,6 +21920,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="RP9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24297,6 +24342,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="RP10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -26714,6 +26764,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="RP11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -29131,6 +29186,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="RP12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -31548,6 +31608,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="RP13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -33965,6 +34030,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="RP14" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -36378,6 +36448,11 @@
         </is>
       </c>
       <c r="RO15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="RP15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -38199,6 +38274,11 @@
           <t>$12.99</t>
         </is>
       </c>
+      <c r="RP16" t="inlineStr">
+        <is>
+          <t>$12.99</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -40616,6 +40696,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="RP17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -43033,6 +43118,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="RP18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -45450,6 +45540,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="RP19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -47867,6 +47962,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="RP20" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -50284,6 +50384,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="RP21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -52697,6 +52802,11 @@
         </is>
       </c>
       <c r="RO22" t="inlineStr">
+        <is>
+          <t>3.679</t>
+        </is>
+      </c>
+      <c r="RP22" t="inlineStr">
         <is>
           <t>3.679</t>
         </is>
@@ -55126,6 +55236,11 @@
         </is>
       </c>
       <c r="RO23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="RP23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -57319,6 +57434,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="RP24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:RP24"/>
+  <dimension ref="A1:RQ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2837,6 +2837,11 @@
           <t>Price_2026-08-09 08:48</t>
         </is>
       </c>
+      <c r="RQ1" t="inlineStr">
+        <is>
+          <t>Price_2026-08-10 09:26</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5255,6 +5260,11 @@
         </is>
       </c>
       <c r="RP2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="RQ2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7517,6 +7527,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="RQ3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9815,6 +9830,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="RQ4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12237,6 +12257,11 @@
           <t>$5.32</t>
         </is>
       </c>
+      <c r="RQ5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14659,6 +14684,11 @@
           <t>$3.97</t>
         </is>
       </c>
+      <c r="RQ6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17081,6 +17111,11 @@
           <t>$6.88</t>
         </is>
       </c>
+      <c r="RQ7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19503,6 +19538,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="RQ8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21925,6 +21965,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="RQ9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24347,6 +24392,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="RQ10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -26769,6 +26819,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="RQ11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -29191,6 +29246,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="RQ12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -31613,6 +31673,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="RQ13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -34035,6 +34100,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="RQ14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -36453,6 +36523,11 @@
         </is>
       </c>
       <c r="RP15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="RQ15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -38279,6 +38354,11 @@
           <t>$12.99</t>
         </is>
       </c>
+      <c r="RQ16" t="inlineStr">
+        <is>
+          <t>$12.99</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -40701,6 +40781,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="RQ17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -43123,6 +43208,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="RQ18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -45545,6 +45635,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="RQ19" t="inlineStr">
+        <is>
+          <t>$1.79</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -47967,6 +48062,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="RQ20" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -50389,6 +50489,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="RQ21" t="inlineStr">
+        <is>
+          <t>$1.28</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -52809,6 +52914,11 @@
       <c r="RP22" t="inlineStr">
         <is>
           <t>3.679</t>
+        </is>
+      </c>
+      <c r="RQ22" t="inlineStr">
+        <is>
+          <t>3.649</t>
         </is>
       </c>
     </row>
@@ -55241,6 +55351,11 @@
         </is>
       </c>
       <c r="RP23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="RQ23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -57439,6 +57554,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="RQ24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:RQ24"/>
+  <dimension ref="A1:RR24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2842,6 +2842,11 @@
           <t>Price_2026-08-10 09:26</t>
         </is>
       </c>
+      <c r="RR1" t="inlineStr">
+        <is>
+          <t>Price_2026-08-11 09:00</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5265,6 +5270,11 @@
         </is>
       </c>
       <c r="RQ2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="RR2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7532,6 +7542,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="RR3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9835,6 +9850,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="RR4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12262,6 +12282,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="RR5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14689,6 +14714,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="RR6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17116,6 +17146,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="RR7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19543,6 +19578,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="RR8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21970,6 +22010,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="RR9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24397,6 +24442,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="RR10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -26824,6 +26874,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="RR11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -29251,6 +29306,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="RR12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -31678,6 +31738,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="RR13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -34105,6 +34170,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="RR14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -36528,6 +36598,11 @@
         </is>
       </c>
       <c r="RQ15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="RR15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -38359,6 +38434,11 @@
           <t>$12.99</t>
         </is>
       </c>
+      <c r="RR16" t="inlineStr">
+        <is>
+          <t>$12.99</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -40786,6 +40866,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="RR17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -43213,6 +43298,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="RR18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -45640,6 +45730,11 @@
           <t>$1.79</t>
         </is>
       </c>
+      <c r="RR19" t="inlineStr">
+        <is>
+          <t>$1.79</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -48067,6 +48162,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="RR20" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -50494,6 +50594,11 @@
           <t>$1.28</t>
         </is>
       </c>
+      <c r="RR21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -52917,6 +53022,11 @@
         </is>
       </c>
       <c r="RQ22" t="inlineStr">
+        <is>
+          <t>3.649</t>
+        </is>
+      </c>
+      <c r="RR22" t="inlineStr">
         <is>
           <t>3.649</t>
         </is>
@@ -55356,6 +55466,11 @@
         </is>
       </c>
       <c r="RQ23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="RR23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -57559,6 +57674,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="RR24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:RR24"/>
+  <dimension ref="A1:RS24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2847,6 +2847,11 @@
           <t>Price_2026-08-11 09:00</t>
         </is>
       </c>
+      <c r="RS1" t="inlineStr">
+        <is>
+          <t>Price_2026-08-12 09:18</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5275,6 +5280,11 @@
         </is>
       </c>
       <c r="RR2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="RS2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7547,6 +7557,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="RS3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9855,6 +9870,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="RS4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12287,6 +12307,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="RS5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14719,6 +14744,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="RS6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17151,6 +17181,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="RS7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19583,6 +19618,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="RS8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -22015,6 +22055,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="RS9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24447,6 +24492,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="RS10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -26879,6 +26929,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="RS11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -29311,6 +29366,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="RS12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -31743,6 +31803,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="RS13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -34175,6 +34240,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="RS14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -36603,6 +36673,11 @@
         </is>
       </c>
       <c r="RR15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="RS15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -38439,6 +38514,11 @@
           <t>$12.99</t>
         </is>
       </c>
+      <c r="RS16" t="inlineStr">
+        <is>
+          <t>$14.96</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -40871,6 +40951,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="RS17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -43303,6 +43388,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="RS18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -45735,6 +45825,11 @@
           <t>$1.79</t>
         </is>
       </c>
+      <c r="RS19" t="inlineStr">
+        <is>
+          <t>$1.79</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -48167,6 +48262,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="RS20" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -50599,6 +50699,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="RS21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -53029,6 +53134,11 @@
       <c r="RR22" t="inlineStr">
         <is>
           <t>3.649</t>
+        </is>
+      </c>
+      <c r="RS22" t="inlineStr">
+        <is>
+          <t>3.999</t>
         </is>
       </c>
     </row>
@@ -55471,6 +55581,11 @@
         </is>
       </c>
       <c r="RR23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="RS23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -57679,6 +57794,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="RS24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:RS24"/>
+  <dimension ref="A1:RT24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2852,6 +2852,11 @@
           <t>Price_2026-08-12 09:18</t>
         </is>
       </c>
+      <c r="RT1" t="inlineStr">
+        <is>
+          <t>Price_2026-08-13 09:18</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5285,6 +5290,11 @@
         </is>
       </c>
       <c r="RS2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="RT2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7562,6 +7572,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="RT3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9875,6 +9890,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="RT4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12312,6 +12332,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="RT5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14749,6 +14774,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="RT6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17186,6 +17216,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="RT7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19623,6 +19658,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="RT8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -22060,6 +22100,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="RT9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24497,6 +24542,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="RT10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -26934,6 +26984,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="RT11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -29371,6 +29426,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="RT12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -31808,6 +31868,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="RT13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -34245,6 +34310,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="RT14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -36678,6 +36748,11 @@
         </is>
       </c>
       <c r="RS15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="RT15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -38519,6 +38594,11 @@
           <t>$14.96</t>
         </is>
       </c>
+      <c r="RT16" t="inlineStr">
+        <is>
+          <t>$14.96</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -40956,6 +41036,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="RT17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -43393,6 +43478,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="RT18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -45830,6 +45920,11 @@
           <t>$1.79</t>
         </is>
       </c>
+      <c r="RT19" t="inlineStr">
+        <is>
+          <t>$1.79</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -48267,6 +48362,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="RT20" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -50704,6 +50804,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="RT21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -53137,6 +53242,11 @@
         </is>
       </c>
       <c r="RS22" t="inlineStr">
+        <is>
+          <t>3.999</t>
+        </is>
+      </c>
+      <c r="RT22" t="inlineStr">
         <is>
           <t>3.999</t>
         </is>
@@ -55586,6 +55696,11 @@
         </is>
       </c>
       <c r="RS23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="RT23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -57799,6 +57914,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="RT24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:RT24"/>
+  <dimension ref="A1:RU24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2857,6 +2857,11 @@
           <t>Price_2026-08-13 09:18</t>
         </is>
       </c>
+      <c r="RU1" t="inlineStr">
+        <is>
+          <t>Price_2026-08-14 09:14</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5295,6 +5300,11 @@
         </is>
       </c>
       <c r="RT2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="RU2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7577,6 +7587,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="RU3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9895,6 +9910,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="RU4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12337,6 +12357,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="RU5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14779,6 +14804,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="RU6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17221,6 +17251,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="RU7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19663,6 +19698,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="RU8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -22105,6 +22145,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="RU9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24547,6 +24592,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="RU10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -26989,6 +27039,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="RU11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -29431,6 +29486,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="RU12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -31873,6 +31933,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="RU13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -34315,6 +34380,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="RU14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -36753,6 +36823,11 @@
         </is>
       </c>
       <c r="RT15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="RU15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -38599,6 +38674,11 @@
           <t>$14.96</t>
         </is>
       </c>
+      <c r="RU16" t="inlineStr">
+        <is>
+          <t>$14.96</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -41041,6 +41121,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="RU17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -43483,6 +43568,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="RU18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -45925,6 +46015,11 @@
           <t>$1.79</t>
         </is>
       </c>
+      <c r="RU19" t="inlineStr">
+        <is>
+          <t>$1.79</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -48367,6 +48462,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="RU20" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -50809,6 +50909,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="RU21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -53247,6 +53352,11 @@
         </is>
       </c>
       <c r="RT22" t="inlineStr">
+        <is>
+          <t>3.999</t>
+        </is>
+      </c>
+      <c r="RU22" t="inlineStr">
         <is>
           <t>3.999</t>
         </is>
@@ -55701,6 +55811,11 @@
         </is>
       </c>
       <c r="RT23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="RU23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -57919,6 +58034,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="RU24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:RU24"/>
+  <dimension ref="A1:RV24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2862,6 +2862,11 @@
           <t>Price_2026-08-14 09:14</t>
         </is>
       </c>
+      <c r="RV1" t="inlineStr">
+        <is>
+          <t>Price_2026-08-15 08:33</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5305,6 +5310,11 @@
         </is>
       </c>
       <c r="RU2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="RV2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7592,6 +7602,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="RV3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9915,6 +9930,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="RV4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12362,6 +12382,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="RV5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14809,6 +14834,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="RV6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17256,6 +17286,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="RV7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19703,6 +19738,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="RV8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -22150,6 +22190,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="RV9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24597,6 +24642,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="RV10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -27044,6 +27094,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="RV11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -29491,6 +29546,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="RV12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -31938,6 +31998,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="RV13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -34385,6 +34450,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="RV14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -36828,6 +36898,11 @@
         </is>
       </c>
       <c r="RU15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="RV15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -38679,6 +38754,11 @@
           <t>$14.96</t>
         </is>
       </c>
+      <c r="RV16" t="inlineStr">
+        <is>
+          <t>$14.96</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -41126,6 +41206,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="RV17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -43573,6 +43658,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="RV18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -46020,6 +46110,11 @@
           <t>$1.79</t>
         </is>
       </c>
+      <c r="RV19" t="inlineStr">
+        <is>
+          <t>$1.79</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -48467,6 +48562,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="RV20" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -50914,6 +51014,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="RV21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -53359,6 +53464,11 @@
       <c r="RU22" t="inlineStr">
         <is>
           <t>3.999</t>
+        </is>
+      </c>
+      <c r="RV22" t="inlineStr">
+        <is>
+          <t>3.949</t>
         </is>
       </c>
     </row>
@@ -55816,6 +55926,11 @@
         </is>
       </c>
       <c r="RU23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="RV23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -58039,6 +58154,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="RV24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:RV24"/>
+  <dimension ref="A1:RW24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2867,6 +2867,11 @@
           <t>Price_2026-08-15 08:33</t>
         </is>
       </c>
+      <c r="RW1" t="inlineStr">
+        <is>
+          <t>Price_2026-08-16 08:34</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5315,6 +5320,11 @@
         </is>
       </c>
       <c r="RV2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="RW2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7607,6 +7617,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="RW3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9935,6 +9950,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="RW4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12387,6 +12407,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="RW5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14839,6 +14864,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="RW6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17291,6 +17321,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="RW7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19743,6 +19778,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="RW8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -22195,6 +22235,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="RW9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24647,6 +24692,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="RW10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -27099,6 +27149,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="RW11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -29551,6 +29606,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="RW12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -32003,6 +32063,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="RW13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -34455,6 +34520,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="RW14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -36903,6 +36973,11 @@
         </is>
       </c>
       <c r="RV15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="RW15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -38759,6 +38834,11 @@
           <t>$14.96</t>
         </is>
       </c>
+      <c r="RW16" t="inlineStr">
+        <is>
+          <t>$14.96</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -41211,6 +41291,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="RW17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -43663,6 +43748,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="RW18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -46115,6 +46205,11 @@
           <t>$1.79</t>
         </is>
       </c>
+      <c r="RW19" t="inlineStr">
+        <is>
+          <t>$1.79</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -48567,6 +48662,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="RW20" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -51019,6 +51119,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="RW21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -53469,6 +53574,11 @@
       <c r="RV22" t="inlineStr">
         <is>
           <t>3.949</t>
+        </is>
+      </c>
+      <c r="RW22" t="inlineStr">
+        <is>
+          <t>3.889</t>
         </is>
       </c>
     </row>
@@ -55931,6 +56041,11 @@
         </is>
       </c>
       <c r="RV23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="RW23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -58159,6 +58274,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="RW24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:RW24"/>
+  <dimension ref="A1:RX24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2872,6 +2872,11 @@
           <t>Price_2026-08-16 08:34</t>
         </is>
       </c>
+      <c r="RX1" t="inlineStr">
+        <is>
+          <t>Price_2026-08-17 08:48</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5325,6 +5330,11 @@
         </is>
       </c>
       <c r="RW2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="RX2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7622,6 +7632,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="RX3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9955,6 +9970,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="RX4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12412,6 +12432,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="RX5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14869,6 +14894,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="RX6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17326,6 +17356,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="RX7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19783,6 +19818,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="RX8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -22240,6 +22280,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="RX9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24697,6 +24742,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="RX10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -27154,6 +27204,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="RX11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -29611,6 +29666,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="RX12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -32068,6 +32128,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="RX13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -34525,6 +34590,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="RX14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -36978,6 +37048,11 @@
         </is>
       </c>
       <c r="RW15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="RX15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -38839,6 +38914,11 @@
           <t>$14.96</t>
         </is>
       </c>
+      <c r="RX16" t="inlineStr">
+        <is>
+          <t>$14.96</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -41296,6 +41376,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="RX17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -43753,6 +43838,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="RX18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -46210,6 +46300,11 @@
           <t>$1.79</t>
         </is>
       </c>
+      <c r="RX19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -48667,6 +48762,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="RX20" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -51124,6 +51224,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="RX21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -53577,6 +53682,11 @@
         </is>
       </c>
       <c r="RW22" t="inlineStr">
+        <is>
+          <t>3.889</t>
+        </is>
+      </c>
+      <c r="RX22" t="inlineStr">
         <is>
           <t>3.889</t>
         </is>
@@ -56046,6 +56156,11 @@
         </is>
       </c>
       <c r="RW23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="RX23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -58279,6 +58394,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="RX24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:RX24"/>
+  <dimension ref="A1:RY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2877,6 +2877,11 @@
           <t>Price_2026-08-17 08:48</t>
         </is>
       </c>
+      <c r="RY1" t="inlineStr">
+        <is>
+          <t>Price_2026-08-18 08:42</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5335,6 +5340,11 @@
         </is>
       </c>
       <c r="RX2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="RY2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7637,6 +7647,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="RY3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9975,6 +9990,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="RY4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12437,6 +12457,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="RY5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14899,6 +14924,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="RY6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17361,6 +17391,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="RY7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19823,6 +19858,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="RY8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -22285,6 +22325,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="RY9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24747,6 +24792,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="RY10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -27209,6 +27259,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="RY11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -29671,6 +29726,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="RY12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -32133,6 +32193,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="RY13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -34595,6 +34660,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="RY14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -37053,6 +37123,11 @@
         </is>
       </c>
       <c r="RX15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="RY15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -38919,6 +38994,11 @@
           <t>$14.96</t>
         </is>
       </c>
+      <c r="RY16" t="inlineStr">
+        <is>
+          <t>$14.96</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -41381,6 +41461,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="RY17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -43843,6 +43928,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="RY18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -46305,6 +46395,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="RY19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -48767,6 +48862,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="RY20" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -51229,6 +51329,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="RY21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -53689,6 +53794,11 @@
       <c r="RX22" t="inlineStr">
         <is>
           <t>3.889</t>
+        </is>
+      </c>
+      <c r="RY22" t="inlineStr">
+        <is>
+          <t>4.199</t>
         </is>
       </c>
     </row>
@@ -56161,6 +56271,11 @@
         </is>
       </c>
       <c r="RX23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="RY23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -58399,6 +58514,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="RY24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:RY24"/>
+  <dimension ref="A1:RZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2882,6 +2882,11 @@
           <t>Price_2026-08-18 08:42</t>
         </is>
       </c>
+      <c r="RZ1" t="inlineStr">
+        <is>
+          <t>Price_2026-08-20 08:43</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5345,6 +5350,11 @@
         </is>
       </c>
       <c r="RY2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="RZ2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7652,6 +7662,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="RZ3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9995,6 +10010,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="RZ4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12462,6 +12482,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="RZ5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14929,6 +14954,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="RZ6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17396,6 +17426,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="RZ7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19863,6 +19898,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="RZ8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -22330,6 +22370,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="RZ9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24797,6 +24842,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="RZ10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -27264,6 +27314,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="RZ11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -29731,6 +29786,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="RZ12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -32198,6 +32258,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="RZ13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -34665,6 +34730,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="RZ14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -37128,6 +37198,11 @@
         </is>
       </c>
       <c r="RY15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="RZ15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -38999,6 +39074,11 @@
           <t>$14.96</t>
         </is>
       </c>
+      <c r="RZ16" t="inlineStr">
+        <is>
+          <t>$14.96</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -41466,6 +41546,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="RZ17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -43933,6 +44018,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="RZ18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -46400,6 +46490,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="RZ19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -48867,6 +48962,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="RZ20" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -51334,6 +51434,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="RZ21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -53799,6 +53904,11 @@
       <c r="RY22" t="inlineStr">
         <is>
           <t>4.199</t>
+        </is>
+      </c>
+      <c r="RZ22" t="inlineStr">
+        <is>
+          <t>4.149</t>
         </is>
       </c>
     </row>
@@ -56276,6 +56386,11 @@
         </is>
       </c>
       <c r="RY23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="RZ23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -58519,6 +58634,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="RZ24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:RZ24"/>
+  <dimension ref="A1:SA24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2887,6 +2887,11 @@
           <t>Price_2026-08-20 08:43</t>
         </is>
       </c>
+      <c r="SA1" t="inlineStr">
+        <is>
+          <t>Price_2026-08-21 08:45</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5355,6 +5360,11 @@
         </is>
       </c>
       <c r="RZ2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="SA2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7667,6 +7677,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="SA3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10015,6 +10030,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="SA4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12487,6 +12507,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="SA5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14959,6 +14984,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="SA6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17431,6 +17461,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="SA7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19903,6 +19938,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="SA8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -22375,6 +22415,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="SA9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24847,6 +24892,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="SA10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -27319,6 +27369,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="SA11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -29791,6 +29846,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="SA12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -32263,6 +32323,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="SA13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -34735,6 +34800,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="SA14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -37203,6 +37273,11 @@
         </is>
       </c>
       <c r="RZ15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="SA15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -39079,6 +39154,11 @@
           <t>$14.96</t>
         </is>
       </c>
+      <c r="SA16" t="inlineStr">
+        <is>
+          <t>$14.96</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -41551,6 +41631,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="SA17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -44023,6 +44108,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="SA18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -46495,6 +46585,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="SA19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -48967,6 +49062,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="SA20" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -51439,6 +51539,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="SA21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -53909,6 +54014,11 @@
       <c r="RZ22" t="inlineStr">
         <is>
           <t>4.149</t>
+        </is>
+      </c>
+      <c r="SA22" t="inlineStr">
+        <is>
+          <t>4.129</t>
         </is>
       </c>
     </row>
@@ -56391,6 +56501,11 @@
         </is>
       </c>
       <c r="RZ23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="SA23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -58639,6 +58754,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="SA24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:SA24"/>
+  <dimension ref="A1:SB24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2892,6 +2892,11 @@
           <t>Price_2026-08-21 08:45</t>
         </is>
       </c>
+      <c r="SB1" t="inlineStr">
+        <is>
+          <t>Price_2026-08-22 08:34</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5365,6 +5370,11 @@
         </is>
       </c>
       <c r="SA2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="SB2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7682,6 +7692,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="SB3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10035,6 +10050,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="SB4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12512,6 +12532,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="SB5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14989,6 +15014,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="SB6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17466,6 +17496,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="SB7" t="inlineStr">
+        <is>
+          <t>$8.49</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19943,6 +19978,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="SB8" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -22420,6 +22460,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="SB9" t="inlineStr">
+        <is>
+          <t>$1.96</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24897,6 +24942,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="SB10" t="inlineStr">
+        <is>
+          <t>$2.75</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -27374,6 +27424,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="SB11" t="inlineStr">
+        <is>
+          <t>$3.37</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -29851,6 +29906,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="SB12" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -32328,6 +32388,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="SB13" t="inlineStr">
+        <is>
+          <t>$7.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -34805,6 +34870,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="SB14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -37280,6 +37350,11 @@
       <c r="SA15" t="inlineStr">
         <is>
           <t>$3.99</t>
+        </is>
+      </c>
+      <c r="SB15" t="inlineStr">
+        <is>
+          <t>$4.49</t>
         </is>
       </c>
     </row>
@@ -39159,6 +39234,11 @@
           <t>$14.96</t>
         </is>
       </c>
+      <c r="SB16" t="inlineStr">
+        <is>
+          <t>$14.96</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -41636,6 +41716,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="SB17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -44113,6 +44198,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="SB18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -46590,6 +46680,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="SB19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -49067,6 +49162,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="SB20" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -51544,6 +51644,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="SB21" t="inlineStr">
+        <is>
+          <t>$1.27</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -54017,6 +54122,11 @@
         </is>
       </c>
       <c r="SA22" t="inlineStr">
+        <is>
+          <t>4.129</t>
+        </is>
+      </c>
+      <c r="SB22" t="inlineStr">
         <is>
           <t>4.129</t>
         </is>
@@ -56506,6 +56616,11 @@
         </is>
       </c>
       <c r="SA23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="SB23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -58759,6 +58874,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="SB24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:SB24"/>
+  <dimension ref="A1:SC24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2897,6 +2897,11 @@
           <t>Price_2026-08-22 08:34</t>
         </is>
       </c>
+      <c r="SC1" t="inlineStr">
+        <is>
+          <t>Price_2026-08-23 08:34</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5375,6 +5380,11 @@
         </is>
       </c>
       <c r="SB2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="SC2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7697,6 +7707,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="SC3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10055,6 +10070,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="SC4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12537,6 +12557,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="SC5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15019,6 +15044,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="SC6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17501,6 +17531,11 @@
           <t>$8.49</t>
         </is>
       </c>
+      <c r="SC7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19983,6 +20018,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="SC8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -22465,6 +22505,11 @@
           <t>$1.96</t>
         </is>
       </c>
+      <c r="SC9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24947,6 +24992,11 @@
           <t>$2.75</t>
         </is>
       </c>
+      <c r="SC10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -27429,6 +27479,11 @@
           <t>$3.37</t>
         </is>
       </c>
+      <c r="SC11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -29911,6 +29966,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="SC12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -32393,6 +32453,11 @@
           <t>$7.99</t>
         </is>
       </c>
+      <c r="SC13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -34875,6 +34940,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="SC14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -37355,6 +37425,11 @@
       <c r="SB15" t="inlineStr">
         <is>
           <t>$4.49</t>
+        </is>
+      </c>
+      <c r="SC15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
         </is>
       </c>
     </row>
@@ -39239,6 +39314,11 @@
           <t>$14.96</t>
         </is>
       </c>
+      <c r="SC16" t="inlineStr">
+        <is>
+          <t>$14.96</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -41721,6 +41801,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="SC17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -44203,6 +44288,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="SC18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -46685,6 +46775,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="SC19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -49167,6 +49262,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="SC20" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -51649,6 +51749,11 @@
           <t>$1.27</t>
         </is>
       </c>
+      <c r="SC21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -54129,6 +54234,11 @@
       <c r="SB22" t="inlineStr">
         <is>
           <t>4.129</t>
+        </is>
+      </c>
+      <c r="SC22" t="inlineStr">
+        <is>
+          <t>4.099</t>
         </is>
       </c>
     </row>
@@ -56621,6 +56731,11 @@
         </is>
       </c>
       <c r="SB23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="SC23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -58879,6 +58994,7 @@
           <t>540</t>
         </is>
       </c>
+      <c r="SC24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:SC24"/>
+  <dimension ref="A1:SD24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2902,6 +2902,11 @@
           <t>Price_2026-08-23 08:34</t>
         </is>
       </c>
+      <c r="SD1" t="inlineStr">
+        <is>
+          <t>Price_2026-08-24 08:54</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5385,6 +5390,11 @@
         </is>
       </c>
       <c r="SC2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="SD2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7712,6 +7722,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="SD3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10075,6 +10090,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="SD4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12562,6 +12582,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="SD5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15049,6 +15074,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="SD6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17536,6 +17566,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="SD7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20023,6 +20058,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="SD8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -22510,6 +22550,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="SD9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24997,6 +25042,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="SD10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -27484,6 +27534,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="SD11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -29971,6 +30026,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="SD12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -32458,6 +32518,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="SD13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -34945,6 +35010,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="SD14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -37428,6 +37498,11 @@
         </is>
       </c>
       <c r="SC15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="SD15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -39319,6 +39394,11 @@
           <t>$14.96</t>
         </is>
       </c>
+      <c r="SD16" t="inlineStr">
+        <is>
+          <t>$14.96</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -41806,6 +41886,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="SD17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -44293,6 +44378,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="SD18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -46780,6 +46870,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="SD19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -49267,6 +49362,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="SD20" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -51754,6 +51854,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="SD21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -54239,6 +54344,11 @@
       <c r="SC22" t="inlineStr">
         <is>
           <t>4.099</t>
+        </is>
+      </c>
+      <c r="SD22" t="inlineStr">
+        <is>
+          <t>4.049</t>
         </is>
       </c>
     </row>
@@ -56736,6 +56846,11 @@
         </is>
       </c>
       <c r="SC23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="SD23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -58995,6 +59110,11 @@
         </is>
       </c>
       <c r="SC24" t="inlineStr"/>
+      <c r="SD24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:SD24"/>
+  <dimension ref="A1:SE24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2907,6 +2907,11 @@
           <t>Price_2026-08-24 08:54</t>
         </is>
       </c>
+      <c r="SE1" t="inlineStr">
+        <is>
+          <t>Price_2026-08-25 08:47</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5395,6 +5400,11 @@
         </is>
       </c>
       <c r="SD2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="SE2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7727,6 +7737,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="SE3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10095,6 +10110,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="SE4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12587,6 +12607,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="SE5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15079,6 +15104,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="SE6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17571,6 +17601,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="SE7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20063,6 +20098,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="SE8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -22555,6 +22595,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="SE9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -25047,6 +25092,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="SE10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -27539,6 +27589,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="SE11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -30031,6 +30086,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="SE12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -32523,6 +32583,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="SE13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -35015,6 +35080,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="SE14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -37503,6 +37573,11 @@
         </is>
       </c>
       <c r="SD15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="SE15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -39399,6 +39474,11 @@
           <t>$14.96</t>
         </is>
       </c>
+      <c r="SE16" t="inlineStr">
+        <is>
+          <t>$14.96</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -41891,6 +41971,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="SE17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -44383,6 +44468,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="SE18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -46875,6 +46965,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="SE19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -49367,6 +49462,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="SE20" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -51859,6 +51959,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="SE21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -54347,6 +54452,11 @@
         </is>
       </c>
       <c r="SD22" t="inlineStr">
+        <is>
+          <t>4.049</t>
+        </is>
+      </c>
+      <c r="SE22" t="inlineStr">
         <is>
           <t>4.049</t>
         </is>
@@ -56851,6 +56961,11 @@
         </is>
       </c>
       <c r="SD23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="SE23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -59115,6 +59230,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="SE24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:SE24"/>
+  <dimension ref="A1:SF24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2912,6 +2912,11 @@
           <t>Price_2026-08-25 08:47</t>
         </is>
       </c>
+      <c r="SF1" t="inlineStr">
+        <is>
+          <t>Price_2026-08-26 03:05</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5405,6 +5410,11 @@
         </is>
       </c>
       <c r="SE2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="SF2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7742,6 +7752,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="SF3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10115,6 +10130,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="SF4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12612,6 +12632,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="SF5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15109,6 +15134,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="SF6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17606,6 +17636,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="SF7" t="inlineStr">
+        <is>
+          <t>$8.49</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20103,6 +20138,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="SF8" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -22600,6 +22640,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="SF9" t="inlineStr">
+        <is>
+          <t>$1.96</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -25097,6 +25142,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="SF10" t="inlineStr">
+        <is>
+          <t>$2.75</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -27594,6 +27644,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="SF11" t="inlineStr">
+        <is>
+          <t>$3.37</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -30091,6 +30146,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="SF12" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -32588,6 +32648,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="SF13" t="inlineStr">
+        <is>
+          <t>$7.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -35085,6 +35150,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="SF14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -37580,6 +37650,11 @@
       <c r="SE15" t="inlineStr">
         <is>
           <t>$3.99</t>
+        </is>
+      </c>
+      <c r="SF15" t="inlineStr">
+        <is>
+          <t>$4.49</t>
         </is>
       </c>
     </row>
@@ -39479,6 +39554,11 @@
           <t>$14.96</t>
         </is>
       </c>
+      <c r="SF16" t="inlineStr">
+        <is>
+          <t>$14.96</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -41976,6 +42056,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="SF17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -44473,6 +44558,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="SF18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -46970,6 +47060,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="SF19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -49467,6 +49562,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="SF20" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -51964,6 +52064,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="SF21" t="inlineStr">
+        <is>
+          <t>$1.27</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -54459,6 +54564,11 @@
       <c r="SE22" t="inlineStr">
         <is>
           <t>4.049</t>
+        </is>
+      </c>
+      <c r="SF22" t="inlineStr">
+        <is>
+          <t>3.999</t>
         </is>
       </c>
     </row>
@@ -56966,6 +57076,11 @@
         </is>
       </c>
       <c r="SE23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="SF23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -59235,6 +59350,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="SF24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:SF24"/>
+  <dimension ref="A1:SG24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2917,6 +2917,11 @@
           <t>Price_2026-08-26 03:05</t>
         </is>
       </c>
+      <c r="SG1" t="inlineStr">
+        <is>
+          <t>Price_2026-08-26 08:49</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5415,6 +5420,11 @@
         </is>
       </c>
       <c r="SF2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="SG2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7757,6 +7767,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="SG3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10135,6 +10150,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="SG4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12637,6 +12657,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="SG5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15139,6 +15164,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="SG6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17641,6 +17671,11 @@
           <t>$8.49</t>
         </is>
       </c>
+      <c r="SG7" t="inlineStr">
+        <is>
+          <t>$8.49</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20143,6 +20178,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="SG8" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -22645,6 +22685,11 @@
           <t>$1.96</t>
         </is>
       </c>
+      <c r="SG9" t="inlineStr">
+        <is>
+          <t>$1.96</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -25147,6 +25192,11 @@
           <t>$2.75</t>
         </is>
       </c>
+      <c r="SG10" t="inlineStr">
+        <is>
+          <t>$2.75</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -27649,6 +27699,11 @@
           <t>$3.37</t>
         </is>
       </c>
+      <c r="SG11" t="inlineStr">
+        <is>
+          <t>$3.37</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -30151,6 +30206,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="SG12" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -32653,6 +32713,11 @@
           <t>$7.99</t>
         </is>
       </c>
+      <c r="SG13" t="inlineStr">
+        <is>
+          <t>$7.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -35155,6 +35220,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="SG14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -37653,6 +37723,11 @@
         </is>
       </c>
       <c r="SF15" t="inlineStr">
+        <is>
+          <t>$4.49</t>
+        </is>
+      </c>
+      <c r="SG15" t="inlineStr">
         <is>
           <t>$4.49</t>
         </is>
@@ -39559,6 +39634,11 @@
           <t>$14.96</t>
         </is>
       </c>
+      <c r="SG16" t="inlineStr">
+        <is>
+          <t>$14.96</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -42061,6 +42141,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="SG17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -44563,6 +44648,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="SG18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -47065,6 +47155,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="SG19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -49567,6 +49662,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="SG20" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -52069,6 +52169,11 @@
           <t>$1.27</t>
         </is>
       </c>
+      <c r="SG21" t="inlineStr">
+        <is>
+          <t>$1.27</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -54567,6 +54672,11 @@
         </is>
       </c>
       <c r="SF22" t="inlineStr">
+        <is>
+          <t>3.999</t>
+        </is>
+      </c>
+      <c r="SG22" t="inlineStr">
         <is>
           <t>3.999</t>
         </is>
@@ -57081,6 +57191,11 @@
         </is>
       </c>
       <c r="SF23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="SG23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -59355,6 +59470,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="SG24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:SG24"/>
+  <dimension ref="A1:SH24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2922,6 +2922,11 @@
           <t>Price_2026-08-26 08:49</t>
         </is>
       </c>
+      <c r="SH1" t="inlineStr">
+        <is>
+          <t>Price_2026-08-27 02:25</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5425,6 +5430,11 @@
         </is>
       </c>
       <c r="SG2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="SH2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7772,6 +7782,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="SH3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10155,6 +10170,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="SH4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12662,6 +12682,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="SH5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15169,6 +15194,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="SH6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17676,6 +17706,11 @@
           <t>$8.49</t>
         </is>
       </c>
+      <c r="SH7" t="inlineStr">
+        <is>
+          <t>$8.49</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20183,6 +20218,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="SH8" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -22690,6 +22730,11 @@
           <t>$1.96</t>
         </is>
       </c>
+      <c r="SH9" t="inlineStr">
+        <is>
+          <t>$1.96</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -25197,6 +25242,11 @@
           <t>$2.75</t>
         </is>
       </c>
+      <c r="SH10" t="inlineStr">
+        <is>
+          <t>$2.75</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -27704,6 +27754,11 @@
           <t>$3.37</t>
         </is>
       </c>
+      <c r="SH11" t="inlineStr">
+        <is>
+          <t>$3.37</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -30211,6 +30266,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="SH12" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -32718,6 +32778,11 @@
           <t>$7.99</t>
         </is>
       </c>
+      <c r="SH13" t="inlineStr">
+        <is>
+          <t>$7.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -35225,6 +35290,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="SH14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -37728,6 +37798,11 @@
         </is>
       </c>
       <c r="SG15" t="inlineStr">
+        <is>
+          <t>$4.49</t>
+        </is>
+      </c>
+      <c r="SH15" t="inlineStr">
         <is>
           <t>$4.49</t>
         </is>
@@ -39639,6 +39714,11 @@
           <t>$14.96</t>
         </is>
       </c>
+      <c r="SH16" t="inlineStr">
+        <is>
+          <t>$14.96</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -42146,6 +42226,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="SH17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -44653,6 +44738,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="SH18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -47160,6 +47250,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="SH19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -49667,6 +49762,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="SH20" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -52174,6 +52274,11 @@
           <t>$1.27</t>
         </is>
       </c>
+      <c r="SH21" t="inlineStr">
+        <is>
+          <t>$1.27</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -54679,6 +54784,11 @@
       <c r="SG22" t="inlineStr">
         <is>
           <t>3.999</t>
+        </is>
+      </c>
+      <c r="SH22" t="inlineStr">
+        <is>
+          <t>3.979</t>
         </is>
       </c>
     </row>
@@ -57196,6 +57306,11 @@
         </is>
       </c>
       <c r="SG23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="SH23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -59475,6 +59590,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="SH24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:SH24"/>
+  <dimension ref="A1:SI24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2927,6 +2927,11 @@
           <t>Price_2026-08-27 02:25</t>
         </is>
       </c>
+      <c r="SI1" t="inlineStr">
+        <is>
+          <t>Price_2026-08-27 18:58</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5435,6 +5440,11 @@
         </is>
       </c>
       <c r="SH2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="SI2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7787,6 +7797,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="SI3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10175,6 +10190,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="SI4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12687,6 +12707,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="SI5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15199,6 +15224,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="SI6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17711,6 +17741,11 @@
           <t>$8.49</t>
         </is>
       </c>
+      <c r="SI7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20223,6 +20258,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="SI8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -22735,6 +22775,11 @@
           <t>$1.96</t>
         </is>
       </c>
+      <c r="SI9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -25247,6 +25292,11 @@
           <t>$2.75</t>
         </is>
       </c>
+      <c r="SI10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -27759,6 +27809,11 @@
           <t>$3.37</t>
         </is>
       </c>
+      <c r="SI11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -30271,6 +30326,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="SI12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -32783,6 +32843,11 @@
           <t>$7.99</t>
         </is>
       </c>
+      <c r="SI13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -35295,6 +35360,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="SI14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -37805,6 +37875,11 @@
       <c r="SH15" t="inlineStr">
         <is>
           <t>$4.49</t>
+        </is>
+      </c>
+      <c r="SI15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
         </is>
       </c>
     </row>
@@ -39719,6 +39794,11 @@
           <t>$14.96</t>
         </is>
       </c>
+      <c r="SI16" t="inlineStr">
+        <is>
+          <t>$14.96</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -42231,6 +42311,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="SI17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -44743,6 +44828,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="SI18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -47255,6 +47345,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="SI19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -49767,6 +49862,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="SI20" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -52279,6 +52379,11 @@
           <t>$1.27</t>
         </is>
       </c>
+      <c r="SI21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -54787,6 +54892,11 @@
         </is>
       </c>
       <c r="SH22" t="inlineStr">
+        <is>
+          <t>3.979</t>
+        </is>
+      </c>
+      <c r="SI22" t="inlineStr">
         <is>
           <t>3.979</t>
         </is>
@@ -57311,6 +57421,11 @@
         </is>
       </c>
       <c r="SH23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="SI23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -59595,6 +59710,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="SI24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:SI24"/>
+  <dimension ref="A1:SJ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2932,6 +2932,11 @@
           <t>Price_2026-08-27 18:58</t>
         </is>
       </c>
+      <c r="SJ1" t="inlineStr">
+        <is>
+          <t>Price_2026-08-28 20:01</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5445,6 +5450,11 @@
         </is>
       </c>
       <c r="SI2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="SJ2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7802,6 +7812,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="SJ3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10195,6 +10210,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="SJ4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12712,6 +12732,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="SJ5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15229,6 +15254,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="SJ6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17746,6 +17776,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="SJ7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20263,6 +20298,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="SJ8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -22780,6 +22820,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="SJ9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -25297,6 +25342,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="SJ10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -27814,6 +27864,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="SJ11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -30331,6 +30386,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="SJ12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -32848,6 +32908,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="SJ13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -35365,6 +35430,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="SJ14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -37878,6 +37948,11 @@
         </is>
       </c>
       <c r="SI15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="SJ15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -39799,6 +39874,11 @@
           <t>$14.96</t>
         </is>
       </c>
+      <c r="SJ16" t="inlineStr">
+        <is>
+          <t>$14.96</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -42316,6 +42396,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="SJ17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -44833,6 +44918,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="SJ18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -47350,6 +47440,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="SJ19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -49867,6 +49962,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="SJ20" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -52384,6 +52484,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="SJ21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -54899,6 +55004,11 @@
       <c r="SI22" t="inlineStr">
         <is>
           <t>3.979</t>
+        </is>
+      </c>
+      <c r="SJ22" t="inlineStr">
+        <is>
+          <t>3.899</t>
         </is>
       </c>
     </row>
@@ -57426,6 +57536,11 @@
         </is>
       </c>
       <c r="SI23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="SJ23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -59715,6 +59830,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="SJ24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:SJ24"/>
+  <dimension ref="A1:SK24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2937,6 +2937,11 @@
           <t>Price_2026-08-28 20:01</t>
         </is>
       </c>
+      <c r="SK1" t="inlineStr">
+        <is>
+          <t>Price_2026-08-29 13:45</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5455,6 +5460,11 @@
         </is>
       </c>
       <c r="SJ2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="SK2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7817,6 +7827,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="SK3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10215,6 +10230,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="SK4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12737,6 +12757,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="SK5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15259,6 +15284,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="SK6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17781,6 +17811,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="SK7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20303,6 +20338,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="SK8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -22825,6 +22865,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="SK9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -25347,6 +25392,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="SK10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -27869,6 +27919,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="SK11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -30391,6 +30446,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="SK12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -32913,6 +32973,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="SK13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -35435,6 +35500,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="SK14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -37953,6 +38023,11 @@
         </is>
       </c>
       <c r="SJ15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="SK15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -39879,6 +39954,11 @@
           <t>$14.96</t>
         </is>
       </c>
+      <c r="SK16" t="inlineStr">
+        <is>
+          <t>$14.96</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -42401,6 +42481,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="SK17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -44923,6 +45008,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="SK18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -47445,6 +47535,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="SK19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -49967,6 +50062,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="SK20" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -52489,6 +52589,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="SK21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -55009,6 +55114,11 @@
       <c r="SJ22" t="inlineStr">
         <is>
           <t>3.899</t>
+        </is>
+      </c>
+      <c r="SK22" t="inlineStr">
+        <is>
+          <t>3.879</t>
         </is>
       </c>
     </row>
@@ -57541,6 +57651,11 @@
         </is>
       </c>
       <c r="SJ23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="SK23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -59835,6 +59950,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="SK24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:SK24"/>
+  <dimension ref="A1:SL24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2942,6 +2942,11 @@
           <t>Price_2026-08-29 13:45</t>
         </is>
       </c>
+      <c r="SL1" t="inlineStr">
+        <is>
+          <t>Price_2026-08-30 13:39</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5465,6 +5470,11 @@
         </is>
       </c>
       <c r="SK2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="SL2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7832,6 +7842,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="SL3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10235,6 +10250,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="SL4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12762,6 +12782,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="SL5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15289,6 +15314,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="SL6" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17816,6 +17846,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="SL7" t="inlineStr">
+        <is>
+          <t>$8.49</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20343,6 +20378,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="SL8" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -22870,6 +22910,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="SL9" t="inlineStr">
+        <is>
+          <t>$1.96</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -25397,6 +25442,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="SL10" t="inlineStr">
+        <is>
+          <t>$2.75</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -27924,6 +27974,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="SL11" t="inlineStr">
+        <is>
+          <t>$3.37</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -30451,6 +30506,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="SL12" t="inlineStr">
+        <is>
+          <t>$2.99</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -32978,6 +33038,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="SL13" t="inlineStr">
+        <is>
+          <t>$7.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -35505,6 +35570,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="SL14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -38030,6 +38100,11 @@
       <c r="SK15" t="inlineStr">
         <is>
           <t>$3.99</t>
+        </is>
+      </c>
+      <c r="SL15" t="inlineStr">
+        <is>
+          <t>$4.49</t>
         </is>
       </c>
     </row>
@@ -39959,6 +40034,11 @@
           <t>$14.96</t>
         </is>
       </c>
+      <c r="SL16" t="inlineStr">
+        <is>
+          <t>$14.86</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -42486,6 +42566,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="SL17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -45013,6 +45098,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="SL18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -47540,6 +47630,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="SL19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -50067,6 +50162,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="SL20" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -52594,6 +52694,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="SL21" t="inlineStr">
+        <is>
+          <t>$1.27</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -55119,6 +55224,11 @@
       <c r="SK22" t="inlineStr">
         <is>
           <t>3.879</t>
+        </is>
+      </c>
+      <c r="SL22" t="inlineStr">
+        <is>
+          <t>3.859</t>
         </is>
       </c>
     </row>
@@ -57656,6 +57766,11 @@
         </is>
       </c>
       <c r="SK23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="SL23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -59955,6 +60070,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="SL24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:SL24"/>
+  <dimension ref="A1:SM24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2947,6 +2947,11 @@
           <t>Price_2026-08-30 13:39</t>
         </is>
       </c>
+      <c r="SM1" t="inlineStr">
+        <is>
+          <t>Price_2026-08-31 15:58</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5475,6 +5480,11 @@
         </is>
       </c>
       <c r="SL2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="SM2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7847,6 +7857,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="SM3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10255,6 +10270,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="SM4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12787,6 +12807,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="SM5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15319,6 +15344,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="SM6" t="inlineStr">
+        <is>
+          <t>$3.48</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17851,6 +17881,11 @@
           <t>$8.49</t>
         </is>
       </c>
+      <c r="SM7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20383,6 +20418,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="SM8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -22915,6 +22955,11 @@
           <t>$1.96</t>
         </is>
       </c>
+      <c r="SM9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -25447,6 +25492,11 @@
           <t>$2.75</t>
         </is>
       </c>
+      <c r="SM10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -27979,6 +28029,11 @@
           <t>$3.37</t>
         </is>
       </c>
+      <c r="SM11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -30511,6 +30566,11 @@
           <t>$2.99</t>
         </is>
       </c>
+      <c r="SM12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -33043,6 +33103,11 @@
           <t>$7.99</t>
         </is>
       </c>
+      <c r="SM13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -35575,6 +35640,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="SM14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -38105,6 +38175,11 @@
       <c r="SL15" t="inlineStr">
         <is>
           <t>$4.49</t>
+        </is>
+      </c>
+      <c r="SM15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
         </is>
       </c>
     </row>
@@ -40039,6 +40114,11 @@
           <t>$14.86</t>
         </is>
       </c>
+      <c r="SM16" t="inlineStr">
+        <is>
+          <t>$14.69</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -42571,6 +42651,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="SM17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -45103,6 +45188,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="SM18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -47635,6 +47725,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="SM19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -50167,6 +50262,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="SM20" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -52699,6 +52799,11 @@
           <t>$1.27</t>
         </is>
       </c>
+      <c r="SM21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -55229,6 +55334,11 @@
       <c r="SL22" t="inlineStr">
         <is>
           <t>3.859</t>
+        </is>
+      </c>
+      <c r="SM22" t="inlineStr">
+        <is>
+          <t>3.849</t>
         </is>
       </c>
     </row>
@@ -57771,6 +57881,11 @@
         </is>
       </c>
       <c r="SL23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="SM23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -60075,6 +60190,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="SM24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:SM24"/>
+  <dimension ref="A1:SN24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2952,6 +2952,11 @@
           <t>Price_2026-08-31 15:58</t>
         </is>
       </c>
+      <c r="SN1" t="inlineStr">
+        <is>
+          <t>Price_2026-09-01 13:12</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5485,6 +5490,11 @@
         </is>
       </c>
       <c r="SM2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="SN2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7862,6 +7872,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="SN3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10275,6 +10290,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="SN4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12812,6 +12832,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="SN5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15349,6 +15374,11 @@
           <t>$3.48</t>
         </is>
       </c>
+      <c r="SN6" t="inlineStr">
+        <is>
+          <t>$3.48</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17886,6 +17916,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="SN7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20423,6 +20458,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="SN8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -22960,6 +23000,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="SN9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -25497,6 +25542,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="SN10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -28034,6 +28084,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="SN11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -30571,6 +30626,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="SN12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -33108,6 +33168,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="SN13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -35645,6 +35710,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="SN14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -38178,6 +38248,11 @@
         </is>
       </c>
       <c r="SM15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="SN15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -40119,6 +40194,11 @@
           <t>$14.69</t>
         </is>
       </c>
+      <c r="SN16" t="inlineStr">
+        <is>
+          <t>$14.69</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -42656,6 +42736,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="SN17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -45193,6 +45278,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="SN18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -47730,6 +47820,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="SN19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -50267,6 +50362,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="SN20" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -52804,6 +52904,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="SN21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -55337,6 +55442,11 @@
         </is>
       </c>
       <c r="SM22" t="inlineStr">
+        <is>
+          <t>3.849</t>
+        </is>
+      </c>
+      <c r="SN22" t="inlineStr">
         <is>
           <t>3.849</t>
         </is>
@@ -57886,6 +57996,11 @@
         </is>
       </c>
       <c r="SM23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="SN23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -60195,6 +60310,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="SN24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:SN24"/>
+  <dimension ref="A1:SO24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2957,6 +2957,11 @@
           <t>Price_2026-09-01 13:12</t>
         </is>
       </c>
+      <c r="SO1" t="inlineStr">
+        <is>
+          <t>Price_2026-09-02 12:40</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5495,6 +5500,11 @@
         </is>
       </c>
       <c r="SN2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="SO2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7877,6 +7887,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="SO3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10295,6 +10310,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="SO4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12837,6 +12857,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="SO5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15379,6 +15404,11 @@
           <t>$3.48</t>
         </is>
       </c>
+      <c r="SO6" t="inlineStr">
+        <is>
+          <t>$3.48</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17921,6 +17951,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="SO7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20463,6 +20498,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="SO8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -23005,6 +23045,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="SO9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -25547,6 +25592,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="SO10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -28089,6 +28139,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="SO11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -30631,6 +30686,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="SO12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -33173,6 +33233,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="SO13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -35715,6 +35780,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="SO14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -38253,6 +38323,11 @@
         </is>
       </c>
       <c r="SN15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="SO15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -40199,6 +40274,11 @@
           <t>$14.69</t>
         </is>
       </c>
+      <c r="SO16" t="inlineStr">
+        <is>
+          <t>$14.69</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -42741,6 +42821,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="SO17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -45283,6 +45368,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="SO18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -47825,6 +47915,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="SO19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -50367,6 +50462,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="SO20" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -52909,6 +53009,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="SO21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -55449,6 +55554,11 @@
       <c r="SN22" t="inlineStr">
         <is>
           <t>3.849</t>
+        </is>
+      </c>
+      <c r="SO22" t="inlineStr">
+        <is>
+          <t>3.779</t>
         </is>
       </c>
     </row>
@@ -58001,6 +58111,11 @@
         </is>
       </c>
       <c r="SN23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="SO23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -60315,6 +60430,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="SO24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:SO24"/>
+  <dimension ref="A1:SP24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2962,6 +2962,11 @@
           <t>Price_2026-09-02 12:40</t>
         </is>
       </c>
+      <c r="SP1" t="inlineStr">
+        <is>
+          <t>Price_2026-09-03 12:43</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5505,6 +5510,11 @@
         </is>
       </c>
       <c r="SO2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="SP2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7892,6 +7902,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="SP3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10315,6 +10330,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="SP4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12862,6 +12882,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="SP5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15409,6 +15434,11 @@
           <t>$3.48</t>
         </is>
       </c>
+      <c r="SP6" t="inlineStr">
+        <is>
+          <t>$3.48</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17956,6 +17986,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="SP7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20503,6 +20538,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="SP8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -23050,6 +23090,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="SP9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -25597,6 +25642,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="SP10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -28144,6 +28194,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="SP11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -30691,6 +30746,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="SP12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -33238,6 +33298,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="SP13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -35785,6 +35850,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="SP14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -38328,6 +38398,11 @@
         </is>
       </c>
       <c r="SO15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="SP15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -40279,6 +40354,11 @@
           <t>$14.69</t>
         </is>
       </c>
+      <c r="SP16" t="inlineStr">
+        <is>
+          <t>$14.69</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -42826,6 +42906,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="SP17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -45373,6 +45458,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="SP18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -47920,6 +48010,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="SP19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -50467,6 +50562,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="SP20" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -53014,6 +53114,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="SP21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -55559,6 +55664,11 @@
       <c r="SO22" t="inlineStr">
         <is>
           <t>3.779</t>
+        </is>
+      </c>
+      <c r="SP22" t="inlineStr">
+        <is>
+          <t>3.749</t>
         </is>
       </c>
     </row>
@@ -58116,6 +58226,11 @@
         </is>
       </c>
       <c r="SO23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="SP23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -60435,6 +60550,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="SP24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:SP24"/>
+  <dimension ref="A1:SQ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2967,6 +2967,11 @@
           <t>Price_2026-09-03 12:43</t>
         </is>
       </c>
+      <c r="SQ1" t="inlineStr">
+        <is>
+          <t>Price_2026-09-04 12:39</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5515,6 +5520,11 @@
         </is>
       </c>
       <c r="SP2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="SQ2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7907,6 +7917,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="SQ3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10335,6 +10350,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="SQ4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12887,6 +12907,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="SQ5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15439,6 +15464,11 @@
           <t>$3.48</t>
         </is>
       </c>
+      <c r="SQ6" t="inlineStr">
+        <is>
+          <t>$3.48</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17991,6 +18021,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="SQ7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20543,6 +20578,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="SQ8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -23095,6 +23135,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="SQ9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -25647,6 +25692,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="SQ10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -28199,6 +28249,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="SQ11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -30751,6 +30806,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="SQ12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -33303,6 +33363,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="SQ13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -35855,6 +35920,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="SQ14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -38403,6 +38473,11 @@
         </is>
       </c>
       <c r="SP15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="SQ15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -40359,6 +40434,11 @@
           <t>$14.69</t>
         </is>
       </c>
+      <c r="SQ16" t="inlineStr">
+        <is>
+          <t>$14.69</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -42911,6 +42991,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="SQ17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -45463,6 +45548,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="SQ18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -48015,6 +48105,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="SQ19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -50567,6 +50662,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="SQ20" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -53119,6 +53219,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="SQ21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -55669,6 +55774,11 @@
       <c r="SP22" t="inlineStr">
         <is>
           <t>3.749</t>
+        </is>
+      </c>
+      <c r="SQ22" t="inlineStr">
+        <is>
+          <t>3.899</t>
         </is>
       </c>
     </row>
@@ -58231,6 +58341,11 @@
         </is>
       </c>
       <c r="SP23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="SQ23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -60555,6 +60670,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="SQ24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/price_extractor.xlsx
+++ b/price_extractor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:SQ24"/>
+  <dimension ref="A1:SR24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2972,6 +2972,11 @@
           <t>Price_2026-09-04 12:39</t>
         </is>
       </c>
+      <c r="SR1" t="inlineStr">
+        <is>
+          <t>Price_2026-09-05 11:45</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5525,6 +5530,11 @@
         </is>
       </c>
       <c r="SQ2" t="inlineStr">
+        <is>
+          <t>$36,900*</t>
+        </is>
+      </c>
+      <c r="SR2" t="inlineStr">
         <is>
           <t>$36,900*</t>
         </is>
@@ -7922,6 +7932,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="SR3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10355,6 +10370,11 @@
           <t>Not found</t>
         </is>
       </c>
+      <c r="SR4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12912,6 +12932,11 @@
           <t>$4.78</t>
         </is>
       </c>
+      <c r="SR5" t="inlineStr">
+        <is>
+          <t>$4.78</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15469,6 +15494,11 @@
           <t>$3.48</t>
         </is>
       </c>
+      <c r="SR6" t="inlineStr">
+        <is>
+          <t>$3.48</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18026,6 +18056,11 @@
           <t>$6.99</t>
         </is>
       </c>
+      <c r="SR7" t="inlineStr">
+        <is>
+          <t>$6.99</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -20583,6 +20618,11 @@
           <t>$5.79</t>
         </is>
       </c>
+      <c r="SR8" t="inlineStr">
+        <is>
+          <t>$5.79</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -23140,6 +23180,11 @@
           <t>$1.97</t>
         </is>
       </c>
+      <c r="SR9" t="inlineStr">
+        <is>
+          <t>$1.97</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -25697,6 +25742,11 @@
           <t>$2.78</t>
         </is>
       </c>
+      <c r="SR10" t="inlineStr">
+        <is>
+          <t>$2.78</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -28254,6 +28304,11 @@
           <t>$2.97</t>
         </is>
       </c>
+      <c r="SR11" t="inlineStr">
+        <is>
+          <t>$2.97</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -30811,6 +30866,11 @@
           <t>$3.29</t>
         </is>
       </c>
+      <c r="SR12" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -33368,6 +33428,11 @@
           <t>$8.99</t>
         </is>
       </c>
+      <c r="SR13" t="inlineStr">
+        <is>
+          <t>$8.99</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -35925,6 +35990,11 @@
           <t>$4.97</t>
         </is>
       </c>
+      <c r="SR14" t="inlineStr">
+        <is>
+          <t>$4.97</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -38478,6 +38548,11 @@
         </is>
       </c>
       <c r="SQ15" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
+      <c r="SR15" t="inlineStr">
         <is>
           <t>$3.99</t>
         </is>
@@ -40439,6 +40514,11 @@
           <t>$14.69</t>
         </is>
       </c>
+      <c r="SR16" t="inlineStr">
+        <is>
+          <t>$14.69</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -42996,6 +43076,11 @@
           <t>$5.99</t>
         </is>
       </c>
+      <c r="SR17" t="inlineStr">
+        <is>
+          <t>$5.99</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -45553,6 +45638,11 @@
           <t>$0.50</t>
         </is>
       </c>
+      <c r="SR18" t="inlineStr">
+        <is>
+          <t>$0.50</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -48110,6 +48200,11 @@
           <t>$1.99</t>
         </is>
       </c>
+      <c r="SR19" t="inlineStr">
+        <is>
+          <t>$1.99</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -50667,6 +50762,11 @@
           <t>$3.99</t>
         </is>
       </c>
+      <c r="SR20" t="inlineStr">
+        <is>
+          <t>$3.99</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -53224,6 +53324,11 @@
           <t>$0.97</t>
         </is>
       </c>
+      <c r="SR21" t="inlineStr">
+        <is>
+          <t>$0.97</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -55779,6 +55884,11 @@
       <c r="SQ22" t="inlineStr">
         <is>
           <t>3.899</t>
+        </is>
+      </c>
+      <c r="SR22" t="inlineStr">
+        <is>
+          <t>3.879</t>
         </is>
       </c>
     </row>
@@ -58346,6 +58456,11 @@
         </is>
       </c>
       <c r="SQ23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="SR23" t="inlineStr">
         <is>
           <t>Not found</t>
         </is>
@@ -60675,6 +60790,11 @@
           <t>540</t>
         </is>
       </c>
+      <c r="SR24" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
